--- a/data/data_analysis/market_shares.xlsx
+++ b/data/data_analysis/market_shares.xlsx
@@ -8,13 +8,58 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6F7EAD3-E5FE-47F7-BE83-22E39FB567F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E501A9-D7B5-4775-974D-B5994B5C1D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Supply" sheetId="1" r:id="rId1"/>
+    <sheet name="Price" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Price!$AB$17:$AC$17</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Price!$A$3:$A$124</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">Price!$B$2</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Price!$F$3:$F$124</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Price!$B$2</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Price!$B$2:$F$2</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Price!$B$3:$B$50</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Price!$C$2</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">Price!$C$3:$C$50</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">Price!$D$2</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">Price!$D$3:$D$50</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">Price!$E$2</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">Price!$E$3:$E$50</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Price!$B$3:$B$124</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">Price!$F$2</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">Price!$F$3:$F$50</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">Price!$A$3:$A$124</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">Price!$A$3:$A$172</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">Price!$B$2</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">Price!$B$3:$B$124</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">Price!$B$3:$B$172</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">Price!$C$2</definedName>
+    <definedName name="_xlchart.v1.28" hidden="1">Price!$C$3:$C$124</definedName>
+    <definedName name="_xlchart.v1.29" hidden="1">Price!$C$3:$C$172</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">Price!$C$2</definedName>
+    <definedName name="_xlchart.v1.30" hidden="1">Price!$D$2</definedName>
+    <definedName name="_xlchart.v1.31" hidden="1">Price!$D$3:$D$124</definedName>
+    <definedName name="_xlchart.v1.32" hidden="1">Price!$D$3:$D$172</definedName>
+    <definedName name="_xlchart.v1.33" hidden="1">Price!$E$2</definedName>
+    <definedName name="_xlchart.v1.34" hidden="1">Price!$E$3:$E$124</definedName>
+    <definedName name="_xlchart.v1.35" hidden="1">Price!$E$3:$E$172</definedName>
+    <definedName name="_xlchart.v1.36" hidden="1">Price!$F$2</definedName>
+    <definedName name="_xlchart.v1.37" hidden="1">Price!$F$3:$F$124</definedName>
+    <definedName name="_xlchart.v1.38" hidden="1">Price!$F$3:$F$172</definedName>
+    <definedName name="_xlchart.v1.39" hidden="1">Price!$G$2</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Price!$C$3:$C$124</definedName>
+    <definedName name="_xlchart.v1.40" hidden="1">Price!$G$3:$G$172</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">Price!$D$2</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Price!$D$3:$D$124</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">Price!$E$2</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Price!$E$3:$E$124</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">Price!$F$2</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="26">
   <si>
     <t>Scenario</t>
   </si>
@@ -75,6 +120,45 @@
   </si>
   <si>
     <t>Percentages</t>
+  </si>
+  <si>
+    <t>DACS</t>
+  </si>
+  <si>
+    <t>Paper - R2R figure 6-31, fermentation and liquid fuels techs (not price survey)</t>
+  </si>
+  <si>
+    <t>Paper (min, mean, max for all states in figure c)</t>
+  </si>
+  <si>
+    <t>Paper (low, high)</t>
+  </si>
+  <si>
+    <t>Tech</t>
+  </si>
+  <si>
+    <t>Reference Location</t>
+  </si>
+  <si>
+    <t>Paper (low, best guesses without shipping emissions, high)</t>
+  </si>
+  <si>
+    <t>Carbon Negative Shot (by 2032)</t>
+  </si>
+  <si>
+    <t>100 Mt CDR Baseline</t>
+  </si>
+  <si>
+    <t>500 Mt CDR Baseline</t>
+  </si>
+  <si>
+    <t>1500 Mt CDR Baseline</t>
+  </si>
+  <si>
+    <t>2400 Mt CDR Baseline</t>
+  </si>
+  <si>
+    <t>Cost Data Scenario</t>
   </si>
 </sst>
 </file>
@@ -219,7 +303,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$M$2</c:f>
+              <c:f>Supply!$M$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -240,7 +324,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$8</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -266,7 +350,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$M$3:$M$8</c:f>
+              <c:f>Supply!$M$3:$M$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -302,7 +386,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$N$2</c:f>
+              <c:f>Supply!$N$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -323,7 +407,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$8</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -349,7 +433,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$3:$N$8</c:f>
+              <c:f>Supply!$N$3:$N$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -385,7 +469,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$O$2</c:f>
+              <c:f>Supply!$O$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -406,7 +490,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$8</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -432,7 +516,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$3:$O$8</c:f>
+              <c:f>Supply!$O$3:$O$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -468,7 +552,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$P$2</c:f>
+              <c:f>Supply!$P$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -489,7 +573,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$8</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -515,7 +599,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$P$3:$P$8</c:f>
+              <c:f>Supply!$P$3:$P$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -567,7 +651,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$L$2</c:f>
+              <c:f>Supply!$L$2</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -590,7 +674,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$8</c:f>
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
@@ -616,7 +700,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$3:$L$8</c:f>
+              <c:f>Supply!$L$3:$L$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="6"/>
@@ -1161,7 +1245,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$L$10</c:f>
+              <c:f>Supply!$L$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1184,7 +1268,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$11:$K$15</c:f>
+              <c:f>Supply!$K$11:$K$15</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1207,7 +1291,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$L$11:$L$15</c:f>
+              <c:f>Supply!$L$11:$L$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1241,7 +1325,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$M$10</c:f>
+              <c:f>Supply!$M$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1264,7 +1348,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$11:$K$15</c:f>
+              <c:f>Supply!$K$11:$K$15</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1287,7 +1371,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$M$11:$M$15</c:f>
+              <c:f>Supply!$M$11:$M$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1321,7 +1405,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$N$10</c:f>
+              <c:f>Supply!$N$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1344,7 +1428,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$11:$K$15</c:f>
+              <c:f>Supply!$K$11:$K$15</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1367,7 +1451,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$N$11:$N$15</c:f>
+              <c:f>Supply!$N$11:$N$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1401,7 +1485,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$O$10</c:f>
+              <c:f>Supply!$O$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1424,7 +1508,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$K$11:$K$15</c:f>
+              <c:f>Supply!$K$11:$K$15</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1447,7 +1531,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$O$11:$O$15</c:f>
+              <c:f>Supply!$O$11:$O$15</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1788,6 +1872,205 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.23</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.26</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.23</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.29</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.23</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.32</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="3">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.23</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.35</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="4">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.23</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.38</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="5">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.23</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.40</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0">
+      <cx:tx>
+        <cx:txData>
+          <cx:v>Price of CDR Technologies in 2050 in Various Scenarios</cx:v>
+        </cx:txData>
+      </cx:tx>
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:sysClr>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            </a:rPr>
+            <a:t>Price of CDR Technologies in 2050 in Various Scenarios</a:t>
+          </a:r>
+        </a:p>
+      </cx:txPr>
+    </cx:title>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="boxWhisker" uniqueId="{0C044789-423D-441C-993A-2DB42148760A}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.24</cx:f>
+              <cx:v>100 Mt CDR Baseline</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{151CE232-CE60-4C99-9E11-83DBD658AEAF}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.27</cx:f>
+              <cx:v>500 Mt CDR Baseline</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{77AD6A69-9708-4668-8AF1-086179DBCE24}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.30</cx:f>
+              <cx:v>1500 Mt CDR Baseline</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{5423C862-10EB-4F16-A668-9C9CA0F7E7CF}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.33</cx:f>
+              <cx:v>2400 Mt CDR Baseline</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="3"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{9B47EEC0-5FC0-415E-AB63-380C200229E9}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.36</cx:f>
+              <cx:v>Cost Data Scenario</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="4"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{841F22C0-6E28-4C73-8BEC-9CF000C157BD}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.39</cx:f>
+              <cx:v>Carbon Negative Shot (by 2032)</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="5"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="1"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:title>
+          <cx:tx>
+            <cx:txData>
+              <cx:v>USD2025/t CDR</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:txPr>
+            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr algn="ctr" rtl="0">
+                <a:defRPr/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:sysClr val="windowText" lastClr="000000">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:sysClr>
+                  </a:solidFill>
+                  <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+                </a:rPr>
+                <a:t>USD2025/t CDR</a:t>
+              </a:r>
+            </a:p>
+          </cx:txPr>
+        </cx:title>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+    <cx:legend pos="t" align="ctr" overlay="0"/>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -1868,6 +2151,46 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -2883,6 +3206,521 @@
         <a:noFill/>
       </a:ln>
     </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="406">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2959,6 +3797,89 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>176211</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>123824</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="Chart 3">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0EBA074-D35E-F255-BF6C-5C36714E55C8}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3800475" y="1890711"/>
+              <a:ext cx="6762750" cy="4329113"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-US" sz="1100"/>
+                <a:t>This chart isn't available in your version of Excel.
+Editing this shape or saving this workbook into a different file format will permanently break the chart.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -3702,4 +4623,2920 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{285A091E-E214-4312-84B9-99C43D160339}">
+  <dimension ref="A1:T172"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="1"/>
+      <c r="T1" s="1"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>124.70119090909</v>
+      </c>
+      <c r="C3">
+        <v>132.41414181818101</v>
+      </c>
+      <c r="D3">
+        <v>148.67402454545399</v>
+      </c>
+      <c r="E3">
+        <v>161.581846363636</v>
+      </c>
+      <c r="F3">
+        <v>62.422997946611801</v>
+      </c>
+      <c r="G3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>126.090327272727</v>
+      </c>
+      <c r="C4">
+        <v>136.141186363636</v>
+      </c>
+      <c r="D4">
+        <v>161.02436181818101</v>
+      </c>
+      <c r="E4">
+        <v>166.20625636363599</v>
+      </c>
+      <c r="F4">
+        <v>73.100616016426997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>126.404089090909</v>
+      </c>
+      <c r="C5">
+        <v>136.83475636363599</v>
+      </c>
+      <c r="D5">
+        <v>161.230486363636</v>
+      </c>
+      <c r="E5">
+        <v>172.836845454545</v>
+      </c>
+      <c r="F5">
+        <v>79.671457905544102</v>
+      </c>
+      <c r="H5" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>128.111645454545</v>
+      </c>
+      <c r="C6">
+        <v>138.29093727272701</v>
+      </c>
+      <c r="D6">
+        <v>163.268607272727</v>
+      </c>
+      <c r="E6">
+        <v>180.81398181818099</v>
+      </c>
+      <c r="F6">
+        <v>91.991786447638603</v>
+      </c>
+      <c r="H6" t="s">
+        <v>4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>129.34523181818099</v>
+      </c>
+      <c r="C7">
+        <v>140.36216454545399</v>
+      </c>
+      <c r="D7">
+        <v>163.35944181818101</v>
+      </c>
+      <c r="E7">
+        <v>181.544318181818</v>
+      </c>
+      <c r="F7">
+        <v>99.383983572895204</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>131.15809636363599</v>
+      </c>
+      <c r="C8">
+        <v>146.28787090909</v>
+      </c>
+      <c r="D8">
+        <v>163.74939818181801</v>
+      </c>
+      <c r="E8">
+        <v>183.011645454545</v>
+      </c>
+      <c r="F8">
+        <v>102.669404517453</v>
+      </c>
+      <c r="H8" t="s">
+        <v>2</v>
+      </c>
+      <c r="I8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>132.72790363636301</v>
+      </c>
+      <c r="C9">
+        <v>147.04715454545399</v>
+      </c>
+      <c r="D9">
+        <v>174.78163636363601</v>
+      </c>
+      <c r="E9">
+        <v>192.22486363636301</v>
+      </c>
+      <c r="F9">
+        <v>104.312114989733</v>
+      </c>
+      <c r="H9" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>136.50552272727199</v>
+      </c>
+      <c r="C10">
+        <v>150.92159727272701</v>
+      </c>
+      <c r="D10">
+        <v>175.16427272727199</v>
+      </c>
+      <c r="E10">
+        <v>195.42237272727201</v>
+      </c>
+      <c r="F10">
+        <v>105.133470225872</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>137.10775909090901</v>
+      </c>
+      <c r="C11">
+        <v>153.29560636363601</v>
+      </c>
+      <c r="D11">
+        <v>175.20752727272699</v>
+      </c>
+      <c r="E11">
+        <v>195.700199999999</v>
+      </c>
+      <c r="F11">
+        <v>106.77618069815099</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>137.93674909090899</v>
+      </c>
+      <c r="C12">
+        <v>153.34900909090899</v>
+      </c>
+      <c r="D12">
+        <v>177.69632727272699</v>
+      </c>
+      <c r="E12">
+        <v>195.70851818181799</v>
+      </c>
+      <c r="F12">
+        <v>109.24024640656999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>138.56826545454501</v>
+      </c>
+      <c r="C13">
+        <v>154.645148181818</v>
+      </c>
+      <c r="D13">
+        <v>180.614345454545</v>
+      </c>
+      <c r="E13">
+        <v>199.46833636363601</v>
+      </c>
+      <c r="F13">
+        <v>111.70431211498899</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>141.11179909090899</v>
+      </c>
+      <c r="C14">
+        <v>154.66111909090901</v>
+      </c>
+      <c r="D14">
+        <v>183.387627272727</v>
+      </c>
+      <c r="E14">
+        <v>199.81603636363599</v>
+      </c>
+      <c r="F14">
+        <v>120.739219712525</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>142.93747363636299</v>
+      </c>
+      <c r="C15">
+        <v>154.96672909090901</v>
+      </c>
+      <c r="D15">
+        <v>185.646845454545</v>
+      </c>
+      <c r="E15">
+        <v>200.09719090908999</v>
+      </c>
+      <c r="F15">
+        <v>124.02464065708401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>143.724373636363</v>
+      </c>
+      <c r="C16">
+        <v>155.41042090908999</v>
+      </c>
+      <c r="D16">
+        <v>185.65349999999901</v>
+      </c>
+      <c r="E16">
+        <v>200.36170909090899</v>
+      </c>
+      <c r="F16">
+        <v>126.48870636550301</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17">
+        <v>147.66452999999899</v>
+      </c>
+      <c r="C17">
+        <v>155.75629090909001</v>
+      </c>
+      <c r="D17">
+        <v>192.42949090908999</v>
+      </c>
+      <c r="E17">
+        <v>204.158127272727</v>
+      </c>
+      <c r="F17">
+        <v>131.41683778234</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18">
+        <v>148.29038999999901</v>
+      </c>
+      <c r="C18">
+        <v>156.55866272727201</v>
+      </c>
+      <c r="D18">
+        <v>192.73559999999901</v>
+      </c>
+      <c r="E18">
+        <v>204.68716363636301</v>
+      </c>
+      <c r="F18">
+        <v>132.23819301847999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19">
+        <v>148.65971727272699</v>
+      </c>
+      <c r="C19">
+        <v>159.02117727272699</v>
+      </c>
+      <c r="D19">
+        <v>193.437654545454</v>
+      </c>
+      <c r="E19">
+        <v>205.74689999999899</v>
+      </c>
+      <c r="F19">
+        <v>132.23819301847999</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20">
+        <v>149.08976727272699</v>
+      </c>
+      <c r="C20">
+        <v>163.22019545454501</v>
+      </c>
+      <c r="D20">
+        <v>193.52915454545399</v>
+      </c>
+      <c r="E20">
+        <v>206.658572727272</v>
+      </c>
+      <c r="F20">
+        <v>141.273100616016</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21">
+        <v>149.89929272727201</v>
+      </c>
+      <c r="C21">
+        <v>164.51982818181801</v>
+      </c>
+      <c r="D21">
+        <v>194.216236363636</v>
+      </c>
+      <c r="E21">
+        <v>213.80888181818099</v>
+      </c>
+      <c r="F21">
+        <v>149.48665297741201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22">
+        <v>152.02392272727201</v>
+      </c>
+      <c r="C22">
+        <v>167.90249999999901</v>
+      </c>
+      <c r="D22">
+        <v>198.533372727272</v>
+      </c>
+      <c r="E22">
+        <v>214.69559999999899</v>
+      </c>
+      <c r="F22">
+        <v>152.77207392197101</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23">
+        <v>152.923783636363</v>
+      </c>
+      <c r="C23">
+        <v>168.31009090909001</v>
+      </c>
+      <c r="D23">
+        <v>199.205481818181</v>
+      </c>
+      <c r="E23">
+        <v>218.79313636363599</v>
+      </c>
+      <c r="F23">
+        <v>157.70020533880901</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24">
+        <v>153.716672727272</v>
+      </c>
+      <c r="C24">
+        <v>168.98552727272701</v>
+      </c>
+      <c r="D24">
+        <v>200.15209090908999</v>
+      </c>
+      <c r="E24">
+        <v>221.17879090909</v>
+      </c>
+      <c r="F24">
+        <v>160.164271047227</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25">
+        <v>153.99782727272699</v>
+      </c>
+      <c r="C25">
+        <v>169.37149090909</v>
+      </c>
+      <c r="D25">
+        <v>200.368363636363</v>
+      </c>
+      <c r="E25">
+        <v>230.71808181818099</v>
+      </c>
+      <c r="F25">
+        <v>169.19917864476301</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26">
+        <v>155.03743363636301</v>
+      </c>
+      <c r="C26">
+        <v>170.950281818181</v>
+      </c>
+      <c r="D26">
+        <v>202.96862727272699</v>
+      </c>
+      <c r="E26">
+        <v>231.744545454545</v>
+      </c>
+      <c r="F26">
+        <v>171.66324435318199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27">
+        <v>157.23393272727199</v>
+      </c>
+      <c r="C27">
+        <v>171.06174545454499</v>
+      </c>
+      <c r="D27">
+        <v>204.221345454545</v>
+      </c>
+      <c r="E27">
+        <v>233.57953636363601</v>
+      </c>
+      <c r="F27">
+        <v>177.41273100615999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28">
+        <v>159.99773181818099</v>
+      </c>
+      <c r="C28">
+        <v>174.56037272727201</v>
+      </c>
+      <c r="D28">
+        <v>206.04469090909001</v>
+      </c>
+      <c r="E28">
+        <v>234.74907272727199</v>
+      </c>
+      <c r="F28">
+        <v>189.733059548254</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29">
+        <v>160.102873636363</v>
+      </c>
+      <c r="C29">
+        <v>176.91275454545399</v>
+      </c>
+      <c r="D29">
+        <v>206.18277272727201</v>
+      </c>
+      <c r="E29">
+        <v>235.97184545454499</v>
+      </c>
+      <c r="F29">
+        <v>189.733059548254</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30">
+        <v>160.325468181818</v>
+      </c>
+      <c r="C30">
+        <v>177.375245454545</v>
+      </c>
+      <c r="D30">
+        <v>207.79150909090899</v>
+      </c>
+      <c r="E30">
+        <v>237.687054545454</v>
+      </c>
+      <c r="F30">
+        <v>192.19712525667299</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31">
+        <v>160.64105999999899</v>
+      </c>
+      <c r="C31">
+        <v>180.611018181818</v>
+      </c>
+      <c r="D31">
+        <v>208.719818181818</v>
+      </c>
+      <c r="E31">
+        <v>238.02144545454499</v>
+      </c>
+      <c r="F31">
+        <v>260.369609856262</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32">
+        <v>161.491677272727</v>
+      </c>
+      <c r="C32">
+        <v>182.56579090909</v>
+      </c>
+      <c r="D32">
+        <v>208.906145454545</v>
+      </c>
+      <c r="E32">
+        <v>238.25102727272699</v>
+      </c>
+      <c r="F32">
+        <v>267.76180698151899</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>4</v>
+      </c>
+      <c r="B33">
+        <v>164.58055090908999</v>
+      </c>
+      <c r="C33">
+        <v>183.17967272727199</v>
+      </c>
+      <c r="D33">
+        <v>209.23221818181801</v>
+      </c>
+      <c r="E33">
+        <v>239.13275454545399</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>4</v>
+      </c>
+      <c r="B34">
+        <v>165.94439999999901</v>
+      </c>
+      <c r="C34">
+        <v>187.090881818181</v>
+      </c>
+      <c r="D34">
+        <v>211.66112727272699</v>
+      </c>
+      <c r="E34">
+        <v>240.568472727272</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35">
+        <v>166.83777272727201</v>
+      </c>
+      <c r="C35">
+        <v>188.67133636363599</v>
+      </c>
+      <c r="D35">
+        <v>211.96557272727199</v>
+      </c>
+      <c r="E35">
+        <v>244.68430909090901</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36">
+        <v>170.28316363636301</v>
+      </c>
+      <c r="C36">
+        <v>189.95067272727201</v>
+      </c>
+      <c r="D36">
+        <v>215.50745454545401</v>
+      </c>
+      <c r="E36">
+        <v>246.327981818181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>4</v>
+      </c>
+      <c r="B37">
+        <v>171.56749090909</v>
+      </c>
+      <c r="C37">
+        <v>191.59101818181799</v>
+      </c>
+      <c r="D37">
+        <v>218.650063636363</v>
+      </c>
+      <c r="E37">
+        <v>246.39785454545401</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="B38">
+        <v>172.47916363636301</v>
+      </c>
+      <c r="C38">
+        <v>192.35795454545399</v>
+      </c>
+      <c r="D38">
+        <v>220.32035454545399</v>
+      </c>
+      <c r="E38">
+        <v>246.74222727272701</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39">
+        <v>173.15792727272699</v>
+      </c>
+      <c r="C39">
+        <v>192.97849090909</v>
+      </c>
+      <c r="D39">
+        <v>221.047363636363</v>
+      </c>
+      <c r="E39">
+        <v>247.31119090908999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40">
+        <v>173.88992727272699</v>
+      </c>
+      <c r="C40">
+        <v>193.20474545454499</v>
+      </c>
+      <c r="D40">
+        <v>221.40504545454499</v>
+      </c>
+      <c r="E40">
+        <v>247.73375454545399</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41">
+        <v>177.852709090909</v>
+      </c>
+      <c r="C41">
+        <v>193.25631818181799</v>
+      </c>
+      <c r="D41">
+        <v>221.43665454545399</v>
+      </c>
+      <c r="E41">
+        <v>264.44165454545401</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42">
+        <v>179.451463636363</v>
+      </c>
+      <c r="C42">
+        <v>196.653463636363</v>
+      </c>
+      <c r="D42">
+        <v>226.720363636363</v>
+      </c>
+      <c r="E42">
+        <v>279.32288181818097</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43">
+        <v>179.549618181818</v>
+      </c>
+      <c r="C43">
+        <v>202.40631818181799</v>
+      </c>
+      <c r="D43">
+        <v>228.85813636363599</v>
+      </c>
+      <c r="E43">
+        <v>281.20112727272698</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>4</v>
+      </c>
+      <c r="B44">
+        <v>180.065345454545</v>
+      </c>
+      <c r="C44">
+        <v>204.67219090909001</v>
+      </c>
+      <c r="D44">
+        <v>242.024154545454</v>
+      </c>
+      <c r="E44">
+        <v>293.66009999999898</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45">
+        <v>180.87719999999899</v>
+      </c>
+      <c r="C45">
+        <v>205.43413636363599</v>
+      </c>
+      <c r="D45">
+        <v>295.24887272727199</v>
+      </c>
+      <c r="E45">
+        <v>358.328972727272</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46">
+        <v>181.078499999999</v>
+      </c>
+      <c r="C46">
+        <v>207.71997272727199</v>
+      </c>
+      <c r="D46">
+        <v>305.89281818181797</v>
+      </c>
+      <c r="E46">
+        <v>382.636363636363</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47">
+        <v>182.26799999999901</v>
+      </c>
+      <c r="C47">
+        <v>223.76408181818101</v>
+      </c>
+      <c r="D47">
+        <v>377.39590909090902</v>
+      </c>
+      <c r="E47">
+        <v>478.88105454545399</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48">
+        <v>187.050954545454</v>
+      </c>
+      <c r="C48">
+        <v>233.276754545454</v>
+      </c>
+      <c r="D48">
+        <v>388.60881818181798</v>
+      </c>
+      <c r="E48">
+        <v>483.35290909090901</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>4</v>
+      </c>
+      <c r="B49">
+        <v>189.69779999999901</v>
+      </c>
+      <c r="C49">
+        <v>250.31239090909</v>
+      </c>
+      <c r="D49">
+        <v>404.89914545454502</v>
+      </c>
+      <c r="E49">
+        <v>503.70749999999902</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50">
+        <v>268.73882727272701</v>
+      </c>
+      <c r="D50">
+        <v>466.33058181818097</v>
+      </c>
+      <c r="E50">
+        <v>562.59689999999898</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>3</v>
+      </c>
+      <c r="B51">
+        <v>139.85325818181801</v>
+      </c>
+      <c r="C51">
+        <v>139.673086363636</v>
+      </c>
+      <c r="D51">
+        <v>143.25073636363601</v>
+      </c>
+      <c r="E51">
+        <v>151.90048090908999</v>
+      </c>
+      <c r="F51">
+        <v>120</v>
+      </c>
+      <c r="G51">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52">
+        <v>169.99535454545401</v>
+      </c>
+      <c r="C52">
+        <v>171.820363636363</v>
+      </c>
+      <c r="D52">
+        <v>175.31899090908999</v>
+      </c>
+      <c r="E52">
+        <v>183.57229090908999</v>
+      </c>
+      <c r="F52">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>3</v>
+      </c>
+      <c r="B53">
+        <v>172.17471818181801</v>
+      </c>
+      <c r="C53">
+        <v>177.25879090909001</v>
+      </c>
+      <c r="D53">
+        <v>180.203427272727</v>
+      </c>
+      <c r="E53">
+        <v>187.46187272727201</v>
+      </c>
+      <c r="F53">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>3</v>
+      </c>
+      <c r="B54">
+        <v>172.94664545454501</v>
+      </c>
+      <c r="C54">
+        <v>179.16032727272699</v>
+      </c>
+      <c r="D54">
+        <v>182.41606363636299</v>
+      </c>
+      <c r="E54">
+        <v>190.23681818181799</v>
+      </c>
+      <c r="F54">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55">
+        <v>175.70661818181799</v>
+      </c>
+      <c r="C55">
+        <v>183.910009090909</v>
+      </c>
+      <c r="D55">
+        <v>187.09254545454499</v>
+      </c>
+      <c r="E55">
+        <v>191.830581818181</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>3</v>
+      </c>
+      <c r="B56">
+        <v>180.195109090909</v>
+      </c>
+      <c r="C56">
+        <v>183.973227272727</v>
+      </c>
+      <c r="D56">
+        <v>187.150772727272</v>
+      </c>
+      <c r="E56">
+        <v>194.454136363636</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>3</v>
+      </c>
+      <c r="B57">
+        <v>180.41637272727201</v>
+      </c>
+      <c r="C57">
+        <v>185.98456363636299</v>
+      </c>
+      <c r="D57">
+        <v>187.387009090909</v>
+      </c>
+      <c r="E57">
+        <v>194.876699999999</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>3</v>
+      </c>
+      <c r="B58">
+        <v>180.88219090909001</v>
+      </c>
+      <c r="C58">
+        <v>188.388518181818</v>
+      </c>
+      <c r="D58">
+        <v>191.336481818181</v>
+      </c>
+      <c r="E58">
+        <v>197.55848181818101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59">
+        <v>182.04174545454501</v>
+      </c>
+      <c r="C59">
+        <v>188.90424545454499</v>
+      </c>
+      <c r="D59">
+        <v>192.748909090909</v>
+      </c>
+      <c r="E59">
+        <v>199.386818181818</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>3</v>
+      </c>
+      <c r="B60">
+        <v>188.54989090909001</v>
+      </c>
+      <c r="C60">
+        <v>190.31667272727199</v>
+      </c>
+      <c r="D60">
+        <v>193.860218181818</v>
+      </c>
+      <c r="E60">
+        <v>205.70031818181801</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>3</v>
+      </c>
+      <c r="B61">
+        <v>189.70445454545401</v>
+      </c>
+      <c r="C61">
+        <v>193.14319090909001</v>
+      </c>
+      <c r="D61">
+        <v>197.293963636363</v>
+      </c>
+      <c r="E61">
+        <v>205.96483636363601</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>3</v>
+      </c>
+      <c r="B62">
+        <v>191.015399999999</v>
+      </c>
+      <c r="C62">
+        <v>196.866409090909</v>
+      </c>
+      <c r="D62">
+        <v>199.75780909090901</v>
+      </c>
+      <c r="E62">
+        <v>206.81329090909</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>3</v>
+      </c>
+      <c r="B63">
+        <v>194.45080909090899</v>
+      </c>
+      <c r="C63">
+        <v>203.334627272727</v>
+      </c>
+      <c r="D63">
+        <v>205.92989999999901</v>
+      </c>
+      <c r="E63">
+        <v>212.23175454545401</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>3</v>
+      </c>
+      <c r="B64">
+        <v>197.37880909090899</v>
+      </c>
+      <c r="C64">
+        <v>210.97404545454501</v>
+      </c>
+      <c r="D64">
+        <v>213.75398181818099</v>
+      </c>
+      <c r="E64">
+        <v>220.505018181818</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65">
+        <v>204.39436363636301</v>
+      </c>
+      <c r="C65">
+        <v>212.675945454545</v>
+      </c>
+      <c r="D65">
+        <v>215.583981818181</v>
+      </c>
+      <c r="E65">
+        <v>220.821109090909</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>3</v>
+      </c>
+      <c r="B66">
+        <v>204.75703636363599</v>
+      </c>
+      <c r="C66">
+        <v>216.02484545454499</v>
+      </c>
+      <c r="D66">
+        <v>218.53693636363599</v>
+      </c>
+      <c r="E66">
+        <v>222.649445454545</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>3</v>
+      </c>
+      <c r="B67">
+        <v>205.35927272727201</v>
+      </c>
+      <c r="C67">
+        <v>217.85983636363599</v>
+      </c>
+      <c r="D67">
+        <v>218.73490909090901</v>
+      </c>
+      <c r="E67">
+        <v>225.28131818181799</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>3</v>
+      </c>
+      <c r="B68">
+        <v>212.161881818181</v>
+      </c>
+      <c r="C68">
+        <v>222.36662727272699</v>
+      </c>
+      <c r="D68">
+        <v>224.828809090909</v>
+      </c>
+      <c r="E68">
+        <v>227.84664545454501</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>3</v>
+      </c>
+      <c r="B69">
+        <v>218.309018181818</v>
+      </c>
+      <c r="C69">
+        <v>224.54765454545401</v>
+      </c>
+      <c r="D69">
+        <v>225.193145454545</v>
+      </c>
+      <c r="E69">
+        <v>230.97927272727199</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>3</v>
+      </c>
+      <c r="B70">
+        <v>232.406672727272</v>
+      </c>
+      <c r="C70">
+        <v>226.46249999999901</v>
+      </c>
+      <c r="D70">
+        <v>229.04779090909</v>
+      </c>
+      <c r="E70">
+        <v>235.337999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>3</v>
+      </c>
+      <c r="C71">
+        <v>226.989872727272</v>
+      </c>
+      <c r="D71">
+        <v>229.61509090908999</v>
+      </c>
+      <c r="E71">
+        <v>235.923599999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72">
+        <v>228.999545454545</v>
+      </c>
+      <c r="D72">
+        <v>231.85434545454501</v>
+      </c>
+      <c r="E72">
+        <v>238.384118181818</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73">
+        <v>236.851909090909</v>
+      </c>
+      <c r="D73">
+        <v>241.59327272727199</v>
+      </c>
+      <c r="E73">
+        <v>251.78969999999899</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>417.55609090909002</v>
+      </c>
+      <c r="D74">
+        <v>415.409999999999</v>
+      </c>
+      <c r="E74">
+        <v>413.05096363636301</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D75">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="E75">
+        <v>159.44557090909001</v>
+      </c>
+      <c r="F75">
+        <v>136.587771203155</v>
+      </c>
+      <c r="G75">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>1</v>
+      </c>
+      <c r="C76">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D76">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="E76">
+        <v>163.58735999999899</v>
+      </c>
+      <c r="F76">
+        <v>144.47731755423999</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D77">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="E77">
+        <v>179.27844545454499</v>
+      </c>
+      <c r="F77">
+        <v>151.380670611439</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>1</v>
+      </c>
+      <c r="C78">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D78">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="E78">
+        <v>185.571981818181</v>
+      </c>
+      <c r="F78">
+        <v>228.79684418145899</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>1</v>
+      </c>
+      <c r="C79">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D79">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="E79">
+        <v>186.094363636363</v>
+      </c>
+      <c r="F79">
+        <v>246.05522682445701</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D80">
+        <v>164.902298181818</v>
+      </c>
+      <c r="E80">
+        <v>226.30778181818101</v>
+      </c>
+      <c r="F80">
+        <v>248.02761341222799</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D81">
+        <v>171.832009090909</v>
+      </c>
+      <c r="E81">
+        <v>234.05034545454501</v>
+      </c>
+      <c r="F81">
+        <v>324.45759368836298</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D82">
+        <v>175.981118181818</v>
+      </c>
+      <c r="E82">
+        <v>239.340709090909</v>
+      </c>
+      <c r="F82">
+        <v>328.402366863905</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D83">
+        <v>176.029363636363</v>
+      </c>
+      <c r="E83">
+        <v>239.891372727272</v>
+      </c>
+      <c r="F83">
+        <v>377.712031558185</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D84">
+        <v>181.18996363636299</v>
+      </c>
+      <c r="E84">
+        <v>251.33386363636299</v>
+      </c>
+      <c r="F84">
+        <v>433.43195266272102</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D85">
+        <v>186.12098181818101</v>
+      </c>
+      <c r="E85">
+        <v>251.541818181818</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>1</v>
+      </c>
+      <c r="C86">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D86">
+        <v>187.486827272727</v>
+      </c>
+      <c r="E86">
+        <v>256.09019999999902</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D87">
+        <v>194.379272727272</v>
+      </c>
+      <c r="E87">
+        <v>260.85152727272703</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D88">
+        <v>194.50570909090899</v>
+      </c>
+      <c r="E88">
+        <v>262.54677272727201</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D89">
+        <v>199.849309090909</v>
+      </c>
+      <c r="E89">
+        <v>265.86739090908998</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>1</v>
+      </c>
+      <c r="C90">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D90">
+        <v>200.18702727272699</v>
+      </c>
+      <c r="E90">
+        <v>270.33259090909002</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D91">
+        <v>204.79696363636299</v>
+      </c>
+      <c r="E91">
+        <v>274.31367272727198</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>1</v>
+      </c>
+      <c r="C92">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D92">
+        <v>209.822809090909</v>
+      </c>
+      <c r="E92">
+        <v>281.46564545454498</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>1</v>
+      </c>
+      <c r="C93">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D93">
+        <v>217.067945454545</v>
+      </c>
+      <c r="E93">
+        <v>287.26009090909002</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>1</v>
+      </c>
+      <c r="C94">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D94">
+        <v>217.48219090909001</v>
+      </c>
+      <c r="E94">
+        <v>287.79744545454503</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D95">
+        <v>218.05115454545401</v>
+      </c>
+      <c r="E95">
+        <v>288.51613636363601</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>1</v>
+      </c>
+      <c r="C96">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D96">
+        <v>218.50199999999899</v>
+      </c>
+      <c r="E96">
+        <v>289.99843636363602</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D97">
+        <v>219.53511818181801</v>
+      </c>
+      <c r="E97">
+        <v>292.95804545454502</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>1</v>
+      </c>
+      <c r="C98">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D98">
+        <v>220.69300909090899</v>
+      </c>
+      <c r="E98">
+        <v>294.04273636363598</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D99">
+        <v>221.76106363636299</v>
+      </c>
+      <c r="E99">
+        <v>294.65828181818102</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>1</v>
+      </c>
+      <c r="C100">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D100">
+        <v>222.81913636363601</v>
+      </c>
+      <c r="E100">
+        <v>296.83598181818098</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D101">
+        <v>223.94209090909001</v>
+      </c>
+      <c r="E101">
+        <v>297.53803636363602</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>1</v>
+      </c>
+      <c r="C102">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D102">
+        <v>225.05839090909001</v>
+      </c>
+      <c r="E102">
+        <v>298.04211818181801</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>1</v>
+      </c>
+      <c r="C103">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D103">
+        <v>225.098318181818</v>
+      </c>
+      <c r="E103">
+        <v>301.109863636363</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>1</v>
+      </c>
+      <c r="C104">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D104">
+        <v>227.061409090909</v>
+      </c>
+      <c r="E104">
+        <v>301.24295454545398</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>1</v>
+      </c>
+      <c r="C105">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D105">
+        <v>228.769963636363</v>
+      </c>
+      <c r="E105">
+        <v>302.76019090909</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>1</v>
+      </c>
+      <c r="C106">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D106">
+        <v>229.24909090909</v>
+      </c>
+      <c r="E106">
+        <v>304.497027272727</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>1</v>
+      </c>
+      <c r="C107">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D107">
+        <v>236.18978181818099</v>
+      </c>
+      <c r="E107">
+        <v>307.67956363636301</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D108">
+        <v>236.51419090908999</v>
+      </c>
+      <c r="E108">
+        <v>309.79570909090899</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>1</v>
+      </c>
+      <c r="C109">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D109">
+        <v>239.658463636363</v>
+      </c>
+      <c r="E109">
+        <v>314.72672727272698</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>1</v>
+      </c>
+      <c r="C110">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D110">
+        <v>239.764936363636</v>
+      </c>
+      <c r="E110">
+        <v>314.98958181818102</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>1</v>
+      </c>
+      <c r="C111">
+        <v>147.81808363636301</v>
+      </c>
+      <c r="D111">
+        <v>243.26356363636299</v>
+      </c>
+      <c r="E111">
+        <v>319.28009999999898</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>1</v>
+      </c>
+      <c r="C112">
+        <v>155.371325454545</v>
+      </c>
+      <c r="D112">
+        <v>245.02369090908999</v>
+      </c>
+      <c r="E112">
+        <v>320.424681818181</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>1</v>
+      </c>
+      <c r="C113">
+        <v>159.57084272727201</v>
+      </c>
+      <c r="D113">
+        <v>250.13271818181801</v>
+      </c>
+      <c r="E113">
+        <v>324.26435454545401</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>1</v>
+      </c>
+      <c r="C114">
+        <v>160.489502727272</v>
+      </c>
+      <c r="D114">
+        <v>251.668254545454</v>
+      </c>
+      <c r="E114">
+        <v>329.02900909090903</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1</v>
+      </c>
+      <c r="C115">
+        <v>162.32316272727201</v>
+      </c>
+      <c r="D115">
+        <v>254.742654545454</v>
+      </c>
+      <c r="E115">
+        <v>331.118536363636</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1</v>
+      </c>
+      <c r="C116">
+        <v>163.60715727272699</v>
+      </c>
+      <c r="D116">
+        <v>257.10668181818102</v>
+      </c>
+      <c r="E116">
+        <v>334.32103636363598</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>165.63213545454499</v>
+      </c>
+      <c r="D117">
+        <v>258.77697272727198</v>
+      </c>
+      <c r="E117">
+        <v>336.51703636363601</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1</v>
+      </c>
+      <c r="C118">
+        <v>165.799497272727</v>
+      </c>
+      <c r="D118">
+        <v>260.61861818181802</v>
+      </c>
+      <c r="E118">
+        <v>338.24555454545401</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1</v>
+      </c>
+      <c r="C119">
+        <v>170.58095454545401</v>
+      </c>
+      <c r="D119">
+        <v>263.74791818181802</v>
+      </c>
+      <c r="E119">
+        <v>338.69473636363603</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1</v>
+      </c>
+      <c r="C120">
+        <v>173.82005454545401</v>
+      </c>
+      <c r="D120">
+        <v>263.957536363636</v>
+      </c>
+      <c r="E120">
+        <v>341.64769090908999</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1</v>
+      </c>
+      <c r="C121">
+        <v>179.73927272727201</v>
+      </c>
+      <c r="D121">
+        <v>268.84529999999899</v>
+      </c>
+      <c r="E121">
+        <v>342.58265454545398</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1</v>
+      </c>
+      <c r="C122">
+        <v>192.08678181818101</v>
+      </c>
+      <c r="D122">
+        <v>282.33739090909</v>
+      </c>
+      <c r="E122">
+        <v>358.90958181818098</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>223.62599999999901</v>
+      </c>
+      <c r="D123">
+        <v>305.55010909090902</v>
+      </c>
+      <c r="E123">
+        <v>382.84764545454499</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>13</v>
+      </c>
+      <c r="B124">
+        <v>218.91624545454499</v>
+      </c>
+      <c r="C124">
+        <v>229.071081818181</v>
+      </c>
+      <c r="D124">
+        <v>239.174345454545</v>
+      </c>
+      <c r="E124">
+        <v>240.33889090909</v>
+      </c>
+      <c r="F124">
+        <v>130</v>
+      </c>
+      <c r="G124">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>13</v>
+      </c>
+      <c r="B125">
+        <v>232.50649090908999</v>
+      </c>
+      <c r="C125">
+        <v>240.112636363636</v>
+      </c>
+      <c r="D125">
+        <v>252.075845454545</v>
+      </c>
+      <c r="E125">
+        <v>255.99869999999899</v>
+      </c>
+      <c r="F125">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>13</v>
+      </c>
+      <c r="B126">
+        <v>232.50649090908999</v>
+      </c>
+      <c r="C126">
+        <v>240.112636363636</v>
+      </c>
+      <c r="D126">
+        <v>252.075845454545</v>
+      </c>
+      <c r="E126">
+        <v>255.99869999999899</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>13</v>
+      </c>
+      <c r="B127">
+        <v>232.50649090908999</v>
+      </c>
+      <c r="C127">
+        <v>240.112636363636</v>
+      </c>
+      <c r="D127">
+        <v>252.075845454545</v>
+      </c>
+      <c r="E127">
+        <v>255.99869999999899</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>13</v>
+      </c>
+      <c r="B128">
+        <v>232.50649090908999</v>
+      </c>
+      <c r="C128">
+        <v>240.112636363636</v>
+      </c>
+      <c r="D128">
+        <v>252.075845454545</v>
+      </c>
+      <c r="E128">
+        <v>255.99869999999899</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>13</v>
+      </c>
+      <c r="B129">
+        <v>235.14834545454499</v>
+      </c>
+      <c r="C129">
+        <v>242.97575454545401</v>
+      </c>
+      <c r="D129">
+        <v>257.44939090909003</v>
+      </c>
+      <c r="E129">
+        <v>258.44590909090903</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>13</v>
+      </c>
+      <c r="B130">
+        <v>235.14834545454499</v>
+      </c>
+      <c r="C130">
+        <v>248.998118181818</v>
+      </c>
+      <c r="D130">
+        <v>257.90189999999899</v>
+      </c>
+      <c r="E130">
+        <v>258.44590909090903</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>13</v>
+      </c>
+      <c r="B131">
+        <v>236.58572727272701</v>
+      </c>
+      <c r="C131">
+        <v>248.998118181818</v>
+      </c>
+      <c r="D131">
+        <v>257.90189999999899</v>
+      </c>
+      <c r="E131">
+        <v>263.21056363636302</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>13</v>
+      </c>
+      <c r="B132">
+        <v>241.08087272727201</v>
+      </c>
+      <c r="C132">
+        <v>253.413409090909</v>
+      </c>
+      <c r="D132">
+        <v>262.64159999999998</v>
+      </c>
+      <c r="E132">
+        <v>263.21056363636302</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>13</v>
+      </c>
+      <c r="B133">
+        <v>241.08087272727201</v>
+      </c>
+      <c r="C133">
+        <v>253.413409090909</v>
+      </c>
+      <c r="D133">
+        <v>262.64159999999998</v>
+      </c>
+      <c r="E133">
+        <v>263.21056363636302</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>13</v>
+      </c>
+      <c r="B134">
+        <v>241.08087272727201</v>
+      </c>
+      <c r="C134">
+        <v>253.413409090909</v>
+      </c>
+      <c r="D134">
+        <v>262.64159999999998</v>
+      </c>
+      <c r="E134">
+        <v>263.21056363636302</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>13</v>
+      </c>
+      <c r="B135">
+        <v>241.08087272727201</v>
+      </c>
+      <c r="C135">
+        <v>253.413409090909</v>
+      </c>
+      <c r="D135">
+        <v>262.64159999999998</v>
+      </c>
+      <c r="E135">
+        <v>263.93590909090898</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>13</v>
+      </c>
+      <c r="B136">
+        <v>241.67312727272699</v>
+      </c>
+      <c r="C136">
+        <v>254.10049090909001</v>
+      </c>
+      <c r="D136">
+        <v>263.38191818181798</v>
+      </c>
+      <c r="E136">
+        <v>263.93590909090898</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>13</v>
+      </c>
+      <c r="B137">
+        <v>241.67312727272699</v>
+      </c>
+      <c r="C137">
+        <v>254.10049090909001</v>
+      </c>
+      <c r="D137">
+        <v>263.38191818181798</v>
+      </c>
+      <c r="E137">
+        <v>268.85195454545402</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>13</v>
+      </c>
+      <c r="B138">
+        <v>241.78126363636301</v>
+      </c>
+      <c r="C138">
+        <v>254.719363636363</v>
+      </c>
+      <c r="D138">
+        <v>268.97672727272698</v>
+      </c>
+      <c r="E138">
+        <v>270.56383636363603</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>13</v>
+      </c>
+      <c r="B139">
+        <v>241.78126363636301</v>
+      </c>
+      <c r="C139">
+        <v>254.719363636363</v>
+      </c>
+      <c r="D139">
+        <v>268.97672727272698</v>
+      </c>
+      <c r="E139">
+        <v>270.56383636363603</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>13</v>
+      </c>
+      <c r="B140">
+        <v>241.78126363636301</v>
+      </c>
+      <c r="C140">
+        <v>254.719363636363</v>
+      </c>
+      <c r="D140">
+        <v>268.97672727272698</v>
+      </c>
+      <c r="E140">
+        <v>270.56383636363603</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>13</v>
+      </c>
+      <c r="B141">
+        <v>241.78126363636301</v>
+      </c>
+      <c r="C141">
+        <v>254.719363636363</v>
+      </c>
+      <c r="D141">
+        <v>268.97672727272698</v>
+      </c>
+      <c r="E141">
+        <v>270.56383636363603</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>13</v>
+      </c>
+      <c r="B142">
+        <v>241.78126363636301</v>
+      </c>
+      <c r="C142">
+        <v>254.719363636363</v>
+      </c>
+      <c r="D142">
+        <v>268.97672727272698</v>
+      </c>
+      <c r="E142">
+        <v>270.56383636363603</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>13</v>
+      </c>
+      <c r="B143">
+        <v>242.78609999999901</v>
+      </c>
+      <c r="C143">
+        <v>257.579154545454</v>
+      </c>
+      <c r="D143">
+        <v>272.32063636363603</v>
+      </c>
+      <c r="E143">
+        <v>273.31549090908999</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>13</v>
+      </c>
+      <c r="B144">
+        <v>242.78609999999901</v>
+      </c>
+      <c r="C144">
+        <v>257.579154545454</v>
+      </c>
+      <c r="D144">
+        <v>272.32063636363603</v>
+      </c>
+      <c r="E144">
+        <v>273.31549090908999</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>13</v>
+      </c>
+      <c r="B145">
+        <v>242.78609999999901</v>
+      </c>
+      <c r="C145">
+        <v>258.26956363636299</v>
+      </c>
+      <c r="D145">
+        <v>272.917881818181</v>
+      </c>
+      <c r="E145">
+        <v>273.31549090908999</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>13</v>
+      </c>
+      <c r="B146">
+        <v>242.78609999999901</v>
+      </c>
+      <c r="C146">
+        <v>258.26956363636299</v>
+      </c>
+      <c r="D146">
+        <v>272.917881818181</v>
+      </c>
+      <c r="E146">
+        <v>273.31549090908999</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>13</v>
+      </c>
+      <c r="B147">
+        <v>242.78609999999901</v>
+      </c>
+      <c r="C147">
+        <v>258.26956363636299</v>
+      </c>
+      <c r="D147">
+        <v>272.917881818181</v>
+      </c>
+      <c r="E147">
+        <v>273.31549090908999</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>13</v>
+      </c>
+      <c r="B148">
+        <v>244.09870909090901</v>
+      </c>
+      <c r="C148">
+        <v>258.26956363636299</v>
+      </c>
+      <c r="D148">
+        <v>272.917881818181</v>
+      </c>
+      <c r="E148">
+        <v>276.63777272727202</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>13</v>
+      </c>
+      <c r="B149">
+        <v>244.09870909090901</v>
+      </c>
+      <c r="C149">
+        <v>258.26956363636299</v>
+      </c>
+      <c r="D149">
+        <v>272.917881818181</v>
+      </c>
+      <c r="E149">
+        <v>276.63777272727202</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>13</v>
+      </c>
+      <c r="B150">
+        <v>244.71259090909001</v>
+      </c>
+      <c r="C150">
+        <v>258.26956363636299</v>
+      </c>
+      <c r="D150">
+        <v>273.06428181818097</v>
+      </c>
+      <c r="E150">
+        <v>277.36977272727199</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>13</v>
+      </c>
+      <c r="B151">
+        <v>244.71259090909001</v>
+      </c>
+      <c r="C151">
+        <v>258.26956363636299</v>
+      </c>
+      <c r="D151">
+        <v>273.06428181818097</v>
+      </c>
+      <c r="E151">
+        <v>277.36977272727199</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>13</v>
+      </c>
+      <c r="B152">
+        <v>244.71259090909001</v>
+      </c>
+      <c r="C152">
+        <v>263.67804545454499</v>
+      </c>
+      <c r="D152">
+        <v>273.06428181818097</v>
+      </c>
+      <c r="E152">
+        <v>277.36977272727199</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>13</v>
+      </c>
+      <c r="B153">
+        <v>244.71259090909001</v>
+      </c>
+      <c r="C153">
+        <v>263.67804545454499</v>
+      </c>
+      <c r="D153">
+        <v>273.06428181818097</v>
+      </c>
+      <c r="E153">
+        <v>277.36977272727199</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>13</v>
+      </c>
+      <c r="B154">
+        <v>244.71259090909001</v>
+      </c>
+      <c r="C154">
+        <v>263.67804545454499</v>
+      </c>
+      <c r="D154">
+        <v>273.06428181818097</v>
+      </c>
+      <c r="E154">
+        <v>277.36977272727199</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>13</v>
+      </c>
+      <c r="B155">
+        <v>244.71259090909001</v>
+      </c>
+      <c r="C155">
+        <v>263.67804545454499</v>
+      </c>
+      <c r="D155">
+        <v>273.06428181818097</v>
+      </c>
+      <c r="E155">
+        <v>277.36977272727199</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>13</v>
+      </c>
+      <c r="B156">
+        <v>244.71259090909001</v>
+      </c>
+      <c r="C156">
+        <v>263.67804545454499</v>
+      </c>
+      <c r="D156">
+        <v>273.06428181818097</v>
+      </c>
+      <c r="E156">
+        <v>277.36977272727199</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>13</v>
+      </c>
+      <c r="B157">
+        <v>247.33448181818099</v>
+      </c>
+      <c r="C157">
+        <v>265.80583636363599</v>
+      </c>
+      <c r="D157">
+        <v>281.74679999999898</v>
+      </c>
+      <c r="E157">
+        <v>284.490136363636</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>13</v>
+      </c>
+      <c r="B158">
+        <v>249.354136363636</v>
+      </c>
+      <c r="C158">
+        <v>265.80583636363599</v>
+      </c>
+      <c r="D158">
+        <v>281.74679999999898</v>
+      </c>
+      <c r="E158">
+        <v>284.490136363636</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>13</v>
+      </c>
+      <c r="B159">
+        <v>249.354136363636</v>
+      </c>
+      <c r="C159">
+        <v>265.80583636363599</v>
+      </c>
+      <c r="D159">
+        <v>281.74679999999898</v>
+      </c>
+      <c r="E159">
+        <v>284.490136363636</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>13</v>
+      </c>
+      <c r="B160">
+        <v>249.354136363636</v>
+      </c>
+      <c r="C160">
+        <v>268.261363636363</v>
+      </c>
+      <c r="D160">
+        <v>286.78595454545399</v>
+      </c>
+      <c r="E160">
+        <v>290.31951818181801</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>13</v>
+      </c>
+      <c r="B161">
+        <v>253.57311818181799</v>
+      </c>
+      <c r="C161">
+        <v>268.906854545454</v>
+      </c>
+      <c r="D161">
+        <v>286.94732727272702</v>
+      </c>
+      <c r="E161">
+        <v>293.76823636363599</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>13</v>
+      </c>
+      <c r="B162">
+        <v>254.142081818181</v>
+      </c>
+      <c r="C162">
+        <v>268.906854545454</v>
+      </c>
+      <c r="D162">
+        <v>287.50464545454503</v>
+      </c>
+      <c r="E162">
+        <v>294.48193636363601</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>13</v>
+      </c>
+      <c r="B163">
+        <v>254.142081818181</v>
+      </c>
+      <c r="C163">
+        <v>268.906854545454</v>
+      </c>
+      <c r="D163">
+        <v>287.50464545454503</v>
+      </c>
+      <c r="E163">
+        <v>294.48193636363601</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>13</v>
+      </c>
+      <c r="B164">
+        <v>262.66988181818101</v>
+      </c>
+      <c r="C164">
+        <v>269.06989090909002</v>
+      </c>
+      <c r="D164">
+        <v>287.50464545454503</v>
+      </c>
+      <c r="E164">
+        <v>294.48193636363601</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>13</v>
+      </c>
+      <c r="B165">
+        <v>287.927209090909</v>
+      </c>
+      <c r="C165">
+        <v>285.20383636363601</v>
+      </c>
+      <c r="D165">
+        <v>304.14599999999899</v>
+      </c>
+      <c r="E165">
+        <v>304.35229090909002</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>13</v>
+      </c>
+      <c r="C166">
+        <v>335.04139090909001</v>
+      </c>
+      <c r="D166">
+        <v>363.27662727272701</v>
+      </c>
+      <c r="E166">
+        <v>360.16396363636301</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>13</v>
+      </c>
+      <c r="C167">
+        <v>335.04139090909001</v>
+      </c>
+      <c r="D167">
+        <v>365.600727272727</v>
+      </c>
+      <c r="E167">
+        <v>362.28676363636299</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>13</v>
+      </c>
+      <c r="C168">
+        <v>473.795318181818</v>
+      </c>
+      <c r="D168">
+        <v>365.600727272727</v>
+      </c>
+      <c r="E168">
+        <v>362.28676363636299</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>13</v>
+      </c>
+      <c r="D169">
+        <v>365.600727272727</v>
+      </c>
+      <c r="E169">
+        <v>362.28676363636299</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>13</v>
+      </c>
+      <c r="D170">
+        <v>365.600727272727</v>
+      </c>
+      <c r="E170">
+        <v>362.28676363636299</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>13</v>
+      </c>
+      <c r="D171">
+        <v>365.600727272727</v>
+      </c>
+      <c r="E171">
+        <v>362.28676363636299</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>13</v>
+      </c>
+      <c r="D172">
+        <v>510.668154545454</v>
+      </c>
+      <c r="E172">
+        <v>506.40092727272702</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/data_analysis/market_shares.xlsx
+++ b/data/data_analysis/market_shares.xlsx
@@ -1,63 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E501A9-D7B5-4775-974D-B5994B5C1D23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AE3D2E-5CE6-4504-B788-2F2D35451982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supply" sheetId="1" r:id="rId1"/>
     <sheet name="Price" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Price!$AB$17:$AC$17</definedName>
-    <definedName name="_xlchart.v1.0" hidden="1">Price!$A$3:$A$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Price!$AC$17:$AD$17</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">Price!$A$3:$A$172</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">Price!$B$2</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Price!$F$3:$F$124</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Price!$B$2</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Price!$B$2:$F$2</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Price!$B$3:$B$50</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Price!$C$2</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Price!$C$3:$C$50</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Price!$D$2</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Price!$D$3:$D$50</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Price!$E$2</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Price!$E$3:$E$50</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Price!$B$3:$B$124</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Price!$F$2</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Price!$F$3:$F$50</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Price!$A$3:$A$124</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Price!$A$3:$A$172</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Price!$B$2</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Price!$B$3:$B$124</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Price!$B$3:$B$172</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Price!$C$2</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Price!$C$3:$C$124</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Price!$C$3:$C$172</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">Price!$F$3:$F$172</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">Price!$G$2</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">Price!$G$3:$G$172</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">Price!$H$2</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">Price!$H$3:$H$172</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">Price!$B$3:$B$172</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">Price!$C$2</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Price!$D$2</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Price!$D$3:$D$124</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Price!$D$3:$D$172</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Price!$E$2</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Price!$E$3:$E$124</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Price!$E$3:$E$172</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Price!$F$2</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Price!$F$3:$F$124</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">Price!$F$3:$F$172</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">Price!$G$2</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Price!$C$3:$C$124</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">Price!$G$3:$G$172</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">Price!$C$3:$C$172</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">Price!$D$2</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Price!$D$3:$D$124</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">Price!$D$3:$D$172</definedName>
     <definedName name="_xlchart.v1.7" hidden="1">Price!$E$2</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Price!$E$3:$E$124</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">Price!$E$3:$E$172</definedName>
     <definedName name="_xlchart.v1.9" hidden="1">Price!$F$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -81,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="22">
   <si>
     <t>Scenario</t>
   </si>
@@ -122,9 +96,6 @@
     <t>Percentages</t>
   </si>
   <si>
-    <t>DACS</t>
-  </si>
-  <si>
     <t>Paper - R2R figure 6-31, fermentation and liquid fuels techs (not price survey)</t>
   </si>
   <si>
@@ -143,22 +114,13 @@
     <t>Paper (low, best guesses without shipping emissions, high)</t>
   </si>
   <si>
-    <t>Carbon Negative Shot (by 2032)</t>
+    <t>4Gt Baseline</t>
   </si>
   <si>
-    <t>100 Mt CDR Baseline</t>
+    <t>Carbon Negative Shot</t>
   </si>
   <si>
-    <t>500 Mt CDR Baseline</t>
-  </si>
-  <si>
-    <t>1500 Mt CDR Baseline</t>
-  </si>
-  <si>
-    <t>2400 Mt CDR Baseline</t>
-  </si>
-  <si>
-    <t>Cost Data Scenario</t>
+    <t>Literature</t>
   </si>
 </sst>
 </file>
@@ -236,64 +198,19 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>CDR Market Share in 2050 (%)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.5403517795112316E-2"/>
+          <c:y val="4.6031258447789131E-2"/>
+          <c:w val="0.78103166342154351"/>
+          <c:h val="0.73127493437924174"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="stacked"/>
@@ -314,7 +231,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2"/>
+              <a:schemeClr val="accent1"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -324,9 +241,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Nothing Baseline</c:v>
                 </c:pt>
@@ -343,6 +260,9 @@
                   <c:v>Excess Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4Gt Baseline</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
                 </c:pt>
               </c:strCache>
@@ -350,10 +270,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$M$3:$M$8</c:f>
+              <c:f>Supply!$M$3:$M$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -370,6 +290,9 @@
                   <c:v>13.971358556094</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>33.333333333333336</c:v>
                 </c:pt>
               </c:numCache>
@@ -397,7 +320,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent3"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -407,9 +330,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Nothing Baseline</c:v>
                 </c:pt>
@@ -426,6 +349,9 @@
                   <c:v>Excess Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4Gt Baseline</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
                 </c:pt>
               </c:strCache>
@@ -433,10 +359,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$N$3:$N$8</c:f>
+              <c:f>Supply!$N$3:$N$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>16.05792107972</c:v>
                 </c:pt>
@@ -453,6 +379,9 @@
                   <c:v>20.2156017331953</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>36.896675146341458</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>28.39506172839506</c:v>
                 </c:pt>
               </c:numCache>
@@ -480,7 +409,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent4"/>
+              <a:schemeClr val="accent3"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -490,9 +419,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Nothing Baseline</c:v>
                 </c:pt>
@@ -509,6 +438,9 @@
                   <c:v>Excess Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4Gt Baseline</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
                 </c:pt>
               </c:strCache>
@@ -516,10 +448,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$O$3:$O$8</c:f>
+              <c:f>Supply!$O$3:$O$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>18.7566878367989</c:v>
                 </c:pt>
@@ -536,6 +468,9 @@
                   <c:v>28.493621918617499</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>30.957383796747809</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>18.518518518518519</c:v>
                 </c:pt>
               </c:numCache>
@@ -563,7 +498,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent5"/>
+              <a:schemeClr val="accent4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -573,9 +508,9 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Nothing Baseline</c:v>
                 </c:pt>
@@ -592,6 +527,9 @@
                   <c:v>Excess Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4Gt Baseline</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
                 </c:pt>
               </c:strCache>
@@ -599,10 +537,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$P$3:$P$8</c:f>
+              <c:f>Supply!$P$3:$P$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>65.185391083480994</c:v>
                 </c:pt>
@@ -619,6 +557,9 @@
                   <c:v>37.319417792093098</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>32.145905482926835</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>19.753086419753089</c:v>
                 </c:pt>
               </c:numCache>
@@ -638,7 +579,7 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
+        <c:gapWidth val="50"/>
         <c:overlap val="100"/>
         <c:axId val="1409867312"/>
         <c:axId val="1409872592"/>
@@ -663,7 +604,10 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="7030A0"/>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="75000"/>
+                  <a:lumOff val="25000"/>
+                </a:schemeClr>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -674,9 +618,9 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$3:$K$8</c:f>
+              <c:f>Supply!$K$3:$K$9</c:f>
               <c:strCache>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>Nothing Baseline</c:v>
                 </c:pt>
@@ -693,6 +637,9 @@
                   <c:v>Excess Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4Gt Baseline</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
                 </c:pt>
               </c:strCache>
@@ -700,10 +647,10 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$L$3:$L$8</c:f>
+              <c:f>Supply!$L$3:$L$9</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="7"/>
                 <c:pt idx="0">
                   <c:v>100</c:v>
                 </c:pt>
@@ -720,6 +667,9 @@
                   <c:v>2400</c:v>
                 </c:pt>
                 <c:pt idx="5">
+                  <c:v>4100</c:v>
+                </c:pt>
+                <c:pt idx="6">
                   <c:v>8100</c:v>
                 </c:pt>
               </c:numCache>
@@ -752,61 +702,6 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Scenario Name</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -815,9 +710,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="10000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -829,16 +723,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="85000"/>
+                    <a:lumOff val="15000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -863,10 +757,7 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
+                <a:schemeClr val="bg1"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -880,25 +771,42 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
+                        <a:lumMod val="85000"/>
+                        <a:lumOff val="15000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>%</a:t>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="85000"/>
+                        <a:lumOff val="15000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>Market Share (%)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="4.1472265422498704E-3"/>
+              <c:y val="0.20906648098340128"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -912,16 +820,16 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
+                      <a:lumMod val="85000"/>
+                      <a:lumOff val="15000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -929,13 +837,17 @@
           </c:txPr>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
+        <c:majorTickMark val="in"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln>
-            <a:noFill/>
+            <a:solidFill>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="10000"/>
+              </a:schemeClr>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -944,16 +856,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="85000"/>
+                    <a:lumOff val="15000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -977,30 +889,91 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
+                        <a:lumMod val="85000"/>
+                        <a:lumOff val="15000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="en-US"/>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="85000"/>
+                        <a:lumOff val="15000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>Market Size</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="85000"/>
+                        <a:lumOff val="15000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t> (</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="85000"/>
+                        <a:lumOff val="15000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
                   <a:t>Mt</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> CDR</a:t>
+                  <a:rPr lang="en-US" sz="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="85000"/>
+                        <a:lumOff val="15000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t> CDR)</a:t>
                 </a:r>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="en-US" sz="1200">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="85000"/>
+                      <a:lumOff val="15000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
+          <c:layout>
+            <c:manualLayout>
+              <c:xMode val="edge"/>
+              <c:yMode val="edge"/>
+              <c:x val="0.95893200752705288"/>
+              <c:y val="0.16287385090214052"/>
+            </c:manualLayout>
+          </c:layout>
           <c:overlay val="0"/>
           <c:spPr>
             <a:noFill/>
@@ -1014,30 +987,34 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
                     <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
+                      <a:lumMod val="85000"/>
+                      <a:lumOff val="15000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:majorTickMark val="in"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:spPr>
           <a:noFill/>
           <a:ln>
-            <a:noFill/>
+            <a:solidFill>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="10000"/>
+              </a:schemeClr>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1046,16 +1023,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                    <a:lumMod val="85000"/>
+                    <a:lumOff val="15000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1077,6 +1054,7 @@
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
         <c:crossAx val="1409878352"/>
+        <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
@@ -1105,16 +1083,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -1137,12 +1115,7 @@
       <a:schemeClr val="bg1"/>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1245,7 +1218,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Supply!$L$10</c:f>
+              <c:f>Supply!$L$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1268,7 +1241,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$11:$K$15</c:f>
+              <c:f>Supply!$K$17:$K$21</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1291,7 +1264,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$L$11:$L$15</c:f>
+              <c:f>Supply!$L$17:$L$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1325,7 +1298,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Supply!$M$10</c:f>
+              <c:f>Supply!$M$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1348,7 +1321,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$11:$K$15</c:f>
+              <c:f>Supply!$K$17:$K$21</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1371,7 +1344,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$M$11:$M$15</c:f>
+              <c:f>Supply!$M$17:$M$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1405,7 +1378,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Supply!$N$10</c:f>
+              <c:f>Supply!$N$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1428,7 +1401,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$11:$K$15</c:f>
+              <c:f>Supply!$K$17:$K$21</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1451,7 +1424,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$N$11:$N$15</c:f>
+              <c:f>Supply!$N$17:$N$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1485,7 +1458,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Supply!$O$10</c:f>
+              <c:f>Supply!$O$16</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1508,7 +1481,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Supply!$K$11:$K$15</c:f>
+              <c:f>Supply!$K$17:$K$21</c:f>
               <c:strCache>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
@@ -1531,7 +1504,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Supply!$O$11:$O$15</c:f>
+              <c:f>Supply!$O$17:$O$21</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
@@ -1877,89 +1850,69 @@
   <cx:chartData>
     <cx:data id="0">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.23</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.26</cx:f>
+        <cx:f>_xlchart.v1.2</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="1">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.23</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.29</cx:f>
+        <cx:f>_xlchart.v1.4</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="2">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.23</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.32</cx:f>
+        <cx:f>_xlchart.v1.6</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="3">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.23</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.35</cx:f>
+        <cx:f>_xlchart.v1.8</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="4">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.23</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.38</cx:f>
+        <cx:f>_xlchart.v1.10</cx:f>
       </cx:numDim>
     </cx:data>
     <cx:data id="5">
       <cx:strDim type="cat">
-        <cx:f>_xlchart.v1.23</cx:f>
+        <cx:f>_xlchart.v1.0</cx:f>
       </cx:strDim>
       <cx:numDim type="val">
-        <cx:f>_xlchart.v1.40</cx:f>
+        <cx:f>_xlchart.v1.12</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="6">
+      <cx:strDim type="cat">
+        <cx:f>_xlchart.v1.0</cx:f>
+      </cx:strDim>
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.14</cx:f>
       </cx:numDim>
     </cx:data>
   </cx:chartData>
   <cx:chart>
-    <cx:title pos="t" align="ctr" overlay="0">
-      <cx:tx>
-        <cx:txData>
-          <cx:v>Price of CDR Technologies in 2050 in Various Scenarios</cx:v>
-        </cx:txData>
-      </cx:tx>
-      <cx:txPr>
-        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr" rtl="0">
-            <a:defRPr/>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:sysClr>
-              </a:solidFill>
-              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-            </a:rPr>
-            <a:t>Price of CDR Technologies in 2050 in Various Scenarios</a:t>
-          </a:r>
-        </a:p>
-      </cx:txPr>
-    </cx:title>
     <cx:plotArea>
       <cx:plotAreaRegion>
-        <cx:series layoutId="boxWhisker" uniqueId="{0C044789-423D-441C-993A-2DB42148760A}">
+        <cx:series layoutId="boxWhisker" uniqueId="{8F9FA29F-053B-4A4E-A7C6-524B25B26F3B}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.24</cx:f>
-              <cx:v>100 Mt CDR Baseline</cx:v>
+              <cx:f>_xlchart.v1.1</cx:f>
+              <cx:v>Nothing Baseline</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="0"/>
@@ -1967,11 +1920,11 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{151CE232-CE60-4C99-9E11-83DBD658AEAF}">
+        <cx:series layoutId="boxWhisker" uniqueId="{B4827AC7-5C07-4D68-8B5F-B643BD9607F9}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.27</cx:f>
-              <cx:v>500 Mt CDR Baseline</cx:v>
+              <cx:f>_xlchart.v1.3</cx:f>
+              <cx:v>Low Baseline</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="1"/>
@@ -1979,11 +1932,11 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{77AD6A69-9708-4668-8AF1-086179DBCE24}">
+        <cx:series layoutId="boxWhisker" uniqueId="{C06A787C-1F9D-43E7-B3D3-8CD5F331E828}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.30</cx:f>
-              <cx:v>1500 Mt CDR Baseline</cx:v>
+              <cx:f>_xlchart.v1.5</cx:f>
+              <cx:v>High Baseline</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="2"/>
@@ -1991,11 +1944,11 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{5423C862-10EB-4F16-A668-9C9CA0F7E7CF}">
+        <cx:series layoutId="boxWhisker" uniqueId="{337FC7EB-A405-4DD2-ACD3-3E34BB4A2AB4}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.33</cx:f>
-              <cx:v>2400 Mt CDR Baseline</cx:v>
+              <cx:f>_xlchart.v1.7</cx:f>
+              <cx:v>Excess Baseline</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="3"/>
@@ -2003,11 +1956,11 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{9B47EEC0-5FC0-415E-AB63-380C200229E9}">
+        <cx:series layoutId="boxWhisker" uniqueId="{D85D0C98-3F13-4665-BB79-A6B4C4DD8638}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.36</cx:f>
-              <cx:v>Cost Data Scenario</cx:v>
+              <cx:f>_xlchart.v1.9</cx:f>
+              <cx:v>4Gt Baseline</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="4"/>
@@ -2015,11 +1968,11 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
-        <cx:series layoutId="boxWhisker" uniqueId="{841F22C0-6E28-4C73-8BEC-9CF000C157BD}">
+        <cx:series layoutId="boxWhisker" uniqueId="{D5E03902-5249-4B72-9950-2C88F6AFE025}">
           <cx:tx>
             <cx:txData>
-              <cx:f>_xlchart.v1.39</cx:f>
-              <cx:v>Carbon Negative Shot (by 2032)</cx:v>
+              <cx:f>_xlchart.v1.11</cx:f>
+              <cx:v>Literature</cx:v>
             </cx:txData>
           </cx:tx>
           <cx:dataId val="5"/>
@@ -2027,47 +1980,187 @@
             <cx:statistics quartileMethod="exclusive"/>
           </cx:layoutPr>
         </cx:series>
+        <cx:series layoutId="boxWhisker" uniqueId="{A2560E12-DAF8-43A2-9E0D-66529237389D}">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.13</cx:f>
+              <cx:v>Carbon Negative Shot</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="6"/>
+          <cx:layoutPr>
+            <cx:statistics quartileMethod="exclusive"/>
+          </cx:layoutPr>
+        </cx:series>
       </cx:plotAreaRegion>
       <cx:axis id="0">
-        <cx:catScaling gapWidth="1"/>
+        <cx:catScaling gapWidth="0.300000012"/>
+        <cx:majorTickMarks type="in"/>
         <cx:tickLabels/>
+        <cx:spPr>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </cx:spPr>
+        <cx:txPr>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1200">
+                <a:solidFill>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:txPr>
       </cx:axis>
       <cx:axis id="1">
-        <cx:valScaling/>
+        <cx:valScaling min="50"/>
         <cx:title>
           <cx:tx>
-            <cx:txData>
-              <cx:v>USD2025/t CDR</cx:v>
-            </cx:txData>
+            <cx:rich>
+              <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr algn="ctr" rtl="0">
+                  <a:defRPr>
+                    <a:solidFill>
+                      <a:schemeClr val="bg2">
+                        <a:lumMod val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg2">
+                        <a:lumMod val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  </a:rPr>
+                  <a:t>CDR Credit Price (USD/t CDR)</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="bg2">
+                      <a:lumMod val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                </a:endParaRPr>
+              </a:p>
+            </cx:rich>
           </cx:tx>
-          <cx:txPr>
-            <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr algn="ctr" rtl="0">
-                <a:defRPr/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="900" b="0" i="0" u="none" strike="noStrike" baseline="0">
-                  <a:solidFill>
-                    <a:sysClr val="windowText" lastClr="000000">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:sysClr>
-                  </a:solidFill>
-                  <a:latin typeface="Calibri" panose="020F0502020204030204"/>
-                </a:rPr>
-                <a:t>USD2025/t CDR</a:t>
-              </a:r>
-            </a:p>
-          </cx:txPr>
         </cx:title>
-        <cx:majorGridlines/>
+        <cx:majorGridlines>
+          <cx:spPr>
+            <a:ln>
+              <a:solidFill>
+                <a:schemeClr val="bg1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+            </a:ln>
+          </cx:spPr>
+        </cx:majorGridlines>
+        <cx:majorTickMarks type="in"/>
         <cx:tickLabels/>
+        <cx:spPr>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </a:ln>
+        </cx:spPr>
+        <cx:txPr>
+          <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0">
+              <a:defRPr sz="1050">
+                <a:solidFill>
+                  <a:schemeClr val="bg2">
+                    <a:lumMod val="25000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </cx:txPr>
       </cx:axis>
     </cx:plotArea>
-    <cx:legend pos="t" align="ctr" overlay="0"/>
+    <cx:legend pos="b" align="ctr" overlay="0">
+      <cx:txPr>
+        <a:bodyPr spcFirstLastPara="1" vertOverflow="ellipsis" horzOverflow="overflow" wrap="square" lIns="0" tIns="0" rIns="0" bIns="0" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr" rtl="0">
+            <a:defRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="bg2">
+                  <a:lumMod val="25000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:solidFill>
+              <a:schemeClr val="bg2">
+                <a:lumMod val="25000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:latin typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </cx:txPr>
+    </cx:legend>
   </cx:chart>
+  <cx:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </cx:spPr>
 </cx:chartSpace>
 </file>
 
@@ -3806,16 +3899,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>176211</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>257174</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>166686</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>123824</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>171449</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -3851,8 +3944,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="3800475" y="1890711"/>
-              <a:ext cx="6762750" cy="4329113"/>
+              <a:off x="4524374" y="2262186"/>
+              <a:ext cx="9667875" cy="4329113"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -3888,7 +3981,7 @@
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Custom 1">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3896,34 +3989,34 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="BFBE43"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="74A751"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="698FC6"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="DD9452"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="C16861"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="A577A8"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="72B1B4"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -4148,7 +4241,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P15"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
@@ -4176,6 +4269,9 @@
         <v>10</v>
       </c>
       <c r="H2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" t="s">
         <v>9</v>
       </c>
       <c r="K2" t="s">
@@ -4217,6 +4313,9 @@
         <v>2400</v>
       </c>
       <c r="H3">
+        <v>4100</v>
+      </c>
+      <c r="I3">
         <v>8100</v>
       </c>
       <c r="K3" t="s">
@@ -4258,6 +4357,9 @@
         <v>13.971358556094</v>
       </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>33.333333333333336</v>
       </c>
       <c r="K4" t="s">
@@ -4299,6 +4401,9 @@
         <v>20.2156017331953</v>
       </c>
       <c r="H5">
+        <v>1512.7636809999999</v>
+      </c>
+      <c r="I5">
         <v>28.39506172839506</v>
       </c>
       <c r="K5" t="s">
@@ -4340,6 +4445,9 @@
         <v>28.493621918617499</v>
       </c>
       <c r="H6">
+        <v>1269.2527356666601</v>
+      </c>
+      <c r="I6">
         <v>18.518518518518519</v>
       </c>
       <c r="K6" t="s">
@@ -4381,6 +4489,9 @@
         <v>37.319417792093098</v>
       </c>
       <c r="H7">
+        <v>1317.9821248000001</v>
+      </c>
+      <c r="I7">
         <v>19.753086419753089</v>
       </c>
       <c r="K7" t="s">
@@ -4404,28 +4515,50 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K8" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L8">
-        <v>8100</v>
+        <v>4100</v>
       </c>
       <c r="M8">
-        <v>33.333333333333336</v>
+        <f>H4/H3</f>
+        <v>0</v>
       </c>
       <c r="N8">
-        <v>28.39506172839506</v>
+        <f>100*H5/H3</f>
+        <v>36.896675146341458</v>
       </c>
       <c r="O8">
-        <v>18.518518518518519</v>
+        <f>100*H6/H3</f>
+        <v>30.957383796747809</v>
       </c>
       <c r="P8">
-        <v>19.753086419753089</v>
+        <f>100*H7/H3</f>
+        <v>32.145905482926835</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="K9" t="s">
+        <v>9</v>
+      </c>
+      <c r="L9">
+        <v>8100</v>
+      </c>
+      <c r="M9">
+        <v>33.333333333333336</v>
+      </c>
+      <c r="N9">
+        <v>28.39506172839506</v>
+      </c>
+      <c r="O9">
+        <v>18.518518518518519</v>
+      </c>
+      <c r="P9">
+        <v>19.753086419753089</v>
+      </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
@@ -4446,21 +4579,6 @@
       <c r="G10" t="s">
         <v>10</v>
       </c>
-      <c r="K10" t="s">
-        <v>0</v>
-      </c>
-      <c r="L10" t="s">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>2</v>
-      </c>
-      <c r="N10" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" t="s">
-        <v>4</v>
-      </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
@@ -4481,21 +4599,6 @@
       <c r="G11">
         <v>335.31257099999999</v>
       </c>
-      <c r="K11" t="s">
-        <v>5</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>15.9971258333333</v>
-      </c>
-      <c r="N11">
-        <v>18.685675066666601</v>
-      </c>
-      <c r="O11">
-        <v>64.938599366666594</v>
-      </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
@@ -4516,21 +4619,6 @@
       <c r="G12">
         <v>485.17439189999999</v>
       </c>
-      <c r="K12" t="s">
-        <v>6</v>
-      </c>
-      <c r="L12">
-        <v>206.888348333333</v>
-      </c>
-      <c r="M12">
-        <v>49.988974566666599</v>
-      </c>
-      <c r="N12">
-        <v>65.061545266666599</v>
-      </c>
-      <c r="O12">
-        <v>177.878598333333</v>
-      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
@@ -4551,21 +4639,6 @@
       <c r="G13">
         <v>683.846856</v>
       </c>
-      <c r="K13" t="s">
-        <v>7</v>
-      </c>
-      <c r="L13">
-        <v>710</v>
-      </c>
-      <c r="M13">
-        <v>200</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
@@ -4586,36 +4659,106 @@
       <c r="G14">
         <v>895.665935266666</v>
       </c>
-      <c r="K14" t="s">
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="K16" t="s">
+        <v>0</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1</v>
+      </c>
+      <c r="M16" t="s">
+        <v>2</v>
+      </c>
+      <c r="N16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O16" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K17" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>15.9971258333333</v>
+      </c>
+      <c r="N17">
+        <v>18.685675066666601</v>
+      </c>
+      <c r="O17">
+        <v>64.938599366666594</v>
+      </c>
+    </row>
+    <row r="18" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K18" t="s">
+        <v>6</v>
+      </c>
+      <c r="L18">
+        <v>206.888348333333</v>
+      </c>
+      <c r="M18">
+        <v>49.988974566666599</v>
+      </c>
+      <c r="N18">
+        <v>65.061545266666599</v>
+      </c>
+      <c r="O18">
+        <v>177.878598333333</v>
+      </c>
+    </row>
+    <row r="19" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K19" t="s">
+        <v>7</v>
+      </c>
+      <c r="L19">
+        <v>710</v>
+      </c>
+      <c r="M19">
+        <v>200</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K20" t="s">
         <v>8</v>
       </c>
-      <c r="L14">
+      <c r="L20">
         <v>348.79311866666598</v>
       </c>
-      <c r="M14">
+      <c r="M20">
         <v>229.705339966666</v>
       </c>
-      <c r="N14">
+      <c r="N20">
         <v>345.10346199999998</v>
       </c>
-      <c r="O14">
+      <c r="O20">
         <v>576.39836760000003</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="K15" t="s">
+    <row r="21" spans="11:15" x14ac:dyDescent="0.25">
+      <c r="K21" t="s">
         <v>10</v>
       </c>
-      <c r="L15">
+      <c r="L21">
         <v>335.31257099999999</v>
       </c>
-      <c r="M15">
+      <c r="M21">
         <v>485.17439189999999</v>
       </c>
-      <c r="N15">
+      <c r="N21">
         <v>683.846856</v>
       </c>
-      <c r="O15">
+      <c r="O21">
         <v>895.665935266666</v>
       </c>
     </row>
@@ -4627,40 +4770,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{285A091E-E214-4312-84B9-99C43D160339}">
-  <dimension ref="A1:T172"/>
+  <dimension ref="A1:U172"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="1"/>
-      <c r="T1" s="1"/>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="O1" s="1"/>
+      <c r="U1" s="1"/>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -4677,13 +4823,16 @@
         <v>161.581846363636</v>
       </c>
       <c r="F3">
+        <v>175.578518181818</v>
+      </c>
+      <c r="G3">
         <v>62.422997946611801</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -4700,10 +4849,13 @@
         <v>166.20625636363599</v>
       </c>
       <c r="F4">
+        <v>182.402754545454</v>
+      </c>
+      <c r="G4">
         <v>73.100616016426997</v>
       </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -4720,16 +4872,19 @@
         <v>172.836845454545</v>
       </c>
       <c r="F5">
+        <v>190.28672727272701</v>
+      </c>
+      <c r="G5">
         <v>79.671457905544102</v>
       </c>
-      <c r="H5" t="s">
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
         <v>17</v>
       </c>
-      <c r="I5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4746,16 +4901,19 @@
         <v>180.81398181818099</v>
       </c>
       <c r="F6">
+        <v>198.528381818181</v>
+      </c>
+      <c r="G6">
         <v>91.991786447638603</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>4</v>
       </c>
-      <c r="I6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>4</v>
       </c>
@@ -4772,16 +4930,19 @@
         <v>181.544318181818</v>
       </c>
       <c r="F7">
+        <v>208.46528181818101</v>
+      </c>
+      <c r="G7">
         <v>99.383983572895204</v>
       </c>
-      <c r="H7" t="s">
+      <c r="I7" t="s">
         <v>1</v>
       </c>
-      <c r="I7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -4798,16 +4959,19 @@
         <v>183.011645454545</v>
       </c>
       <c r="F8">
+        <v>212.17519090908999</v>
+      </c>
+      <c r="G8">
         <v>102.669404517453</v>
       </c>
-      <c r="H8" t="s">
+      <c r="I8" t="s">
         <v>2</v>
       </c>
-      <c r="I8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -4824,16 +4988,19 @@
         <v>192.22486363636301</v>
       </c>
       <c r="F9">
+        <v>212.755799999999</v>
+      </c>
+      <c r="G9">
         <v>104.312114989733</v>
       </c>
-      <c r="H9" t="s">
+      <c r="I9" t="s">
         <v>3</v>
       </c>
-      <c r="I9" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="J9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
@@ -4850,10 +5017,13 @@
         <v>195.42237272727201</v>
       </c>
       <c r="F10">
+        <v>216.72523636363599</v>
+      </c>
+      <c r="G10">
         <v>105.133470225872</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -4870,10 +5040,13 @@
         <v>195.700199999999</v>
       </c>
       <c r="F11">
+        <v>219.72310909090899</v>
+      </c>
+      <c r="G11">
         <v>106.77618069815099</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>4</v>
       </c>
@@ -4890,10 +5063,13 @@
         <v>195.70851818181799</v>
       </c>
       <c r="F12">
+        <v>219.86618181818099</v>
+      </c>
+      <c r="G12">
         <v>109.24024640656999</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>4</v>
       </c>
@@ -4910,10 +5086,13 @@
         <v>199.46833636363601</v>
       </c>
       <c r="F13">
+        <v>220.616481818181</v>
+      </c>
+      <c r="G13">
         <v>111.70431211498899</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>4</v>
       </c>
@@ -4930,10 +5109,13 @@
         <v>199.81603636363599</v>
       </c>
       <c r="F14">
+        <v>222.448145454545</v>
+      </c>
+      <c r="G14">
         <v>120.739219712525</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -4950,10 +5132,13 @@
         <v>200.09719090908999</v>
       </c>
       <c r="F15">
+        <v>223.95706363636299</v>
+      </c>
+      <c r="G15">
         <v>124.02464065708401</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
@@ -4970,10 +5155,13 @@
         <v>200.36170909090899</v>
       </c>
       <c r="F16">
+        <v>225.284645454545</v>
+      </c>
+      <c r="G16">
         <v>126.48870636550301</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>4</v>
       </c>
@@ -4990,10 +5178,13 @@
         <v>204.158127272727</v>
       </c>
       <c r="F17">
+        <v>225.92348181818099</v>
+      </c>
+      <c r="G17">
         <v>131.41683778234</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>4</v>
       </c>
@@ -5010,10 +5201,13 @@
         <v>204.68716363636301</v>
       </c>
       <c r="F18">
+        <v>228.34074545454499</v>
+      </c>
+      <c r="G18">
         <v>132.23819301847999</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -5030,10 +5224,13 @@
         <v>205.74689999999899</v>
       </c>
       <c r="F19">
+        <v>229.94449090909001</v>
+      </c>
+      <c r="G19">
         <v>132.23819301847999</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>4</v>
       </c>
@@ -5050,10 +5247,13 @@
         <v>206.658572727272</v>
       </c>
       <c r="F20">
+        <v>238.450663636363</v>
+      </c>
+      <c r="G20">
         <v>141.273100616016</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>4</v>
       </c>
@@ -5070,10 +5270,13 @@
         <v>213.80888181818099</v>
       </c>
       <c r="F21">
+        <v>245.87879999999899</v>
+      </c>
+      <c r="G21">
         <v>149.48665297741201</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -5090,10 +5293,13 @@
         <v>214.69559999999899</v>
       </c>
       <c r="F22">
+        <v>247.071627272727</v>
+      </c>
+      <c r="G22">
         <v>152.77207392197101</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>4</v>
       </c>
@@ -5110,10 +5316,13 @@
         <v>218.79313636363599</v>
       </c>
       <c r="F23">
+        <v>248.765209090909</v>
+      </c>
+      <c r="G23">
         <v>157.70020533880901</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>4</v>
       </c>
@@ -5130,10 +5339,13 @@
         <v>221.17879090909</v>
       </c>
       <c r="F24">
+        <v>259.13964545454502</v>
+      </c>
+      <c r="G24">
         <v>160.164271047227</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>4</v>
       </c>
@@ -5150,10 +5362,13 @@
         <v>230.71808181818099</v>
       </c>
       <c r="F25">
+        <v>269.04160909090899</v>
+      </c>
+      <c r="G25">
         <v>169.19917864476301</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>4</v>
       </c>
@@ -5170,10 +5385,13 @@
         <v>231.744545454545</v>
       </c>
       <c r="F26">
+        <v>271.06126363636298</v>
+      </c>
+      <c r="G26">
         <v>171.66324435318199</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>4</v>
       </c>
@@ -5190,10 +5408,13 @@
         <v>233.57953636363601</v>
       </c>
       <c r="F27">
+        <v>290.44595454545401</v>
+      </c>
+      <c r="G27">
         <v>177.41273100615999</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>4</v>
       </c>
@@ -5210,10 +5431,13 @@
         <v>234.74907272727199</v>
       </c>
       <c r="F28">
+        <v>298.95212727272701</v>
+      </c>
+      <c r="G28">
         <v>189.733059548254</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>4</v>
       </c>
@@ -5230,10 +5454,13 @@
         <v>235.97184545454499</v>
       </c>
       <c r="F29">
+        <v>299.20832727272699</v>
+      </c>
+      <c r="G29">
         <v>189.733059548254</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>4</v>
       </c>
@@ -5250,10 +5477,13 @@
         <v>237.687054545454</v>
       </c>
       <c r="F30">
+        <v>299.93367272727198</v>
+      </c>
+      <c r="G30">
         <v>192.19712525667299</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>4</v>
       </c>
@@ -5270,10 +5500,13 @@
         <v>238.02144545454499</v>
       </c>
       <c r="F31">
+        <v>304.868018181818</v>
+      </c>
+      <c r="G31">
         <v>260.369609856262</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>4</v>
       </c>
@@ -5290,10 +5523,13 @@
         <v>238.25102727272699</v>
       </c>
       <c r="F32">
+        <v>306.86937272727198</v>
+      </c>
+      <c r="G32">
         <v>267.76180698151899</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>4</v>
       </c>
@@ -5309,8 +5545,11 @@
       <c r="E33">
         <v>239.13275454545399</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33">
+        <v>307.49489999999901</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>4</v>
       </c>
@@ -5326,8 +5565,11 @@
       <c r="E34">
         <v>240.568472727272</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34">
+        <v>316.62493636363598</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>4</v>
       </c>
@@ -5343,8 +5585,11 @@
       <c r="E35">
         <v>244.68430909090901</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35">
+        <v>316.76135454545403</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>4</v>
       </c>
@@ -5360,8 +5605,11 @@
       <c r="E36">
         <v>246.327981818181</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36">
+        <v>319.92891818181801</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>4</v>
       </c>
@@ -5377,8 +5625,11 @@
       <c r="E37">
         <v>246.39785454545401</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37">
+        <v>329.689472727272</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -5394,8 +5645,11 @@
       <c r="E38">
         <v>246.74222727272701</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38">
+        <v>332.25979090908999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>4</v>
       </c>
@@ -5411,8 +5665,11 @@
       <c r="E39">
         <v>247.31119090908999</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39">
+        <v>333.82693636363598</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>4</v>
       </c>
@@ -5428,8 +5685,11 @@
       <c r="E40">
         <v>247.73375454545399</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F40">
+        <v>336.35732727272699</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>4</v>
       </c>
@@ -5445,8 +5705,11 @@
       <c r="E41">
         <v>264.44165454545401</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F41">
+        <v>336.43219090909002</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>4</v>
       </c>
@@ -5462,8 +5725,11 @@
       <c r="E42">
         <v>279.32288181818097</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F42">
+        <v>361.300227272727</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>4</v>
       </c>
@@ -5479,8 +5745,11 @@
       <c r="E43">
         <v>281.20112727272698</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F43">
+        <v>366.61887272727199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>4</v>
       </c>
@@ -5496,8 +5765,11 @@
       <c r="E44">
         <v>293.66009999999898</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44">
+        <v>377.086472727272</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>4</v>
       </c>
@@ -5513,8 +5785,11 @@
       <c r="E45">
         <v>358.328972727272</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45">
+        <v>455.07774545454498</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>4</v>
       </c>
@@ -5530,8 +5805,11 @@
       <c r="E46">
         <v>382.636363636363</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46">
+        <v>545.29009090909005</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>4</v>
       </c>
@@ -5547,8 +5825,11 @@
       <c r="E47">
         <v>478.88105454545399</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47">
+        <v>624.32945454545404</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>4</v>
       </c>
@@ -5564,8 +5845,11 @@
       <c r="E48">
         <v>483.35290909090901</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F48">
+        <v>629.20224545454505</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
@@ -5581,8 +5865,11 @@
       <c r="E49">
         <v>503.70749999999902</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F49">
+        <v>661.11411818181796</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>4</v>
       </c>
@@ -5595,8 +5882,11 @@
       <c r="E50">
         <v>562.59689999999898</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F50">
+        <v>706.47316363636298</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>3</v>
       </c>
@@ -5613,13 +5903,16 @@
         <v>151.90048090908999</v>
       </c>
       <c r="F51">
+        <v>167.519863636363</v>
+      </c>
+      <c r="G51">
         <v>120</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <v>100</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>3</v>
       </c>
@@ -5636,10 +5929,13 @@
         <v>183.57229090908999</v>
       </c>
       <c r="F52">
+        <v>197.832981818181</v>
+      </c>
+      <c r="G52">
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>3</v>
       </c>
@@ -5656,10 +5952,13 @@
         <v>187.46187272727201</v>
       </c>
       <c r="F53">
+        <v>199.782763636363</v>
+      </c>
+      <c r="G53">
         <v>234</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>3</v>
       </c>
@@ -5676,10 +5975,13 @@
         <v>190.23681818181799</v>
       </c>
       <c r="F54">
+        <v>200.205327272727</v>
+      </c>
+      <c r="G54">
         <v>350</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>3</v>
       </c>
@@ -5695,8 +5997,11 @@
       <c r="E55">
         <v>191.830581818181</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F55">
+        <v>203.75386363636301</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>3</v>
       </c>
@@ -5712,8 +6017,11 @@
       <c r="E56">
         <v>194.454136363636</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F56">
+        <v>207.049527272727</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>3</v>
       </c>
@@ -5729,8 +6037,11 @@
       <c r="E57">
         <v>194.876699999999</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F57">
+        <v>208.21573636363601</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>3</v>
       </c>
@@ -5746,8 +6057,11 @@
       <c r="E58">
         <v>197.55848181818101</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F58">
+        <v>208.268972727272</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>3</v>
       </c>
@@ -5763,8 +6077,11 @@
       <c r="E59">
         <v>199.386818181818</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F59">
+        <v>210.91415454545401</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>3</v>
       </c>
@@ -5780,8 +6097,11 @@
       <c r="E60">
         <v>205.70031818181801</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F60">
+        <v>218.13433636363601</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>3</v>
       </c>
@@ -5797,8 +6117,11 @@
       <c r="E61">
         <v>205.96483636363601</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F61">
+        <v>219.12919090909</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>3</v>
       </c>
@@ -5814,8 +6137,11 @@
       <c r="E62">
         <v>206.81329090909</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F62">
+        <v>222.67273636363601</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>3</v>
       </c>
@@ -5831,8 +6157,11 @@
       <c r="E63">
         <v>212.23175454545401</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F63">
+        <v>223.60603636363601</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>3</v>
       </c>
@@ -5848,8 +6177,11 @@
       <c r="E64">
         <v>220.505018181818</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F64">
+        <v>224.05688181818101</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>3</v>
       </c>
@@ -5865,8 +6197,11 @@
       <c r="E65">
         <v>220.821109090909</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F65">
+        <v>232.36009090908999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>3</v>
       </c>
@@ -5882,8 +6217,11 @@
       <c r="E66">
         <v>222.649445454545</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F66">
+        <v>232.46989090909</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>3</v>
       </c>
@@ -5899,8 +6237,11 @@
       <c r="E67">
         <v>225.28131818181799</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F67">
+        <v>234.52448181818099</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>3</v>
       </c>
@@ -5916,8 +6257,11 @@
       <c r="E68">
         <v>227.84664545454501</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F68">
+        <v>236.928436363636</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>3</v>
       </c>
@@ -5933,8 +6277,11 @@
       <c r="E69">
         <v>230.97927272727199</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F69">
+        <v>241.37699999999899</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>3</v>
       </c>
@@ -5950,8 +6297,11 @@
       <c r="E70">
         <v>235.337999999999</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F70">
+        <v>246.62743636363601</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>3</v>
       </c>
@@ -5964,8 +6314,11 @@
       <c r="E71">
         <v>235.923599999999</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F71">
+        <v>247.118209090909</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>3</v>
       </c>
@@ -5978,8 +6331,11 @@
       <c r="E72">
         <v>238.384118181818</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F72">
+        <v>249.58039090909</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>3</v>
       </c>
@@ -5992,8 +6348,11 @@
       <c r="E73">
         <v>251.78969999999899</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F73">
+        <v>266.828972727272</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>3</v>
       </c>
@@ -6006,8 +6365,11 @@
       <c r="E74">
         <v>413.05096363636301</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F74">
+        <v>411.84649090908999</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1</v>
       </c>
@@ -6020,14 +6382,14 @@
       <c r="E75">
         <v>159.44557090909001</v>
       </c>
-      <c r="F75">
+      <c r="G75">
         <v>136.587771203155</v>
       </c>
-      <c r="G75">
+      <c r="H75">
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>1</v>
       </c>
@@ -6040,11 +6402,11 @@
       <c r="E76">
         <v>163.58735999999899</v>
       </c>
-      <c r="F76">
+      <c r="G76">
         <v>144.47731755423999</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>1</v>
       </c>
@@ -6057,11 +6419,11 @@
       <c r="E77">
         <v>179.27844545454499</v>
       </c>
-      <c r="F77">
+      <c r="G77">
         <v>151.380670611439</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>1</v>
       </c>
@@ -6074,11 +6436,11 @@
       <c r="E78">
         <v>185.571981818181</v>
       </c>
-      <c r="F78">
+      <c r="G78">
         <v>228.79684418145899</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1</v>
       </c>
@@ -6091,11 +6453,11 @@
       <c r="E79">
         <v>186.094363636363</v>
       </c>
-      <c r="F79">
+      <c r="G79">
         <v>246.05522682445701</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1</v>
       </c>
@@ -6108,11 +6470,11 @@
       <c r="E80">
         <v>226.30778181818101</v>
       </c>
-      <c r="F80">
+      <c r="G80">
         <v>248.02761341222799</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>1</v>
       </c>
@@ -6125,11 +6487,11 @@
       <c r="E81">
         <v>234.05034545454501</v>
       </c>
-      <c r="F81">
+      <c r="G81">
         <v>324.45759368836298</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1</v>
       </c>
@@ -6142,11 +6504,11 @@
       <c r="E82">
         <v>239.340709090909</v>
       </c>
-      <c r="F82">
+      <c r="G82">
         <v>328.402366863905</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>1</v>
       </c>
@@ -6159,11 +6521,11 @@
       <c r="E83">
         <v>239.891372727272</v>
       </c>
-      <c r="F83">
+      <c r="G83">
         <v>377.712031558185</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>1</v>
       </c>
@@ -6176,11 +6538,11 @@
       <c r="E84">
         <v>251.33386363636299</v>
       </c>
-      <c r="F84">
+      <c r="G84">
         <v>433.43195266272102</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>1</v>
       </c>
@@ -6194,7 +6556,7 @@
         <v>251.541818181818</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1</v>
       </c>
@@ -6208,7 +6570,7 @@
         <v>256.09019999999902</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>1</v>
       </c>
@@ -6222,7 +6584,7 @@
         <v>260.85152727272703</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>1</v>
       </c>
@@ -6236,7 +6598,7 @@
         <v>262.54677272727201</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1</v>
       </c>
@@ -6250,7 +6612,7 @@
         <v>265.86739090908998</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>1</v>
       </c>
@@ -6264,7 +6626,7 @@
         <v>270.33259090909002</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1</v>
       </c>
@@ -6278,7 +6640,7 @@
         <v>274.31367272727198</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1</v>
       </c>
@@ -6292,7 +6654,7 @@
         <v>281.46564545454498</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1</v>
       </c>
@@ -6306,7 +6668,7 @@
         <v>287.26009090909002</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1</v>
       </c>
@@ -6320,7 +6682,7 @@
         <v>287.79744545454503</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1</v>
       </c>
@@ -6334,7 +6696,7 @@
         <v>288.51613636363601</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>1</v>
       </c>
@@ -6572,7 +6934,7 @@
         <v>320.424681818181</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1</v>
       </c>
@@ -6586,7 +6948,7 @@
         <v>324.26435454545401</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1</v>
       </c>
@@ -6600,7 +6962,7 @@
         <v>329.02900909090903</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1</v>
       </c>
@@ -6614,7 +6976,7 @@
         <v>331.118536363636</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1</v>
       </c>
@@ -6628,7 +6990,7 @@
         <v>334.32103636363598</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1</v>
       </c>
@@ -6642,7 +7004,7 @@
         <v>336.51703636363601</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1</v>
       </c>
@@ -6656,7 +7018,7 @@
         <v>338.24555454545401</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1</v>
       </c>
@@ -6670,7 +7032,7 @@
         <v>338.69473636363603</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1</v>
       </c>
@@ -6684,7 +7046,7 @@
         <v>341.64769090908999</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1</v>
       </c>
@@ -6698,7 +7060,7 @@
         <v>342.58265454545398</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1</v>
       </c>
@@ -6712,7 +7074,7 @@
         <v>358.90958181818098</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1</v>
       </c>
@@ -6726,9 +7088,9 @@
         <v>382.84764545454499</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B124">
         <v>218.91624545454499</v>
@@ -6743,15 +7105,18 @@
         <v>240.33889090909</v>
       </c>
       <c r="F124">
+        <v>218.748218181818</v>
+      </c>
+      <c r="G124">
         <v>130</v>
       </c>
-      <c r="G124">
+      <c r="H124">
         <v>100</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B125">
         <v>232.50649090908999</v>
@@ -6766,12 +7131,15 @@
         <v>255.99869999999899</v>
       </c>
       <c r="F125">
+        <v>236.87519999999901</v>
+      </c>
+      <c r="G125">
         <v>320</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B126">
         <v>232.50649090908999</v>
@@ -6785,10 +7153,13 @@
       <c r="E126">
         <v>255.99869999999899</v>
       </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F126">
+        <v>236.87519999999901</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B127">
         <v>232.50649090908999</v>
@@ -6802,10 +7173,13 @@
       <c r="E127">
         <v>255.99869999999899</v>
       </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F127">
+        <v>236.87519999999901</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B128">
         <v>232.50649090908999</v>
@@ -6819,10 +7193,13 @@
       <c r="E128">
         <v>255.99869999999899</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F128">
+        <v>236.87519999999901</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B129">
         <v>235.14834545454499</v>
@@ -6836,10 +7213,13 @@
       <c r="E129">
         <v>258.44590909090903</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F129">
+        <v>237.36430909090899</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B130">
         <v>235.14834545454499</v>
@@ -6853,10 +7233,13 @@
       <c r="E130">
         <v>258.44590909090903</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F130">
+        <v>240.62004545454499</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B131">
         <v>236.58572727272701</v>
@@ -6870,10 +7253,13 @@
       <c r="E131">
         <v>263.21056363636302</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F131">
+        <v>240.62004545454499</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B132">
         <v>241.08087272727201</v>
@@ -6887,10 +7273,13 @@
       <c r="E132">
         <v>263.21056363636302</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F132">
+        <v>248.74690909090901</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B133">
         <v>241.08087272727201</v>
@@ -6904,10 +7293,13 @@
       <c r="E133">
         <v>263.21056363636302</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F133">
+        <v>248.74690909090901</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B134">
         <v>241.08087272727201</v>
@@ -6921,10 +7313,13 @@
       <c r="E134">
         <v>263.21056363636302</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F134">
+        <v>248.74690909090901</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B135">
         <v>241.08087272727201</v>
@@ -6938,10 +7333,13 @@
       <c r="E135">
         <v>263.93590909090898</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F135">
+        <v>248.74690909090901</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B136">
         <v>241.67312727272699</v>
@@ -6955,10 +7353,13 @@
       <c r="E136">
         <v>263.93590909090898</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F136">
+        <v>248.74690909090901</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B137">
         <v>241.67312727272699</v>
@@ -6972,10 +7373,13 @@
       <c r="E137">
         <v>268.85195454545402</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F137">
+        <v>249.30589090909001</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B138">
         <v>241.78126363636301</v>
@@ -6989,10 +7393,13 @@
       <c r="E138">
         <v>270.56383636363603</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F138">
+        <v>249.30589090909001</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B139">
         <v>241.78126363636301</v>
@@ -7006,10 +7413,13 @@
       <c r="E139">
         <v>270.56383636363603</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F139">
+        <v>250.022918181818</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B140">
         <v>241.78126363636301</v>
@@ -7023,10 +7433,13 @@
       <c r="E140">
         <v>270.56383636363603</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F140">
+        <v>250.022918181818</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B141">
         <v>241.78126363636301</v>
@@ -7040,10 +7453,13 @@
       <c r="E141">
         <v>270.56383636363603</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F141">
+        <v>250.022918181818</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B142">
         <v>241.78126363636301</v>
@@ -7057,10 +7473,13 @@
       <c r="E142">
         <v>270.56383636363603</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F142">
+        <v>250.022918181818</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B143">
         <v>242.78609999999901</v>
@@ -7074,10 +7493,13 @@
       <c r="E143">
         <v>273.31549090908999</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F143">
+        <v>250.022918181818</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B144">
         <v>242.78609999999901</v>
@@ -7091,10 +7513,13 @@
       <c r="E144">
         <v>273.31549090908999</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F144">
+        <v>250.022918181818</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B145">
         <v>242.78609999999901</v>
@@ -7108,10 +7533,13 @@
       <c r="E145">
         <v>273.31549090908999</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F145">
+        <v>250.022918181818</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B146">
         <v>242.78609999999901</v>
@@ -7125,10 +7553,13 @@
       <c r="E146">
         <v>273.31549090908999</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F146">
+        <v>250.66508181818099</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B147">
         <v>242.78609999999901</v>
@@ -7142,10 +7573,13 @@
       <c r="E147">
         <v>273.31549090908999</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F147">
+        <v>250.66508181818099</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B148">
         <v>244.09870909090901</v>
@@ -7159,10 +7593,13 @@
       <c r="E148">
         <v>276.63777272727202</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F148">
+        <v>250.66508181818099</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B149">
         <v>244.09870909090901</v>
@@ -7176,10 +7613,13 @@
       <c r="E149">
         <v>276.63777272727202</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F149">
+        <v>250.66508181818099</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B150">
         <v>244.71259090909001</v>
@@ -7193,10 +7633,13 @@
       <c r="E150">
         <v>277.36977272727199</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F150">
+        <v>250.96120909090899</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B151">
         <v>244.71259090909001</v>
@@ -7210,10 +7653,13 @@
       <c r="E151">
         <v>277.36977272727199</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F151">
+        <v>250.96120909090899</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B152">
         <v>244.71259090909001</v>
@@ -7227,10 +7673,13 @@
       <c r="E152">
         <v>277.36977272727199</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F152">
+        <v>250.96120909090899</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B153">
         <v>244.71259090909001</v>
@@ -7244,10 +7693,13 @@
       <c r="E153">
         <v>277.36977272727199</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F153">
+        <v>250.96120909090899</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B154">
         <v>244.71259090909001</v>
@@ -7261,10 +7713,13 @@
       <c r="E154">
         <v>277.36977272727199</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F154">
+        <v>250.96120909090899</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B155">
         <v>244.71259090909001</v>
@@ -7278,10 +7733,13 @@
       <c r="E155">
         <v>277.36977272727199</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F155">
+        <v>251.380445454545</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B156">
         <v>244.71259090909001</v>
@@ -7295,10 +7753,13 @@
       <c r="E156">
         <v>277.36977272727199</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F156">
+        <v>251.380445454545</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B157">
         <v>247.33448181818099</v>
@@ -7312,10 +7773,13 @@
       <c r="E157">
         <v>284.490136363636</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F157">
+        <v>263.77952727272702</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B158">
         <v>249.354136363636</v>
@@ -7329,10 +7793,13 @@
       <c r="E158">
         <v>284.490136363636</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F158">
+        <v>263.77952727272702</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B159">
         <v>249.354136363636</v>
@@ -7346,10 +7813,13 @@
       <c r="E159">
         <v>284.490136363636</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F159">
+        <v>263.77952727272702</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B160">
         <v>249.354136363636</v>
@@ -7363,10 +7833,13 @@
       <c r="E160">
         <v>290.31951818181801</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F160">
+        <v>266.45299090908998</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B161">
         <v>253.57311818181799</v>
@@ -7380,10 +7853,13 @@
       <c r="E161">
         <v>293.76823636363599</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F161">
+        <v>267.15171818181801</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B162">
         <v>254.142081818181</v>
@@ -7397,10 +7873,13 @@
       <c r="E162">
         <v>294.48193636363601</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F162">
+        <v>267.15171818181801</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B163">
         <v>254.142081818181</v>
@@ -7414,10 +7893,13 @@
       <c r="E163">
         <v>294.48193636363601</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F163">
+        <v>267.15171818181801</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B164">
         <v>262.66988181818101</v>
@@ -7431,10 +7913,13 @@
       <c r="E164">
         <v>294.48193636363601</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F164">
+        <v>273.22731818181802</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="B165">
         <v>287.927209090909</v>
@@ -7448,10 +7933,13 @@
       <c r="E165">
         <v>304.35229090909002</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F165">
+        <v>286.187045454545</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C166">
         <v>335.04139090909001</v>
@@ -7462,10 +7950,13 @@
       <c r="E166">
         <v>360.16396363636301</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F166">
+        <v>335.22439090909</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C167">
         <v>335.04139090909001</v>
@@ -7476,10 +7967,13 @@
       <c r="E167">
         <v>362.28676363636299</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F167">
+        <v>337.28896363636301</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C168">
         <v>473.795318181818</v>
@@ -7490,10 +7984,13 @@
       <c r="E168">
         <v>362.28676363636299</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F168">
+        <v>337.28896363636301</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D169">
         <v>365.600727272727</v>
@@ -7501,10 +7998,13 @@
       <c r="E169">
         <v>362.28676363636299</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F169">
+        <v>337.28896363636301</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D170">
         <v>365.600727272727</v>
@@ -7512,10 +8012,13 @@
       <c r="E170">
         <v>362.28676363636299</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F170">
+        <v>337.28896363636301</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D171">
         <v>365.600727272727</v>
@@ -7523,16 +8026,22 @@
       <c r="E171">
         <v>362.28676363636299</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F171">
+        <v>337.28896363636301</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D172">
         <v>510.668154545454</v>
       </c>
       <c r="E172">
         <v>506.40092727272702</v>
+      </c>
+      <c r="F172">
+        <v>477.262336363636</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_analysis/market_shares.xlsx
+++ b/data/data_analysis/market_shares.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62AE3D2E-5CE6-4504-B788-2F2D35451982}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF78505C-FDCF-494F-B09D-8BB839F68B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supply" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="27">
   <si>
     <t>Scenario</t>
   </si>
@@ -122,6 +122,21 @@
   <si>
     <t>Literature</t>
   </si>
+  <si>
+    <t>100 Mt Baseline</t>
+  </si>
+  <si>
+    <t>500 Mt Baseline</t>
+  </si>
+  <si>
+    <t>1500 Mt Baseline</t>
+  </si>
+  <si>
+    <t>2400 Mt Baseline</t>
+  </si>
+  <si>
+    <t>4100 Mt Baseline</t>
+  </si>
 </sst>
 </file>
 
@@ -173,6 +188,20 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF001536"/>
+      <color rgb="FF486800"/>
+      <color rgb="FF93D500"/>
+      <color rgb="FF2063AC"/>
+      <color rgb="FF8AB7E9"/>
+      <color rgb="FF004639"/>
+      <color rgb="FF00AE8D"/>
+      <color rgb="FF5F1546"/>
+      <color rgb="FFC22A90"/>
+      <color rgb="FF005B70"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -245,22 +274,22 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Nothing Baseline</c:v>
+                  <c:v>100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Low Baseline</c:v>
+                  <c:v>500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>R2R Report</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>High Baseline</c:v>
+                  <c:v>1500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Excess Baseline</c:v>
+                  <c:v>2400 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4Gt Baseline</c:v>
+                  <c:v>4100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
@@ -334,22 +363,22 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Nothing Baseline</c:v>
+                  <c:v>100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Low Baseline</c:v>
+                  <c:v>500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>R2R Report</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>High Baseline</c:v>
+                  <c:v>1500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Excess Baseline</c:v>
+                  <c:v>2400 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4Gt Baseline</c:v>
+                  <c:v>4100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
@@ -423,22 +452,22 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Nothing Baseline</c:v>
+                  <c:v>100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Low Baseline</c:v>
+                  <c:v>500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>R2R Report</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>High Baseline</c:v>
+                  <c:v>1500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Excess Baseline</c:v>
+                  <c:v>2400 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4Gt Baseline</c:v>
+                  <c:v>4100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
@@ -512,22 +541,22 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Nothing Baseline</c:v>
+                  <c:v>100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Low Baseline</c:v>
+                  <c:v>500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>R2R Report</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>High Baseline</c:v>
+                  <c:v>1500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Excess Baseline</c:v>
+                  <c:v>2400 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4Gt Baseline</c:v>
+                  <c:v>4100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
@@ -622,22 +651,22 @@
               <c:strCache>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>Nothing Baseline</c:v>
+                  <c:v>100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Low Baseline</c:v>
+                  <c:v>500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>R2R Report</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>High Baseline</c:v>
+                  <c:v>1500 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Excess Baseline</c:v>
+                  <c:v>2400 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4Gt Baseline</c:v>
+                  <c:v>4100 Mt Baseline</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Policy Integrity</c:v>
@@ -1912,9 +1941,19 @@
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.1</cx:f>
-              <cx:v>Nothing Baseline</cx:v>
+              <cx:v>100 Mt Baseline</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="0047BB"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="001536"/>
+              </a:solidFill>
+            </a:ln>
+          </cx:spPr>
           <cx:dataId val="0"/>
           <cx:layoutPr>
             <cx:statistics quartileMethod="exclusive"/>
@@ -1924,9 +1963,19 @@
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.3</cx:f>
-              <cx:v>Low Baseline</cx:v>
+              <cx:v>500 Mt Baseline</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00B5E2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="005B70"/>
+              </a:solidFill>
+            </a:ln>
+          </cx:spPr>
           <cx:dataId val="1"/>
           <cx:layoutPr>
             <cx:statistics quartileMethod="exclusive"/>
@@ -1936,9 +1985,19 @@
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.5</cx:f>
-              <cx:v>High Baseline</cx:v>
+              <cx:v>1500 Mt Baseline</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="C22A90"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="5F1546"/>
+              </a:solidFill>
+            </a:ln>
+          </cx:spPr>
           <cx:dataId val="2"/>
           <cx:layoutPr>
             <cx:statistics quartileMethod="exclusive"/>
@@ -1948,9 +2007,19 @@
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.7</cx:f>
-              <cx:v>Excess Baseline</cx:v>
+              <cx:v>2400 Mt Baseline</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="00AE8D"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="004639"/>
+              </a:solidFill>
+            </a:ln>
+          </cx:spPr>
           <cx:dataId val="3"/>
           <cx:layoutPr>
             <cx:statistics quartileMethod="exclusive"/>
@@ -1960,9 +2029,19 @@
           <cx:tx>
             <cx:txData>
               <cx:f>_xlchart.v1.9</cx:f>
-              <cx:v>4Gt Baseline</cx:v>
+              <cx:v>4100 Mt Baseline</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="8AB7E9"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2063AC"/>
+              </a:solidFill>
+            </a:ln>
+          </cx:spPr>
           <cx:dataId val="4"/>
           <cx:layoutPr>
             <cx:statistics quartileMethod="exclusive"/>
@@ -1975,6 +2054,16 @@
               <cx:v>Literature</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="93D500"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="486800"/>
+              </a:solidFill>
+            </a:ln>
+          </cx:spPr>
           <cx:dataId val="5"/>
           <cx:layoutPr>
             <cx:statistics quartileMethod="exclusive"/>
@@ -1987,6 +2076,16 @@
               <cx:v>Carbon Negative Shot</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:srgbClr val="001536"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="001536"/>
+              </a:solidFill>
+            </a:ln>
+          </cx:spPr>
           <cx:dataId val="6"/>
           <cx:layoutPr>
             <cx:statistics quartileMethod="exclusive"/>
@@ -2033,7 +2132,7 @@
         </cx:txPr>
       </cx:axis>
       <cx:axis id="1">
-        <cx:valScaling min="50"/>
+        <cx:valScaling max="750" min="50"/>
         <cx:title>
           <cx:tx>
             <cx:rich>
@@ -3944,7 +4043,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="4524374" y="2262186"/>
+              <a:off x="5133974" y="2262186"/>
               <a:ext cx="9667875" cy="4329113"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -4319,7 +4418,7 @@
         <v>8100</v>
       </c>
       <c r="K3" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="L3">
         <v>100</v>
@@ -4363,7 +4462,7 @@
         <v>33.333333333333336</v>
       </c>
       <c r="K4" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="L4">
         <v>500</v>
@@ -4451,7 +4550,7 @@
         <v>18.518518518518519</v>
       </c>
       <c r="K6" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L6">
         <v>1500</v>
@@ -4495,7 +4594,7 @@
         <v>19.753086419753089</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L7">
         <v>2400</v>
@@ -4515,7 +4614,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="K8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L8">
         <v>4100</v>
@@ -4785,19 +4884,19 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G2" t="s">
         <v>21</v>

--- a/data/data_analysis/market_shares.xlsx
+++ b/data/data_analysis/market_shares.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\natha\PycharmProjects\GCAM-CDR-policy\data\data_analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF78505C-FDCF-494F-B09D-8BB839F68B6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DFF3858-8371-4F22-82BA-E7F651E91D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Supply" sheetId="1" r:id="rId1"/>
@@ -304,19 +304,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>44.927060409523001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>41.392780804976702</c:v>
+                  <c:v>44.0143448942841</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>71</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.252870109609599</c:v>
+                  <c:v>24.73326775</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>13.971358556094</c:v>
+                  <c:v>16.290950412660901</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -393,22 +393,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>16.05792107972</c:v>
+                  <c:v>8.9943445050531103</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>10.001446111260799</c:v>
+                  <c:v>9.5071269083703598</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>15.3136863885011</c:v>
+                  <c:v>14.72902215</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20.2156017331953</c:v>
+                  <c:v>18.8364130216703</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>36.896675146341458</c:v>
+                  <c:v>36.2467777669142</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>28.39506172839506</c:v>
@@ -482,22 +482,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>18.7566878367989</c:v>
+                  <c:v>10.282869248906</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.017061152797201</c:v>
+                  <c:v>12.4646736325696</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>23.006893045764301</c:v>
+                  <c:v>23.015151240000002</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>28.493621918617499</c:v>
+                  <c:v>28.756493502038602</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>30.957383796747809</c:v>
+                  <c:v>31.870292268598401</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>18.518518518518519</c:v>
@@ -571,22 +571,22 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>65.185391083480994</c:v>
+                  <c:v>35.795725836517803</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>35.588711930965097</c:v>
+                  <c:v>34.013854564775798</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>38.426550456124801</c:v>
+                  <c:v>37.522558859999997</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>37.319417792093098</c:v>
+                  <c:v>36.116143063630098</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>32.145905482926835</c:v>
+                  <c:v>31.8829299644872</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>19.753086419753089</c:v>
@@ -2108,7 +2108,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1200">
+              <a:defRPr sz="1400">
                 <a:solidFill>
                   <a:schemeClr val="bg2">
                     <a:lumMod val="25000"/>
@@ -2119,7 +2119,7 @@
                 <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:endParaRPr lang="en-US" sz="1400" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="25000"/>
@@ -2201,7 +2201,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr" rtl="0">
-              <a:defRPr sz="1050">
+              <a:defRPr sz="1200">
                 <a:solidFill>
                   <a:schemeClr val="bg2">
                     <a:lumMod val="25000"/>
@@ -2212,7 +2212,7 @@
                 <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US" sz="1050" b="0" i="0" u="none" strike="noStrike" baseline="0">
+            <a:endParaRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="25000"/>
@@ -2231,7 +2231,7 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr" rtl="0">
-            <a:defRPr sz="1100">
+            <a:defRPr sz="1200">
               <a:solidFill>
                 <a:schemeClr val="bg2">
                   <a:lumMod val="25000"/>
@@ -2242,7 +2242,7 @@
               <a:cs typeface="Arial" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+          <a:endParaRPr lang="en-US" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0">
             <a:solidFill>
               <a:schemeClr val="bg2">
                 <a:lumMod val="25000"/>
@@ -4353,7 +4353,7 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -4424,16 +4424,20 @@
         <v>100</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <f>C4</f>
+        <v>44.927060409523001</v>
       </c>
       <c r="N3">
-        <v>16.05792107972</v>
+        <f>C5</f>
+        <v>8.9943445050531103</v>
       </c>
       <c r="O3">
-        <v>18.7566878367989</v>
+        <f>C6</f>
+        <v>10.282869248906</v>
       </c>
       <c r="P3">
-        <v>65.185391083480994</v>
+        <f>C7</f>
+        <v>35.795725836517803</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
@@ -4441,19 +4445,19 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>44.927060409523001</v>
       </c>
       <c r="D4">
-        <v>41.392780804976702</v>
+        <v>44.0143448942841</v>
       </c>
       <c r="E4">
         <v>71</v>
       </c>
       <c r="F4">
-        <v>23.252870109609599</v>
+        <v>24.73326775</v>
       </c>
       <c r="G4">
-        <v>13.971358556094</v>
+        <v>16.290950412660901</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -4468,16 +4472,20 @@
         <v>500</v>
       </c>
       <c r="M4">
-        <v>41.392780804976702</v>
+        <f>D4</f>
+        <v>44.0143448942841</v>
       </c>
       <c r="N4">
-        <v>10.001446111260799</v>
+        <f>D5</f>
+        <v>9.5071269083703598</v>
       </c>
       <c r="O4">
-        <v>13.017061152797201</v>
+        <f>D6</f>
+        <v>12.4646736325696</v>
       </c>
       <c r="P4">
-        <v>35.588711930965097</v>
+        <f>D7</f>
+        <v>34.013854564775798</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -4485,22 +4493,22 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>16.05792107972</v>
+        <v>8.9943445050531103</v>
       </c>
       <c r="D5">
-        <v>10.001446111260799</v>
+        <v>9.5071269083703598</v>
       </c>
       <c r="E5">
         <v>29</v>
       </c>
       <c r="F5">
-        <v>15.3136863885011</v>
+        <v>14.72902215</v>
       </c>
       <c r="G5">
-        <v>20.2156017331953</v>
+        <v>18.8364130216703</v>
       </c>
       <c r="H5">
-        <v>1512.7636809999999</v>
+        <v>36.2467777669142</v>
       </c>
       <c r="I5">
         <v>28.39506172839506</v>
@@ -4529,22 +4537,22 @@
         <v>3</v>
       </c>
       <c r="C6">
-        <v>18.7566878367989</v>
+        <v>10.282869248906</v>
       </c>
       <c r="D6">
-        <v>13.017061152797201</v>
+        <v>12.4646736325696</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>23.006893045764301</v>
+        <v>23.015151240000002</v>
       </c>
       <c r="G6">
-        <v>28.493621918617499</v>
+        <v>28.756493502038602</v>
       </c>
       <c r="H6">
-        <v>1269.2527356666601</v>
+        <v>31.870292268598401</v>
       </c>
       <c r="I6">
         <v>18.518518518518519</v>
@@ -4556,16 +4564,20 @@
         <v>1500</v>
       </c>
       <c r="M6">
-        <v>23.252870109609599</v>
+        <f>F4</f>
+        <v>24.73326775</v>
       </c>
       <c r="N6">
-        <v>15.3136863885011</v>
+        <f>F5</f>
+        <v>14.72902215</v>
       </c>
       <c r="O6">
-        <v>23.006893045764301</v>
+        <f>F6</f>
+        <v>23.015151240000002</v>
       </c>
       <c r="P6">
-        <v>38.426550456124801</v>
+        <f>F7</f>
+        <v>37.522558859999997</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -4573,22 +4585,22 @@
         <v>4</v>
       </c>
       <c r="C7">
-        <v>65.185391083480994</v>
+        <v>35.795725836517803</v>
       </c>
       <c r="D7">
-        <v>35.588711930965097</v>
+        <v>34.013854564775798</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>38.426550456124801</v>
+        <v>37.522558859999997</v>
       </c>
       <c r="G7">
-        <v>37.319417792093098</v>
+        <v>36.116143063630098</v>
       </c>
       <c r="H7">
-        <v>1317.9821248000001</v>
+        <v>31.8829299644872</v>
       </c>
       <c r="I7">
         <v>19.753086419753089</v>
@@ -4600,16 +4612,20 @@
         <v>2400</v>
       </c>
       <c r="M7">
-        <v>13.971358556094</v>
+        <f>G4</f>
+        <v>16.290950412660901</v>
       </c>
       <c r="N7">
-        <v>20.2156017331953</v>
+        <f>G5</f>
+        <v>18.8364130216703</v>
       </c>
       <c r="O7">
-        <v>28.493621918617499</v>
+        <f>G6</f>
+        <v>28.756493502038602</v>
       </c>
       <c r="P7">
-        <v>37.319417792093098</v>
+        <f>G7</f>
+        <v>36.116143063630098</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -4620,20 +4636,20 @@
         <v>4100</v>
       </c>
       <c r="M8">
-        <f>H4/H3</f>
+        <f>H4</f>
         <v>0</v>
       </c>
       <c r="N8">
-        <f>100*H5/H3</f>
-        <v>36.896675146341458</v>
+        <f>H5</f>
+        <v>36.2467777669142</v>
       </c>
       <c r="O8">
-        <f>100*H6/H3</f>
-        <v>30.957383796747809</v>
+        <f>H6</f>
+        <v>31.870292268598401</v>
       </c>
       <c r="P8">
-        <f>100*H7/H3</f>
-        <v>32.145905482926835</v>
+        <f>H7</f>
+        <v>31.8829299644872</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -4910,19 +4926,19 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>124.70119090909</v>
+        <v>113.876241818181</v>
       </c>
       <c r="C3">
-        <v>132.41414181818101</v>
+        <v>125.932281818181</v>
       </c>
       <c r="D3">
-        <v>148.67402454545399</v>
+        <v>141.89986363636299</v>
       </c>
       <c r="E3">
-        <v>161.581846363636</v>
+        <v>154.01313272727199</v>
       </c>
       <c r="F3">
-        <v>175.578518181818</v>
+        <v>175.08608181818099</v>
       </c>
       <c r="G3">
         <v>62.422997946611801</v>
@@ -4936,19 +4952,19 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>126.090327272727</v>
+        <v>119.64955909090899</v>
       </c>
       <c r="C4">
-        <v>136.141186363636</v>
+        <v>129.26021999999901</v>
       </c>
       <c r="D4">
-        <v>161.02436181818101</v>
+        <v>154.04141454545399</v>
       </c>
       <c r="E4">
-        <v>166.20625636363599</v>
+        <v>158.97459545454501</v>
       </c>
       <c r="F4">
-        <v>182.402754545454</v>
+        <v>181.61751818181801</v>
       </c>
       <c r="G4">
         <v>73.100616016426997</v>
@@ -4959,19 +4975,19 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>126.404089090909</v>
+        <v>121.70780999999999</v>
       </c>
       <c r="C5">
-        <v>136.83475636363599</v>
+        <v>129.66548181818101</v>
       </c>
       <c r="D5">
-        <v>161.230486363636</v>
+        <v>154.203951818181</v>
       </c>
       <c r="E5">
-        <v>172.836845454545</v>
+        <v>165.22271454545401</v>
       </c>
       <c r="F5">
-        <v>190.28672727272701</v>
+        <v>189.436609090909</v>
       </c>
       <c r="G5">
         <v>79.671457905544102</v>
@@ -4988,19 +5004,19 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>128.111645454545</v>
+        <v>122.59286454545401</v>
       </c>
       <c r="C6">
-        <v>138.29093727272701</v>
+        <v>131.37403636363601</v>
       </c>
       <c r="D6">
-        <v>163.268607272727</v>
+        <v>155.865591818181</v>
       </c>
       <c r="E6">
-        <v>180.81398181818099</v>
+        <v>172.63720909090901</v>
       </c>
       <c r="F6">
-        <v>198.528381818181</v>
+        <v>198.14740909090901</v>
       </c>
       <c r="G6">
         <v>91.991786447638603</v>
@@ -5017,19 +5033,19 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>129.34523181818099</v>
+        <v>122.727452727272</v>
       </c>
       <c r="C7">
-        <v>140.36216454545399</v>
+        <v>133.53826090909001</v>
       </c>
       <c r="D7">
-        <v>163.35944181818101</v>
+        <v>155.94611181818101</v>
       </c>
       <c r="E7">
-        <v>181.544318181818</v>
+        <v>173.13463636363599</v>
       </c>
       <c r="F7">
-        <v>208.46528181818101</v>
+        <v>206.781681818181</v>
       </c>
       <c r="G7">
         <v>99.383983572895204</v>
@@ -5046,19 +5062,19 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <v>131.15809636363599</v>
+        <v>122.946054545454</v>
       </c>
       <c r="C8">
-        <v>146.28787090909</v>
+        <v>138.51569454545401</v>
       </c>
       <c r="D8">
-        <v>163.74939818181801</v>
+        <v>156.45618272727199</v>
       </c>
       <c r="E8">
-        <v>183.011645454545</v>
+        <v>174.58033636363601</v>
       </c>
       <c r="F8">
-        <v>212.17519090908999</v>
+        <v>211.556318181818</v>
       </c>
       <c r="G8">
         <v>102.669404517453</v>
@@ -5075,19 +5091,19 @@
         <v>4</v>
       </c>
       <c r="B9">
-        <v>132.72790363636301</v>
+        <v>127.029949090909</v>
       </c>
       <c r="C9">
-        <v>147.04715454545399</v>
+        <v>139.61735454545399</v>
       </c>
       <c r="D9">
-        <v>174.78163636363601</v>
+        <v>165.91428818181799</v>
       </c>
       <c r="E9">
-        <v>192.22486363636301</v>
+        <v>183.52404545454499</v>
       </c>
       <c r="F9">
-        <v>212.755799999999</v>
+        <v>212.17186363636301</v>
       </c>
       <c r="G9">
         <v>104.312114989733</v>
@@ -5104,19 +5120,19 @@
         <v>4</v>
       </c>
       <c r="B10">
-        <v>136.50552272727199</v>
+        <v>127.06488545454501</v>
       </c>
       <c r="C10">
-        <v>150.92159727272701</v>
+        <v>143.62255909090899</v>
       </c>
       <c r="D10">
-        <v>175.16427272727199</v>
+        <v>167.055709090909</v>
       </c>
       <c r="E10">
-        <v>195.42237272727201</v>
+        <v>185.50210909090899</v>
       </c>
       <c r="F10">
-        <v>216.72523636363599</v>
+        <v>216.07309090909001</v>
       </c>
       <c r="G10">
         <v>105.133470225872</v>
@@ -5127,19 +5143,19 @@
         <v>4</v>
       </c>
       <c r="B11">
-        <v>137.10775909090901</v>
+        <v>129.644686363636</v>
       </c>
       <c r="C11">
-        <v>153.29560636363601</v>
+        <v>145.66533818181799</v>
       </c>
       <c r="D11">
-        <v>175.20752727272699</v>
+        <v>167.48991818181801</v>
       </c>
       <c r="E11">
-        <v>195.700199999999</v>
+        <v>186.224127272727</v>
       </c>
       <c r="F11">
-        <v>219.72310909090899</v>
+        <v>218.753209090909</v>
       </c>
       <c r="G11">
         <v>106.77618069815099</v>
@@ -5150,19 +5166,19 @@
         <v>4</v>
       </c>
       <c r="B12">
-        <v>137.93674909090899</v>
+        <v>130.21947272727201</v>
       </c>
       <c r="C12">
-        <v>153.34900909090899</v>
+        <v>146.30617090909001</v>
       </c>
       <c r="D12">
-        <v>177.69632727272699</v>
+        <v>169.216772727272</v>
       </c>
       <c r="E12">
-        <v>195.70851818181799</v>
+        <v>188.14562727272701</v>
       </c>
       <c r="F12">
-        <v>219.86618181818099</v>
+        <v>218.83306363636299</v>
       </c>
       <c r="G12">
         <v>109.24024640656999</v>
@@ -5173,19 +5189,19 @@
         <v>4</v>
       </c>
       <c r="B13">
-        <v>138.56826545454501</v>
+        <v>132.98792999999901</v>
       </c>
       <c r="C13">
-        <v>154.645148181818</v>
+        <v>147.18340636363601</v>
       </c>
       <c r="D13">
-        <v>180.614345454545</v>
+        <v>172.044954545454</v>
       </c>
       <c r="E13">
-        <v>199.46833636363601</v>
+        <v>190.14032727272701</v>
       </c>
       <c r="F13">
-        <v>220.616481818181</v>
+        <v>219.017727272727</v>
       </c>
       <c r="G13">
         <v>111.70431211498899</v>
@@ -5196,19 +5212,19 @@
         <v>4</v>
       </c>
       <c r="B14">
-        <v>141.11179909090899</v>
+        <v>135.872841818181</v>
       </c>
       <c r="C14">
-        <v>154.66111909090901</v>
+        <v>147.23264999999901</v>
       </c>
       <c r="D14">
-        <v>183.387627272727</v>
+        <v>175.03450909090901</v>
       </c>
       <c r="E14">
-        <v>199.81603636363599</v>
+        <v>190.80411818181801</v>
       </c>
       <c r="F14">
-        <v>222.448145454545</v>
+        <v>221.454954545454</v>
       </c>
       <c r="G14">
         <v>120.739219712525</v>
@@ -5219,19 +5235,19 @@
         <v>4</v>
       </c>
       <c r="B15">
-        <v>142.93747363636299</v>
+        <v>138.953064545454</v>
       </c>
       <c r="C15">
-        <v>154.96672909090901</v>
+        <v>147.628928181818</v>
       </c>
       <c r="D15">
-        <v>185.646845454545</v>
+        <v>177.63477272727201</v>
       </c>
       <c r="E15">
-        <v>200.09719090908999</v>
+        <v>191.58769090909001</v>
       </c>
       <c r="F15">
-        <v>223.95706363636299</v>
+        <v>222.132054545454</v>
       </c>
       <c r="G15">
         <v>124.02464065708401</v>
@@ -5242,19 +5258,19 @@
         <v>4</v>
       </c>
       <c r="B16">
-        <v>143.724373636363</v>
+        <v>140.26500818181799</v>
       </c>
       <c r="C16">
-        <v>155.41042090908999</v>
+        <v>147.956664545454</v>
       </c>
       <c r="D16">
-        <v>185.65349999999901</v>
+        <v>178.004099999999</v>
       </c>
       <c r="E16">
-        <v>200.36170909090899</v>
+        <v>191.609318181818</v>
       </c>
       <c r="F16">
-        <v>225.284645454545</v>
+        <v>224.69571818181799</v>
       </c>
       <c r="G16">
         <v>126.48870636550301</v>
@@ -5265,19 +5281,19 @@
         <v>4</v>
       </c>
       <c r="B17">
-        <v>147.66452999999899</v>
+        <v>141.757955454545</v>
       </c>
       <c r="C17">
-        <v>155.75629090909001</v>
+        <v>148.53577636363599</v>
       </c>
       <c r="D17">
-        <v>192.42949090908999</v>
+        <v>183.81019090909001</v>
       </c>
       <c r="E17">
-        <v>204.158127272727</v>
+        <v>195.287618181818</v>
       </c>
       <c r="F17">
-        <v>225.92348181818099</v>
+        <v>224.90200909090899</v>
       </c>
       <c r="G17">
         <v>131.41683778234</v>
@@ -5288,19 +5304,19 @@
         <v>4</v>
       </c>
       <c r="B18">
-        <v>148.29038999999901</v>
+        <v>142.14009272727199</v>
       </c>
       <c r="C18">
-        <v>156.55866272727201</v>
+        <v>148.75820454545399</v>
       </c>
       <c r="D18">
-        <v>192.73559999999901</v>
+        <v>184.33922727272699</v>
       </c>
       <c r="E18">
-        <v>204.68716363636301</v>
+        <v>195.478936363636</v>
       </c>
       <c r="F18">
-        <v>228.34074545454499</v>
+        <v>226.48246363636301</v>
       </c>
       <c r="G18">
         <v>132.23819301847999</v>
@@ -5311,19 +5327,19 @@
         <v>4</v>
       </c>
       <c r="B19">
-        <v>148.65971727272699</v>
+        <v>144.724551818181</v>
       </c>
       <c r="C19">
-        <v>159.02117727272699</v>
+        <v>151.36246090909</v>
       </c>
       <c r="D19">
-        <v>193.437654545454</v>
+        <v>185.35570909090899</v>
       </c>
       <c r="E19">
-        <v>205.74689999999899</v>
+        <v>196.08117272727199</v>
       </c>
       <c r="F19">
-        <v>229.94449090909001</v>
+        <v>228.05959090908999</v>
       </c>
       <c r="G19">
         <v>132.23819301847999</v>
@@ -5334,19 +5350,19 @@
         <v>4</v>
       </c>
       <c r="B20">
-        <v>149.08976727272699</v>
+        <v>144.97626</v>
       </c>
       <c r="C20">
-        <v>163.22019545454501</v>
+        <v>156.02663181818099</v>
       </c>
       <c r="D20">
-        <v>193.52915454545399</v>
+        <v>185.89139999999901</v>
       </c>
       <c r="E20">
-        <v>206.658572727272</v>
+        <v>197.70654545454499</v>
       </c>
       <c r="F20">
-        <v>238.450663636363</v>
+        <v>236.61400909090901</v>
       </c>
       <c r="G20">
         <v>141.273100616016</v>
@@ -5357,19 +5373,19 @@
         <v>4</v>
       </c>
       <c r="B21">
-        <v>149.89929272727201</v>
+        <v>144.990234545454</v>
       </c>
       <c r="C21">
-        <v>164.51982818181801</v>
+        <v>157.22145545454501</v>
       </c>
       <c r="D21">
-        <v>194.216236363636</v>
+        <v>186.38549999999901</v>
       </c>
       <c r="E21">
-        <v>213.80888181818099</v>
+        <v>206.13619090909</v>
       </c>
       <c r="F21">
-        <v>245.87879999999899</v>
+        <v>244.14196363636299</v>
       </c>
       <c r="G21">
         <v>149.48665297741201</v>
@@ -5380,19 +5396,19 @@
         <v>4</v>
       </c>
       <c r="B22">
-        <v>152.02392272727201</v>
+        <v>146.77132363636301</v>
       </c>
       <c r="C22">
-        <v>167.90249999999901</v>
+        <v>159.54721909090901</v>
       </c>
       <c r="D22">
-        <v>198.533372727272</v>
+        <v>190.35327272727201</v>
       </c>
       <c r="E22">
-        <v>214.69559999999899</v>
+        <v>206.247654545454</v>
       </c>
       <c r="F22">
-        <v>247.071627272727</v>
+        <v>245.076927272727</v>
       </c>
       <c r="G22">
         <v>152.77207392197101</v>
@@ -5403,19 +5419,19 @@
         <v>4</v>
       </c>
       <c r="B23">
-        <v>152.923783636363</v>
+        <v>147.725918181818</v>
       </c>
       <c r="C23">
-        <v>168.31009090909001</v>
+        <v>161.258768181818</v>
       </c>
       <c r="D23">
-        <v>199.205481818181</v>
+        <v>191.18509090909001</v>
       </c>
       <c r="E23">
-        <v>218.79313636363599</v>
+        <v>209.59655454545401</v>
       </c>
       <c r="F23">
-        <v>248.765209090909</v>
+        <v>247.83689999999899</v>
       </c>
       <c r="G23">
         <v>157.70020533880901</v>
@@ -5426,19 +5442,19 @@
         <v>4</v>
       </c>
       <c r="B24">
-        <v>153.716672727272</v>
+        <v>148.16911090908999</v>
       </c>
       <c r="C24">
-        <v>168.98552727272701</v>
+        <v>161.44808999999901</v>
       </c>
       <c r="D24">
-        <v>200.15209090908999</v>
+        <v>191.85553636363599</v>
       </c>
       <c r="E24">
-        <v>221.17879090909</v>
+        <v>211.58959090908999</v>
       </c>
       <c r="F24">
-        <v>259.13964545454502</v>
+        <v>257.00519999999898</v>
       </c>
       <c r="G24">
         <v>160.164271047227</v>
@@ -5449,19 +5465,19 @@
         <v>4</v>
       </c>
       <c r="B25">
-        <v>153.99782727272699</v>
+        <v>148.81726363636301</v>
       </c>
       <c r="C25">
-        <v>169.37149090909</v>
+        <v>161.893445454545</v>
       </c>
       <c r="D25">
-        <v>200.368363636363</v>
+        <v>192.28309090908999</v>
       </c>
       <c r="E25">
-        <v>230.71808181818099</v>
+        <v>221.331845454545</v>
       </c>
       <c r="F25">
-        <v>269.04160909090899</v>
+        <v>266.41306363636301</v>
       </c>
       <c r="G25">
         <v>169.19917864476301</v>
@@ -5472,19 +5488,19 @@
         <v>4</v>
       </c>
       <c r="B26">
-        <v>155.03743363636301</v>
+        <v>148.83107181818099</v>
       </c>
       <c r="C26">
-        <v>170.950281818181</v>
+        <v>163.20355909090901</v>
       </c>
       <c r="D26">
-        <v>202.96862727272699</v>
+        <v>194.42918181818101</v>
       </c>
       <c r="E26">
-        <v>231.744545454545</v>
+        <v>222.09878181818101</v>
       </c>
       <c r="F26">
-        <v>271.06126363636298</v>
+        <v>268.78041818181799</v>
       </c>
       <c r="G26">
         <v>171.66324435318199</v>
@@ -5495,19 +5511,19 @@
         <v>4</v>
       </c>
       <c r="B27">
-        <v>157.23393272727199</v>
+        <v>154.37547272727201</v>
       </c>
       <c r="C27">
-        <v>171.06174545454499</v>
+        <v>163.43680090909001</v>
       </c>
       <c r="D27">
-        <v>204.221345454545</v>
+        <v>195.39409090909001</v>
       </c>
       <c r="E27">
-        <v>233.57953636363601</v>
+        <v>222.942245454545</v>
       </c>
       <c r="F27">
-        <v>290.44595454545401</v>
+        <v>287.90558181818102</v>
       </c>
       <c r="G27">
         <v>177.41273100615999</v>
@@ -5518,19 +5534,19 @@
         <v>4</v>
       </c>
       <c r="B28">
-        <v>159.99773181818099</v>
+        <v>154.875894545454</v>
       </c>
       <c r="C28">
-        <v>174.56037272727201</v>
+        <v>166.83777272727201</v>
       </c>
       <c r="D28">
-        <v>206.04469090909001</v>
+        <v>197.51356363636299</v>
       </c>
       <c r="E28">
-        <v>234.74907272727199</v>
+        <v>223.61601818181799</v>
       </c>
       <c r="F28">
-        <v>298.95212727272701</v>
+        <v>296.76610909090903</v>
       </c>
       <c r="G28">
         <v>189.733059548254</v>
@@ -5541,19 +5557,19 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>160.102873636363</v>
+        <v>156.57280363636301</v>
       </c>
       <c r="C29">
-        <v>176.91275454545399</v>
+        <v>169.19847272727199</v>
       </c>
       <c r="D29">
-        <v>206.18277272727201</v>
+        <v>198.02429999999899</v>
       </c>
       <c r="E29">
-        <v>235.97184545454499</v>
+        <v>225.27133636363601</v>
       </c>
       <c r="F29">
-        <v>299.20832727272699</v>
+        <v>297.08885454545401</v>
       </c>
       <c r="G29">
         <v>189.733059548254</v>
@@ -5564,19 +5580,19 @@
         <v>4</v>
       </c>
       <c r="B30">
-        <v>160.325468181818</v>
+        <v>156.78691363636301</v>
       </c>
       <c r="C30">
-        <v>177.375245454545</v>
+        <v>169.47463636363599</v>
       </c>
       <c r="D30">
-        <v>207.79150909090899</v>
+        <v>199.46001818181799</v>
       </c>
       <c r="E30">
-        <v>237.687054545454</v>
+        <v>225.376145454545</v>
       </c>
       <c r="F30">
-        <v>299.93367272727198</v>
+        <v>297.97557272727198</v>
       </c>
       <c r="G30">
         <v>192.19712525667299</v>
@@ -5587,19 +5603,19 @@
         <v>4</v>
       </c>
       <c r="B31">
-        <v>160.64105999999899</v>
+        <v>157.342401818181</v>
       </c>
       <c r="C31">
-        <v>180.611018181818</v>
+        <v>173.03648181818099</v>
       </c>
       <c r="D31">
-        <v>208.719818181818</v>
+        <v>199.88424545454501</v>
       </c>
       <c r="E31">
-        <v>238.02144545454499</v>
+        <v>225.50091818181801</v>
       </c>
       <c r="F31">
-        <v>304.868018181818</v>
+        <v>302.57219999999899</v>
       </c>
       <c r="G31">
         <v>260.369609856262</v>
@@ -5610,19 +5626,19 @@
         <v>4</v>
       </c>
       <c r="B32">
-        <v>161.491677272727</v>
+        <v>158.84666181818099</v>
       </c>
       <c r="C32">
-        <v>182.56579090909</v>
+        <v>174.186054545454</v>
       </c>
       <c r="D32">
-        <v>208.906145454545</v>
+        <v>199.99071818181801</v>
       </c>
       <c r="E32">
-        <v>238.25102727272699</v>
+        <v>227.88158181818099</v>
       </c>
       <c r="F32">
-        <v>306.86937272727198</v>
+        <v>304.65673636363601</v>
       </c>
       <c r="G32">
         <v>267.76180698151899</v>
@@ -5633,19 +5649,19 @@
         <v>4</v>
       </c>
       <c r="B33">
-        <v>164.58055090908999</v>
+        <v>163.348129090909</v>
       </c>
       <c r="C33">
-        <v>183.17967272727199</v>
+        <v>174.918054545454</v>
       </c>
       <c r="D33">
-        <v>209.23221818181801</v>
+        <v>200.69942727272701</v>
       </c>
       <c r="E33">
-        <v>239.13275454545399</v>
+        <v>229.44040909090899</v>
       </c>
       <c r="F33">
-        <v>307.49489999999901</v>
+        <v>304.92291818181798</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -5653,19 +5669,19 @@
         <v>4</v>
       </c>
       <c r="B34">
-        <v>165.94439999999901</v>
+        <v>163.51415999999901</v>
       </c>
       <c r="C34">
-        <v>187.090881818181</v>
+        <v>179.58289090909</v>
       </c>
       <c r="D34">
-        <v>211.66112727272699</v>
+        <v>203.06844545454501</v>
       </c>
       <c r="E34">
-        <v>240.568472727272</v>
+        <v>230.92104545454501</v>
       </c>
       <c r="F34">
-        <v>316.62493636363598</v>
+        <v>313.78344545454502</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -5673,19 +5689,19 @@
         <v>4</v>
       </c>
       <c r="B35">
-        <v>166.83777272727201</v>
+        <v>165.37743272727201</v>
       </c>
       <c r="C35">
-        <v>188.67133636363599</v>
+        <v>180.55611818181799</v>
       </c>
       <c r="D35">
-        <v>211.96557272727199</v>
+        <v>203.26142727272699</v>
       </c>
       <c r="E35">
-        <v>244.68430909090901</v>
+        <v>231.50830909090899</v>
       </c>
       <c r="F35">
-        <v>316.76135454545403</v>
+        <v>313.92152727272702</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -5693,19 +5709,19 @@
         <v>4</v>
       </c>
       <c r="B36">
-        <v>170.28316363636301</v>
+        <v>169.27999090909</v>
       </c>
       <c r="C36">
-        <v>189.95067272727201</v>
+        <v>182.379463636363</v>
       </c>
       <c r="D36">
-        <v>215.50745454545401</v>
+        <v>206.991299999999</v>
       </c>
       <c r="E36">
-        <v>246.327981818181</v>
+        <v>233.11704545454501</v>
       </c>
       <c r="F36">
-        <v>319.92891818181801</v>
+        <v>317.68799999999902</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -5713,19 +5729,19 @@
         <v>4</v>
       </c>
       <c r="B37">
-        <v>171.56749090909</v>
+        <v>170.37799090908999</v>
       </c>
       <c r="C37">
-        <v>191.59101818181799</v>
+        <v>183.17634545454499</v>
       </c>
       <c r="D37">
-        <v>218.650063636363</v>
+        <v>209.94092727272701</v>
       </c>
       <c r="E37">
-        <v>246.39785454545401</v>
+        <v>233.972154545454</v>
       </c>
       <c r="F37">
-        <v>329.689472727272</v>
+        <v>326.69159999999903</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -5733,19 +5749,19 @@
         <v>4</v>
       </c>
       <c r="B38">
-        <v>172.47916363636301</v>
+        <v>172.05826363636299</v>
       </c>
       <c r="C38">
-        <v>192.35795454545399</v>
+        <v>184.701899999999</v>
       </c>
       <c r="D38">
-        <v>220.32035454545399</v>
+        <v>210.88919999999899</v>
       </c>
       <c r="E38">
-        <v>246.74222727272701</v>
+        <v>233.97880909090901</v>
       </c>
       <c r="F38">
-        <v>332.25979090908999</v>
+        <v>329.23197272727202</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -5753,19 +5769,19 @@
         <v>4</v>
       </c>
       <c r="B39">
-        <v>173.15792727272699</v>
+        <v>177.77950909090899</v>
       </c>
       <c r="C39">
-        <v>192.97849090909</v>
+        <v>184.71021818181799</v>
       </c>
       <c r="D39">
-        <v>221.047363636363</v>
+        <v>211.865754545454</v>
       </c>
       <c r="E39">
-        <v>247.31119090908999</v>
+        <v>235.00859999999901</v>
       </c>
       <c r="F39">
-        <v>333.82693636363598</v>
+        <v>330.76917272727201</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -5773,19 +5789,19 @@
         <v>4</v>
       </c>
       <c r="B40">
-        <v>173.88992727272699</v>
+        <v>177.81278181818101</v>
       </c>
       <c r="C40">
-        <v>193.20474545454499</v>
+        <v>185.40062727272701</v>
       </c>
       <c r="D40">
-        <v>221.40504545454499</v>
+        <v>212.49627272727199</v>
       </c>
       <c r="E40">
-        <v>247.73375454545399</v>
+        <v>236.60569090908999</v>
       </c>
       <c r="F40">
-        <v>336.35732727272699</v>
+        <v>333.60899999999998</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -5793,19 +5809,19 @@
         <v>4</v>
       </c>
       <c r="B41">
-        <v>177.852709090909</v>
+        <v>181.65744545454501</v>
       </c>
       <c r="C41">
-        <v>193.25631818181799</v>
+        <v>185.51375454545399</v>
       </c>
       <c r="D41">
-        <v>221.43665454545399</v>
+        <v>212.71254545454499</v>
       </c>
       <c r="E41">
-        <v>264.44165454545401</v>
+        <v>252.28379999999899</v>
       </c>
       <c r="F41">
-        <v>336.43219090909002</v>
+        <v>334.29774545454501</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -5813,19 +5829,19 @@
         <v>4</v>
       </c>
       <c r="B42">
-        <v>179.451463636363</v>
+        <v>181.710681818181</v>
       </c>
       <c r="C42">
-        <v>196.653463636363</v>
+        <v>189.022363636363</v>
       </c>
       <c r="D42">
-        <v>226.720363636363</v>
+        <v>217.53209999999899</v>
       </c>
       <c r="E42">
-        <v>279.32288181818097</v>
+        <v>264.360136363636</v>
       </c>
       <c r="F42">
-        <v>361.300227272727</v>
+        <v>358.621772727272</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -5833,19 +5849,19 @@
         <v>4</v>
       </c>
       <c r="B43">
-        <v>179.549618181818</v>
+        <v>183.332727272727</v>
       </c>
       <c r="C43">
-        <v>202.40631818181799</v>
+        <v>194.540645454545</v>
       </c>
       <c r="D43">
-        <v>228.85813636363599</v>
+        <v>217.94301818181799</v>
       </c>
       <c r="E43">
-        <v>281.20112727272698</v>
+        <v>266.76741818181802</v>
       </c>
       <c r="F43">
-        <v>366.61887272727199</v>
+        <v>364.49773636363602</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -5853,19 +5869,19 @@
         <v>4</v>
       </c>
       <c r="B44">
-        <v>180.065345454545</v>
+        <v>184.013154545454</v>
       </c>
       <c r="C44">
-        <v>204.67219090909001</v>
+        <v>196.40724545454501</v>
       </c>
       <c r="D44">
-        <v>242.024154545454</v>
+        <v>232.105554545454</v>
       </c>
       <c r="E44">
-        <v>293.66009999999898</v>
+        <v>278.42618181818102</v>
       </c>
       <c r="F44">
-        <v>377.086472727272</v>
+        <v>374.75405454545398</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -5873,19 +5889,19 @@
         <v>4</v>
       </c>
       <c r="B45">
-        <v>180.87719999999899</v>
+        <v>186.64169999999899</v>
       </c>
       <c r="C45">
-        <v>205.43413636363599</v>
+        <v>197.540181818181</v>
       </c>
       <c r="D45">
-        <v>295.24887272727199</v>
+        <v>283.49528181818101</v>
       </c>
       <c r="E45">
-        <v>358.328972727272</v>
+        <v>346.74340909090898</v>
       </c>
       <c r="F45">
-        <v>455.07774545454498</v>
+        <v>451.42606363636298</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -5893,19 +5909,19 @@
         <v>4</v>
       </c>
       <c r="B46">
-        <v>181.078499999999</v>
+        <v>187.38534545454499</v>
       </c>
       <c r="C46">
-        <v>207.71997272727199</v>
+        <v>198.74798181818099</v>
       </c>
       <c r="D46">
-        <v>305.89281818181797</v>
+        <v>291.97816363636298</v>
       </c>
       <c r="E46">
-        <v>382.636363636363</v>
+        <v>363.65926363636299</v>
       </c>
       <c r="F46">
-        <v>545.29009090909005</v>
+        <v>540.26424545454495</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -5913,19 +5929,19 @@
         <v>4</v>
       </c>
       <c r="B47">
-        <v>182.26799999999901</v>
+        <v>191.86219090909</v>
       </c>
       <c r="C47">
-        <v>223.76408181818101</v>
+        <v>211.16369999999901</v>
       </c>
       <c r="D47">
-        <v>377.39590909090902</v>
+        <v>360.00092727272698</v>
       </c>
       <c r="E47">
-        <v>478.88105454545399</v>
+        <v>457.777827272727</v>
       </c>
       <c r="F47">
-        <v>624.32945454545404</v>
+        <v>620.71769999999901</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -5933,39 +5949,36 @@
         <v>4</v>
       </c>
       <c r="B48">
-        <v>187.050954545454</v>
+        <v>193.85689090909</v>
       </c>
       <c r="C48">
-        <v>233.276754545454</v>
+        <v>220.335327272727</v>
       </c>
       <c r="D48">
-        <v>388.60881818181798</v>
+        <v>372.599645454545</v>
       </c>
       <c r="E48">
-        <v>483.35290909090901</v>
+        <v>459.20855454545398</v>
       </c>
       <c r="F48">
-        <v>629.20224545454505</v>
+        <v>624.07658181818101</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>4</v>
       </c>
-      <c r="B49">
-        <v>189.69779999999901</v>
-      </c>
       <c r="C49">
-        <v>250.31239090909</v>
+        <v>236.682218181818</v>
       </c>
       <c r="D49">
-        <v>404.89914545454502</v>
+        <v>387.62394545454498</v>
       </c>
       <c r="E49">
-        <v>503.70749999999902</v>
+        <v>479.917499999999</v>
       </c>
       <c r="F49">
-        <v>661.11411818181796</v>
+        <v>655.86700909090803</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -5973,16 +5986,16 @@
         <v>4</v>
       </c>
       <c r="C50">
-        <v>268.73882727272701</v>
+        <v>254.216945454545</v>
       </c>
       <c r="D50">
-        <v>466.33058181818097</v>
+        <v>448.61119090909</v>
       </c>
       <c r="E50">
-        <v>562.59689999999898</v>
+        <v>545.93558181818105</v>
       </c>
       <c r="F50">
-        <v>706.47316363636298</v>
+        <v>700.71199090908999</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -5990,19 +6003,19 @@
         <v>3</v>
       </c>
       <c r="B51">
-        <v>139.85325818181801</v>
+        <v>131.69711454545401</v>
       </c>
       <c r="C51">
-        <v>139.673086363636</v>
+        <v>131.98325999999901</v>
       </c>
       <c r="D51">
-        <v>143.25073636363601</v>
+        <v>134.928894545454</v>
       </c>
       <c r="E51">
-        <v>151.90048090908999</v>
+        <v>141.63218454545401</v>
       </c>
       <c r="F51">
-        <v>167.519863636363</v>
+        <v>163.944209999999</v>
       </c>
       <c r="G51">
         <v>120</v>
@@ -6016,19 +6029,19 @@
         <v>3</v>
       </c>
       <c r="B52">
-        <v>169.99535454545401</v>
+        <v>163.35894272727199</v>
       </c>
       <c r="C52">
-        <v>171.820363636363</v>
+        <v>163.63710272727201</v>
       </c>
       <c r="D52">
-        <v>175.31899090908999</v>
+        <v>166.506709090909</v>
       </c>
       <c r="E52">
-        <v>183.57229090908999</v>
+        <v>172.94165454545401</v>
       </c>
       <c r="F52">
-        <v>197.832981818181</v>
+        <v>194.24950909090899</v>
       </c>
       <c r="G52">
         <v>161</v>
@@ -6039,19 +6052,19 @@
         <v>3</v>
       </c>
       <c r="B53">
-        <v>172.17471818181801</v>
+        <v>168.48310909090901</v>
       </c>
       <c r="C53">
-        <v>177.25879090909001</v>
+        <v>168.67775454545401</v>
       </c>
       <c r="D53">
-        <v>180.203427272727</v>
+        <v>171.01516363636301</v>
       </c>
       <c r="E53">
-        <v>187.46187272727201</v>
+        <v>176.62494545454501</v>
       </c>
       <c r="F53">
-        <v>199.782763636363</v>
+        <v>196.22091818181801</v>
       </c>
       <c r="G53">
         <v>234</v>
@@ -6062,19 +6075,19 @@
         <v>3</v>
       </c>
       <c r="B54">
-        <v>172.94664545454501</v>
+        <v>175.24412727272701</v>
       </c>
       <c r="C54">
-        <v>179.16032727272699</v>
+        <v>170.71903636363601</v>
       </c>
       <c r="D54">
-        <v>182.41606363636299</v>
+        <v>173.347581818181</v>
       </c>
       <c r="E54">
-        <v>190.23681818181799</v>
+        <v>179.40987272727199</v>
       </c>
       <c r="F54">
-        <v>200.205327272727</v>
+        <v>196.82481818181799</v>
       </c>
       <c r="G54">
         <v>350</v>
@@ -6085,19 +6098,19 @@
         <v>3</v>
       </c>
       <c r="B55">
-        <v>175.70661818181799</v>
+        <v>175.59182727272699</v>
       </c>
       <c r="C55">
-        <v>183.910009090909</v>
+        <v>175.48868181818099</v>
       </c>
       <c r="D55">
-        <v>187.09254545454499</v>
+        <v>177.89762727272699</v>
       </c>
       <c r="E55">
-        <v>191.830581818181</v>
+        <v>181.01694545454501</v>
       </c>
       <c r="F55">
-        <v>203.75386363636301</v>
+        <v>200.12879999999899</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -6105,19 +6118,19 @@
         <v>3</v>
       </c>
       <c r="B56">
-        <v>180.195109090909</v>
+        <v>177.005918181818</v>
       </c>
       <c r="C56">
-        <v>183.973227272727</v>
+        <v>175.82972727272701</v>
       </c>
       <c r="D56">
-        <v>187.150772727272</v>
+        <v>178.10890909090901</v>
       </c>
       <c r="E56">
-        <v>194.454136363636</v>
+        <v>184.09467272727201</v>
       </c>
       <c r="F56">
-        <v>207.049527272727</v>
+        <v>203.71726363636299</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -6125,19 +6138,19 @@
         <v>3</v>
       </c>
       <c r="B57">
-        <v>180.41637272727201</v>
+        <v>177.09908181818099</v>
       </c>
       <c r="C57">
-        <v>185.98456363636299</v>
+        <v>177.085772727272</v>
       </c>
       <c r="D57">
-        <v>187.387009090909</v>
+        <v>178.35845454545401</v>
       </c>
       <c r="E57">
-        <v>194.876699999999</v>
+        <v>184.107981818181</v>
       </c>
       <c r="F57">
-        <v>208.21573636363601</v>
+        <v>204.640581818181</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -6145,19 +6158,19 @@
         <v>3</v>
       </c>
       <c r="B58">
-        <v>180.88219090909001</v>
+        <v>179.933918181818</v>
       </c>
       <c r="C58">
-        <v>188.388518181818</v>
+        <v>177.505009090909</v>
       </c>
       <c r="D58">
-        <v>191.336481818181</v>
+        <v>181.900336363636</v>
       </c>
       <c r="E58">
-        <v>197.55848181818101</v>
+        <v>186.63837272727201</v>
       </c>
       <c r="F58">
-        <v>208.268972727272</v>
+        <v>204.66220909090899</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -6165,19 +6178,19 @@
         <v>3</v>
       </c>
       <c r="B59">
-        <v>182.04174545454501</v>
+        <v>181.53932727272701</v>
       </c>
       <c r="C59">
-        <v>188.90424545454499</v>
+        <v>180.060354545454</v>
       </c>
       <c r="D59">
-        <v>192.748909090909</v>
+        <v>182.29295454545399</v>
       </c>
       <c r="E59">
-        <v>199.386818181818</v>
+        <v>188.598136363636</v>
       </c>
       <c r="F59">
-        <v>210.91415454545401</v>
+        <v>207.46709999999899</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -6185,19 +6198,19 @@
         <v>3</v>
       </c>
       <c r="B60">
-        <v>188.54989090909001</v>
+        <v>182.47429090909</v>
       </c>
       <c r="C60">
-        <v>190.31667272727199</v>
+        <v>181.630827272727</v>
       </c>
       <c r="D60">
-        <v>193.860218181818</v>
+        <v>183.48910909090901</v>
       </c>
       <c r="E60">
-        <v>205.70031818181801</v>
+        <v>192.071809090909</v>
       </c>
       <c r="F60">
-        <v>218.13433636363601</v>
+        <v>214.329599999999</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -6205,19 +6218,19 @@
         <v>3</v>
       </c>
       <c r="B61">
-        <v>189.70445454545401</v>
+        <v>187.90772727272699</v>
       </c>
       <c r="C61">
-        <v>193.14319090909001</v>
+        <v>182.84528181818101</v>
       </c>
       <c r="D61">
-        <v>197.293963636363</v>
+        <v>186.46036363636301</v>
       </c>
       <c r="E61">
-        <v>205.96483636363601</v>
+        <v>193.63229999999899</v>
       </c>
       <c r="F61">
-        <v>219.12919090909</v>
+        <v>215.53074545454501</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -6225,19 +6238,19 @@
         <v>3</v>
       </c>
       <c r="B62">
-        <v>191.015399999999</v>
+        <v>193.69884545454499</v>
       </c>
       <c r="C62">
-        <v>196.866409090909</v>
+        <v>188.10569999999899</v>
       </c>
       <c r="D62">
-        <v>199.75780909090901</v>
+        <v>190.37989090908999</v>
       </c>
       <c r="E62">
-        <v>206.81329090909</v>
+        <v>195.80833636363599</v>
       </c>
       <c r="F62">
-        <v>222.67273636363601</v>
+        <v>218.997763636363</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -6245,19 +6258,19 @@
         <v>3</v>
       </c>
       <c r="B63">
-        <v>194.45080909090899</v>
+        <v>201.77912727272701</v>
       </c>
       <c r="C63">
-        <v>203.334627272727</v>
+        <v>193.85855454545401</v>
       </c>
       <c r="D63">
-        <v>205.92989999999901</v>
+        <v>195.878209090909</v>
       </c>
       <c r="E63">
-        <v>212.23175454545401</v>
+        <v>200.75765454545399</v>
       </c>
       <c r="F63">
-        <v>223.60603636363601</v>
+        <v>219.307199999999</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -6265,19 +6278,19 @@
         <v>3</v>
       </c>
       <c r="B64">
-        <v>197.37880909090899</v>
+        <v>202.69745454545401</v>
       </c>
       <c r="C64">
-        <v>210.97404545454501</v>
+        <v>201.96545454545401</v>
       </c>
       <c r="D64">
-        <v>213.75398181818099</v>
+        <v>204.154799999999</v>
       </c>
       <c r="E64">
-        <v>220.505018181818</v>
+        <v>209.178981818181</v>
       </c>
       <c r="F64">
-        <v>224.05688181818101</v>
+        <v>220.596518181818</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -6285,19 +6298,19 @@
         <v>3</v>
       </c>
       <c r="B65">
-        <v>204.39436363636301</v>
+        <v>207.462109090909</v>
       </c>
       <c r="C65">
-        <v>212.675945454545</v>
+        <v>202.88378181818101</v>
       </c>
       <c r="D65">
-        <v>215.583981818181</v>
+        <v>205.15797272727201</v>
       </c>
       <c r="E65">
-        <v>220.821109090909</v>
+        <v>209.41854545454501</v>
       </c>
       <c r="F65">
-        <v>232.36009090908999</v>
+        <v>228.695099999999</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -6305,19 +6318,19 @@
         <v>3</v>
       </c>
       <c r="B66">
-        <v>204.75703636363599</v>
+        <v>212.35652727272699</v>
       </c>
       <c r="C66">
-        <v>216.02484545454499</v>
+        <v>206.824936363636</v>
       </c>
       <c r="D66">
-        <v>218.53693636363599</v>
+        <v>207.57856363636299</v>
       </c>
       <c r="E66">
-        <v>222.649445454545</v>
+        <v>210.63299999999899</v>
       </c>
       <c r="F66">
-        <v>232.46989090909</v>
+        <v>228.838172727272</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -6325,19 +6338,19 @@
         <v>3</v>
       </c>
       <c r="B67">
-        <v>205.35927272727201</v>
+        <v>214.60576363636301</v>
       </c>
       <c r="C67">
-        <v>217.85983636363599</v>
+        <v>207.36229090909001</v>
       </c>
       <c r="D67">
-        <v>218.73490909090901</v>
+        <v>208.95439090908999</v>
       </c>
       <c r="E67">
-        <v>225.28131818181799</v>
+        <v>214.10500909090899</v>
       </c>
       <c r="F67">
-        <v>234.52448181818099</v>
+        <v>230.61659999999901</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -6345,19 +6358,19 @@
         <v>3</v>
       </c>
       <c r="B68">
-        <v>212.161881818181</v>
+        <v>217.16776363636299</v>
       </c>
       <c r="C68">
-        <v>222.36662727272699</v>
+        <v>212.48795454545399</v>
       </c>
       <c r="D68">
-        <v>224.828809090909</v>
+        <v>214.337918181818</v>
       </c>
       <c r="E68">
-        <v>227.84664545454501</v>
+        <v>216.34592727272701</v>
       </c>
       <c r="F68">
-        <v>236.928436363636</v>
+        <v>233.078781818181</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -6365,39 +6378,36 @@
         <v>3</v>
       </c>
       <c r="B69">
-        <v>218.309018181818</v>
+        <v>224.778899999999</v>
       </c>
       <c r="C69">
-        <v>224.54765454545401</v>
+        <v>214.495963636363</v>
       </c>
       <c r="D69">
-        <v>225.193145454545</v>
+        <v>214.61574545454499</v>
       </c>
       <c r="E69">
-        <v>230.97927272727199</v>
+        <v>219.04767272727199</v>
       </c>
       <c r="F69">
-        <v>241.37699999999899</v>
+        <v>237.540654545454</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>3</v>
       </c>
-      <c r="B70">
-        <v>232.406672727272</v>
-      </c>
       <c r="C70">
-        <v>226.46249999999901</v>
+        <v>217.00139999999899</v>
       </c>
       <c r="D70">
-        <v>229.04779090909</v>
+        <v>219.006081818181</v>
       </c>
       <c r="E70">
-        <v>235.337999999999</v>
+        <v>223.955399999999</v>
       </c>
       <c r="F70">
-        <v>246.62743636363601</v>
+        <v>242.69959090909001</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -6405,16 +6415,16 @@
         <v>3</v>
       </c>
       <c r="C71">
-        <v>226.989872727272</v>
+        <v>217.32747272727201</v>
       </c>
       <c r="D71">
-        <v>229.61509090908999</v>
+        <v>219.37707272727201</v>
       </c>
       <c r="E71">
-        <v>235.923599999999</v>
+        <v>224.391272727272</v>
       </c>
       <c r="F71">
-        <v>247.118209090909</v>
+        <v>243.103854545454</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -6422,16 +6432,16 @@
         <v>3</v>
       </c>
       <c r="C72">
-        <v>228.999545454545</v>
+        <v>218.641745454545</v>
       </c>
       <c r="D72">
-        <v>231.85434545454501</v>
+        <v>220.92591818181799</v>
       </c>
       <c r="E72">
-        <v>238.384118181818</v>
+        <v>226.31110909090901</v>
       </c>
       <c r="F72">
-        <v>249.58039090909</v>
+        <v>245.299854545454</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -6439,16 +6449,16 @@
         <v>3</v>
       </c>
       <c r="C73">
-        <v>236.851909090909</v>
+        <v>225.18149999999901</v>
       </c>
       <c r="D73">
-        <v>241.59327272727199</v>
+        <v>229.22746363636301</v>
       </c>
       <c r="E73">
-        <v>251.78969999999899</v>
+        <v>237.65877272727201</v>
       </c>
       <c r="F73">
-        <v>266.828972727272</v>
+        <v>262.47689999999898</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -6456,30 +6466,33 @@
         <v>3</v>
       </c>
       <c r="C74">
-        <v>417.55609090909002</v>
+        <v>407.53101818181801</v>
       </c>
       <c r="D74">
-        <v>415.409999999999</v>
+        <v>404.95903636363602</v>
       </c>
       <c r="E74">
-        <v>413.05096363636301</v>
+        <v>402.36209999999897</v>
       </c>
       <c r="F74">
-        <v>411.84649090908999</v>
+        <v>408.87523636363602</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1</v>
       </c>
+      <c r="B75">
+        <v>136.813295454545</v>
+      </c>
       <c r="C75">
+        <v>136.26346363636301</v>
+      </c>
+      <c r="D75">
+        <v>135.82326545454501</v>
+      </c>
+      <c r="E75">
         <v>147.81808363636301</v>
-      </c>
-      <c r="D75">
-        <v>147.81808363636301</v>
-      </c>
-      <c r="E75">
-        <v>159.44557090909001</v>
       </c>
       <c r="G75">
         <v>136.587771203155</v>
@@ -6492,14 +6505,17 @@
       <c r="A76" t="s">
         <v>1</v>
       </c>
+      <c r="B76">
+        <v>136.813295454545</v>
+      </c>
       <c r="C76">
+        <v>136.26346363636301</v>
+      </c>
+      <c r="D76">
+        <v>135.82326545454501</v>
+      </c>
+      <c r="E76">
         <v>147.81808363636301</v>
-      </c>
-      <c r="D76">
-        <v>147.81808363636301</v>
-      </c>
-      <c r="E76">
-        <v>163.58735999999899</v>
       </c>
       <c r="G76">
         <v>144.47731755423999</v>
@@ -6509,14 +6525,17 @@
       <c r="A77" t="s">
         <v>1</v>
       </c>
+      <c r="B77">
+        <v>136.813295454545</v>
+      </c>
       <c r="C77">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D77">
-        <v>147.81808363636301</v>
+        <v>135.82326545454501</v>
       </c>
       <c r="E77">
-        <v>179.27844545454499</v>
+        <v>156.29697272727199</v>
       </c>
       <c r="G77">
         <v>151.380670611439</v>
@@ -6526,14 +6545,17 @@
       <c r="A78" t="s">
         <v>1</v>
       </c>
+      <c r="B78">
+        <v>136.813295454545</v>
+      </c>
       <c r="C78">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D78">
-        <v>147.81808363636301</v>
+        <v>135.82326545454501</v>
       </c>
       <c r="E78">
-        <v>185.571981818181</v>
+        <v>161.37505636363599</v>
       </c>
       <c r="G78">
         <v>228.79684418145899</v>
@@ -6543,14 +6565,17 @@
       <c r="A79" t="s">
         <v>1</v>
       </c>
+      <c r="B79">
+        <v>136.813295454545</v>
+      </c>
       <c r="C79">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D79">
-        <v>147.81808363636301</v>
+        <v>135.82326545454501</v>
       </c>
       <c r="E79">
-        <v>186.094363636363</v>
+        <v>161.545579090909</v>
       </c>
       <c r="G79">
         <v>246.05522682445701</v>
@@ -6560,14 +6585,17 @@
       <c r="A80" t="s">
         <v>1</v>
       </c>
+      <c r="B80">
+        <v>136.813295454545</v>
+      </c>
       <c r="C80">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D80">
-        <v>164.902298181818</v>
+        <v>153.25135363636301</v>
       </c>
       <c r="E80">
-        <v>226.30778181818101</v>
+        <v>195.88319999999899</v>
       </c>
       <c r="G80">
         <v>248.02761341222799</v>
@@ -6577,14 +6605,17 @@
       <c r="A81" t="s">
         <v>1</v>
       </c>
+      <c r="B81">
+        <v>136.813295454545</v>
+      </c>
       <c r="C81">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D81">
-        <v>171.832009090909</v>
+        <v>159.716244545454</v>
       </c>
       <c r="E81">
-        <v>234.05034545454501</v>
+        <v>203.113363636363</v>
       </c>
       <c r="G81">
         <v>324.45759368836298</v>
@@ -6594,14 +6625,17 @@
       <c r="A82" t="s">
         <v>1</v>
       </c>
+      <c r="B82">
+        <v>136.813295454545</v>
+      </c>
       <c r="C82">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D82">
-        <v>175.981118181818</v>
+        <v>163.33481999999901</v>
       </c>
       <c r="E82">
-        <v>239.340709090909</v>
+        <v>207.23419090908999</v>
       </c>
       <c r="G82">
         <v>328.402366863905</v>
@@ -6611,14 +6645,17 @@
       <c r="A83" t="s">
         <v>1</v>
       </c>
+      <c r="B83">
+        <v>136.813295454545</v>
+      </c>
       <c r="C83">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D83">
-        <v>176.029363636363</v>
+        <v>163.597508181818</v>
       </c>
       <c r="E83">
-        <v>239.891372727272</v>
+        <v>208.220727272727</v>
       </c>
       <c r="G83">
         <v>377.712031558185</v>
@@ -6628,14 +6665,17 @@
       <c r="A84" t="s">
         <v>1</v>
       </c>
+      <c r="B84">
+        <v>136.813295454545</v>
+      </c>
       <c r="C84">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D84">
-        <v>181.18996363636299</v>
+        <v>168.33338181818101</v>
       </c>
       <c r="E84">
-        <v>251.33386363636299</v>
+        <v>217.547072727272</v>
       </c>
       <c r="G84">
         <v>433.43195266272102</v>
@@ -6645,546 +6685,663 @@
       <c r="A85" t="s">
         <v>1</v>
       </c>
+      <c r="B85">
+        <v>136.813295454545</v>
+      </c>
       <c r="C85">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D85">
-        <v>186.12098181818101</v>
+        <v>170.913681818181</v>
       </c>
       <c r="E85">
-        <v>251.541818181818</v>
+        <v>217.63524545454499</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1</v>
       </c>
+      <c r="B86">
+        <v>136.813295454545</v>
+      </c>
       <c r="C86">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D86">
-        <v>187.486827272727</v>
+        <v>173.129645454545</v>
       </c>
       <c r="E86">
-        <v>256.09019999999902</v>
+        <v>224.667436363636</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>1</v>
       </c>
+      <c r="B87">
+        <v>136.813295454545</v>
+      </c>
       <c r="C87">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D87">
-        <v>194.379272727272</v>
+        <v>180.65759999999901</v>
       </c>
       <c r="E87">
-        <v>260.85152727272703</v>
+        <v>230.74303636363601</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>1</v>
       </c>
+      <c r="B88">
+        <v>136.813295454545</v>
+      </c>
       <c r="C88">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D88">
-        <v>194.50570909090899</v>
+        <v>180.89383636363601</v>
       </c>
       <c r="E88">
-        <v>262.54677272727201</v>
+        <v>232.108881818181</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1</v>
       </c>
+      <c r="B89">
+        <v>136.813295454545</v>
+      </c>
       <c r="C89">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D89">
-        <v>199.849309090909</v>
+        <v>185.967927272727</v>
       </c>
       <c r="E89">
-        <v>265.86739090908998</v>
+        <v>236.67389999999901</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>1</v>
       </c>
+      <c r="B90">
+        <v>136.813295454545</v>
+      </c>
       <c r="C90">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D90">
-        <v>200.18702727272699</v>
+        <v>186.81471818181799</v>
       </c>
       <c r="E90">
-        <v>270.33259090909002</v>
+        <v>240.453681818181</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1</v>
       </c>
+      <c r="B91">
+        <v>136.813295454545</v>
+      </c>
       <c r="C91">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D91">
-        <v>204.79696363636299</v>
+        <v>190.13034545454499</v>
       </c>
       <c r="E91">
-        <v>274.31367272727198</v>
+        <v>243.92901818181801</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1</v>
       </c>
+      <c r="B92">
+        <v>136.813295454545</v>
+      </c>
       <c r="C92">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D92">
-        <v>209.822809090909</v>
+        <v>195.77672727272699</v>
       </c>
       <c r="E92">
-        <v>281.46564545454498</v>
+        <v>251.32221818181799</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>1</v>
       </c>
+      <c r="B93">
+        <v>136.813295454545</v>
+      </c>
       <c r="C93">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D93">
-        <v>217.067945454545</v>
+        <v>197.75146363636301</v>
       </c>
       <c r="E93">
-        <v>287.26009090909002</v>
+        <v>252.88603636363601</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1</v>
       </c>
+      <c r="B94">
+        <v>136.813295454545</v>
+      </c>
       <c r="C94">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D94">
-        <v>217.48219090909001</v>
+        <v>202.72407272727199</v>
       </c>
       <c r="E94">
-        <v>287.79744545454503</v>
+        <v>257.47101818181801</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1</v>
       </c>
+      <c r="B95">
+        <v>136.813295454545</v>
+      </c>
       <c r="C95">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D95">
-        <v>218.05115454545401</v>
+        <v>202.817236363636</v>
       </c>
       <c r="E95">
-        <v>288.51613636363601</v>
+        <v>257.56584545454501</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>1</v>
       </c>
+      <c r="B96">
+        <v>136.813295454545</v>
+      </c>
       <c r="C96">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D96">
-        <v>218.50199999999899</v>
+        <v>202.96030909090899</v>
       </c>
       <c r="E96">
-        <v>289.99843636363602</v>
+        <v>259.11635454545399</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1</v>
       </c>
+      <c r="B97">
+        <v>136.813295454545</v>
+      </c>
       <c r="C97">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D97">
-        <v>219.53511818181801</v>
+        <v>203.36457272727199</v>
       </c>
       <c r="E97">
-        <v>292.95804545454502</v>
+        <v>260.320827272727</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>1</v>
       </c>
+      <c r="B98">
+        <v>136.813295454545</v>
+      </c>
       <c r="C98">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D98">
-        <v>220.69300909090899</v>
+        <v>204.43761818181801</v>
       </c>
       <c r="E98">
-        <v>294.04273636363598</v>
+        <v>261.91625454545402</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>1</v>
       </c>
+      <c r="B99">
+        <v>136.813295454545</v>
+      </c>
       <c r="C99">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D99">
-        <v>221.76106363636299</v>
+        <v>206.08129090909</v>
       </c>
       <c r="E99">
-        <v>294.65828181818102</v>
+        <v>262.987636363636</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1</v>
       </c>
+      <c r="B100">
+        <v>136.813295454545</v>
+      </c>
       <c r="C100">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D100">
-        <v>222.81913636363601</v>
+        <v>207.27744545454499</v>
       </c>
       <c r="E100">
-        <v>296.83598181818098</v>
+        <v>265.87570909090903</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>1</v>
       </c>
+      <c r="B101">
+        <v>136.813295454545</v>
+      </c>
       <c r="C101">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D101">
-        <v>223.94209090909001</v>
+        <v>208.31721818181799</v>
       </c>
       <c r="E101">
-        <v>297.53803636363602</v>
+        <v>267.13009090908997</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>1</v>
       </c>
+      <c r="B102">
+        <v>136.813295454545</v>
+      </c>
       <c r="C102">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D102">
-        <v>225.05839090909001</v>
+        <v>209.13406363636301</v>
       </c>
       <c r="E102">
-        <v>298.04211818181801</v>
+        <v>267.21992727272698</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>1</v>
       </c>
+      <c r="B103">
+        <v>136.813295454545</v>
+      </c>
       <c r="C103">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D103">
-        <v>225.098318181818</v>
+        <v>210.43169999999901</v>
       </c>
       <c r="E103">
-        <v>301.109863636363</v>
+        <v>269.79357272727202</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1</v>
       </c>
+      <c r="B104">
+        <v>136.813295454545</v>
+      </c>
       <c r="C104">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D104">
-        <v>227.061409090909</v>
+        <v>210.979036363636</v>
       </c>
       <c r="E104">
-        <v>301.24295454545398</v>
+        <v>269.81187272727198</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1</v>
       </c>
+      <c r="B105">
+        <v>136.813295454545</v>
+      </c>
       <c r="C105">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D105">
-        <v>228.769963636363</v>
+        <v>212.64599999999899</v>
       </c>
       <c r="E105">
-        <v>302.76019090909</v>
+        <v>271.33409999999901</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>1</v>
       </c>
+      <c r="B106">
+        <v>136.813295454545</v>
+      </c>
       <c r="C106">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D106">
-        <v>229.24909090909</v>
+        <v>213.78891818181799</v>
       </c>
       <c r="E106">
-        <v>304.497027272727</v>
+        <v>273.54008181818102</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>1</v>
       </c>
+      <c r="B107">
+        <v>136.813295454545</v>
+      </c>
       <c r="C107">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D107">
-        <v>236.18978181818099</v>
+        <v>220.40353636363599</v>
       </c>
       <c r="E107">
-        <v>307.67956363636301</v>
+        <v>277.47790909090901</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>1</v>
       </c>
+      <c r="B108">
+        <v>136.813295454545</v>
+      </c>
       <c r="C108">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D108">
-        <v>236.51419090908999</v>
+        <v>220.46841818181801</v>
       </c>
       <c r="E108">
-        <v>309.79570909090899</v>
+        <v>279.44599090909003</v>
       </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>1</v>
       </c>
+      <c r="B109">
+        <v>136.813295454545</v>
+      </c>
       <c r="C109">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D109">
-        <v>239.658463636363</v>
+        <v>222.06218181818099</v>
       </c>
       <c r="E109">
-        <v>314.72672727272698</v>
+        <v>282.12278181818101</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>1</v>
       </c>
+      <c r="B110">
+        <v>136.813295454545</v>
+      </c>
       <c r="C110">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D110">
-        <v>239.764936363636</v>
+        <v>223.24502727272699</v>
       </c>
       <c r="E110">
-        <v>314.98958181818102</v>
+        <v>283.63336363636301</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>1</v>
       </c>
+      <c r="B111">
+        <v>136.813295454545</v>
+      </c>
       <c r="C111">
-        <v>147.81808363636301</v>
+        <v>136.26346363636301</v>
       </c>
       <c r="D111">
-        <v>243.26356363636299</v>
+        <v>225.53252727272701</v>
       </c>
       <c r="E111">
-        <v>319.28009999999898</v>
+        <v>286.73604545454498</v>
       </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1</v>
       </c>
+      <c r="B112">
+        <v>136.813295454545</v>
+      </c>
       <c r="C112">
-        <v>155.371325454545</v>
+        <v>143.26221545454499</v>
       </c>
       <c r="D112">
-        <v>245.02369090908999</v>
+        <v>228.45553636363601</v>
       </c>
       <c r="E112">
-        <v>320.424681818181</v>
+        <v>289.62744545454501</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>1</v>
       </c>
+      <c r="B113">
+        <v>136.813295454545</v>
+      </c>
       <c r="C113">
-        <v>159.57084272727201</v>
+        <v>145.203512727272</v>
       </c>
       <c r="D113">
-        <v>250.13271818181801</v>
+        <v>233.60282727272701</v>
       </c>
       <c r="E113">
-        <v>324.26435454545401</v>
+        <v>294.43868181818101</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1</v>
       </c>
+      <c r="B114">
+        <v>136.813295454545</v>
+      </c>
       <c r="C114">
-        <v>160.489502727272</v>
+        <v>148.121697272727</v>
       </c>
       <c r="D114">
-        <v>251.668254545454</v>
+        <v>234.241663636363</v>
       </c>
       <c r="E114">
-        <v>329.02900909090903</v>
+        <v>297.905699999999</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1</v>
       </c>
+      <c r="B115">
+        <v>136.813295454545</v>
+      </c>
       <c r="C115">
-        <v>162.32316272727201</v>
+        <v>149.28224999999901</v>
       </c>
       <c r="D115">
-        <v>254.742654545454</v>
+        <v>235.99513636363599</v>
       </c>
       <c r="E115">
-        <v>331.118536363636</v>
+        <v>298.84565454545401</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>1</v>
       </c>
+      <c r="B116">
+        <v>136.813295454545</v>
+      </c>
       <c r="C116">
-        <v>163.60715727272699</v>
+        <v>150.573231818181</v>
       </c>
       <c r="D116">
-        <v>257.10668181818102</v>
+        <v>239.91799090909001</v>
       </c>
       <c r="E116">
-        <v>334.32103636363598</v>
+        <v>304.270772727272</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1</v>
       </c>
+      <c r="B117">
+        <v>136.813295454545</v>
+      </c>
       <c r="C117">
-        <v>165.63213545454499</v>
+        <v>151.976176363636</v>
       </c>
       <c r="D117">
-        <v>258.77697272727198</v>
+        <v>241.17403636363599</v>
       </c>
       <c r="E117">
-        <v>336.51703636363601</v>
+        <v>306.70134545454499</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1</v>
       </c>
+      <c r="B118">
+        <v>136.813295454545</v>
+      </c>
       <c r="C118">
-        <v>165.799497272727</v>
+        <v>152.01443999999901</v>
       </c>
       <c r="D118">
-        <v>260.61861818181802</v>
+        <v>243.48482727272699</v>
       </c>
       <c r="E118">
-        <v>338.24555454545401</v>
+        <v>308.183645454545</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1</v>
       </c>
+      <c r="B119">
+        <v>136.813295454545</v>
+      </c>
       <c r="C119">
-        <v>170.58095454545401</v>
+        <v>157.32992454545399</v>
       </c>
       <c r="D119">
-        <v>263.74791818181802</v>
+        <v>246.471054545454</v>
       </c>
       <c r="E119">
-        <v>338.69473636363603</v>
+        <v>308.24519999999899</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>1</v>
       </c>
+      <c r="B120">
+        <v>136.813295454545</v>
+      </c>
       <c r="C120">
-        <v>173.82005454545401</v>
+        <v>160.121506363636</v>
       </c>
       <c r="D120">
-        <v>263.957536363636</v>
+        <v>246.70063636363599</v>
       </c>
       <c r="E120">
-        <v>341.64769090908999</v>
+        <v>308.602881818181</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>1</v>
       </c>
+      <c r="B121">
+        <v>136.813295454545</v>
+      </c>
       <c r="C121">
-        <v>179.73927272727201</v>
+        <v>162.81360272727201</v>
       </c>
       <c r="D121">
-        <v>268.84529999999899</v>
+        <v>248.89497272727201</v>
       </c>
       <c r="E121">
-        <v>342.58265454545398</v>
+        <v>313.21780909090899</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>1</v>
       </c>
+      <c r="B122">
+        <v>136.813295454545</v>
+      </c>
       <c r="C122">
-        <v>192.08678181818101</v>
+        <v>177.074127272727</v>
       </c>
       <c r="D122">
-        <v>282.33739090909</v>
+        <v>264.31854545454502</v>
       </c>
       <c r="E122">
-        <v>358.90958181818098</v>
+        <v>329.91073636363598</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>1</v>
       </c>
+      <c r="B123">
+        <v>136.813295454545</v>
+      </c>
       <c r="C123">
-        <v>223.62599999999901</v>
+        <v>205.771854545454</v>
       </c>
       <c r="D123">
-        <v>305.55010909090902</v>
+        <v>286.76432727272697</v>
       </c>
       <c r="E123">
-        <v>382.84764545454499</v>
+        <v>354.70058181818098</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -7192,19 +7349,19 @@
         <v>2</v>
       </c>
       <c r="B124">
-        <v>218.91624545454499</v>
+        <v>213.862118181818</v>
       </c>
       <c r="C124">
-        <v>229.071081818181</v>
+        <v>219.92108181818099</v>
       </c>
       <c r="D124">
-        <v>239.174345454545</v>
+        <v>230.119172727272</v>
       </c>
       <c r="E124">
-        <v>240.33889090909</v>
+        <v>232.366745454545</v>
       </c>
       <c r="F124">
-        <v>218.748218181818</v>
+        <v>218.88463636363599</v>
       </c>
       <c r="G124">
         <v>130</v>
@@ -7218,19 +7375,19 @@
         <v>2</v>
       </c>
       <c r="B125">
-        <v>232.50649090908999</v>
+        <v>220.628127272727</v>
       </c>
       <c r="C125">
-        <v>240.112636363636</v>
+        <v>230.139136363636</v>
       </c>
       <c r="D125">
-        <v>252.075845454545</v>
+        <v>242.811054545454</v>
       </c>
       <c r="E125">
-        <v>255.99869999999899</v>
+        <v>247.79863636363601</v>
       </c>
       <c r="F125">
-        <v>236.87519999999901</v>
+        <v>236.72380909090899</v>
       </c>
       <c r="G125">
         <v>320</v>
@@ -7241,19 +7398,19 @@
         <v>2</v>
       </c>
       <c r="B126">
-        <v>232.50649090908999</v>
+        <v>220.628127272727</v>
       </c>
       <c r="C126">
-        <v>240.112636363636</v>
+        <v>230.139136363636</v>
       </c>
       <c r="D126">
-        <v>252.075845454545</v>
+        <v>242.811054545454</v>
       </c>
       <c r="E126">
-        <v>255.99869999999899</v>
+        <v>247.79863636363601</v>
       </c>
       <c r="F126">
-        <v>236.87519999999901</v>
+        <v>236.72380909090899</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -7261,19 +7418,19 @@
         <v>2</v>
       </c>
       <c r="B127">
-        <v>232.50649090908999</v>
+        <v>220.628127272727</v>
       </c>
       <c r="C127">
-        <v>240.112636363636</v>
+        <v>230.139136363636</v>
       </c>
       <c r="D127">
-        <v>252.075845454545</v>
+        <v>242.811054545454</v>
       </c>
       <c r="E127">
-        <v>255.99869999999899</v>
+        <v>247.79863636363601</v>
       </c>
       <c r="F127">
-        <v>236.87519999999901</v>
+        <v>236.72380909090899</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -7281,19 +7438,19 @@
         <v>2</v>
       </c>
       <c r="B128">
-        <v>232.50649090908999</v>
+        <v>220.628127272727</v>
       </c>
       <c r="C128">
-        <v>240.112636363636</v>
+        <v>230.139136363636</v>
       </c>
       <c r="D128">
-        <v>252.075845454545</v>
+        <v>242.811054545454</v>
       </c>
       <c r="E128">
-        <v>255.99869999999899</v>
+        <v>247.79863636363601</v>
       </c>
       <c r="F128">
-        <v>236.87519999999901</v>
+        <v>236.72380909090899</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -7301,19 +7458,19 @@
         <v>2</v>
       </c>
       <c r="B129">
-        <v>235.14834545454499</v>
+        <v>223.512872727272</v>
       </c>
       <c r="C129">
-        <v>242.97575454545401</v>
+        <v>232.05065454545399</v>
       </c>
       <c r="D129">
-        <v>257.44939090909003</v>
+        <v>246.802118181818</v>
       </c>
       <c r="E129">
-        <v>258.44590909090903</v>
+        <v>249.13619999999901</v>
       </c>
       <c r="F129">
-        <v>237.36430909090899</v>
+        <v>236.753754545454</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -7321,19 +7478,19 @@
         <v>2</v>
       </c>
       <c r="B130">
-        <v>235.14834545454499</v>
+        <v>227.38748181818099</v>
       </c>
       <c r="C130">
-        <v>248.998118181818</v>
+        <v>237.82347272727199</v>
       </c>
       <c r="D130">
-        <v>257.90189999999899</v>
+        <v>247.74207272727199</v>
       </c>
       <c r="E130">
-        <v>258.44590909090903</v>
+        <v>249.13619999999901</v>
       </c>
       <c r="F130">
-        <v>240.62004545454499</v>
+        <v>239.50873636363599</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -7341,19 +7498,19 @@
         <v>2</v>
       </c>
       <c r="B131">
-        <v>236.58572727272701</v>
+        <v>227.38748181818099</v>
       </c>
       <c r="C131">
-        <v>248.998118181818</v>
+        <v>237.82347272727199</v>
       </c>
       <c r="D131">
-        <v>257.90189999999899</v>
+        <v>247.74207272727199</v>
       </c>
       <c r="E131">
-        <v>263.21056363636302</v>
+        <v>253.754454545454</v>
       </c>
       <c r="F131">
-        <v>240.62004545454499</v>
+        <v>239.50873636363599</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -7361,19 +7518,19 @@
         <v>2</v>
       </c>
       <c r="B132">
-        <v>241.08087272727201</v>
+        <v>229.751509090909</v>
       </c>
       <c r="C132">
-        <v>253.413409090909</v>
+        <v>241.50343636363601</v>
       </c>
       <c r="D132">
-        <v>262.64159999999998</v>
+        <v>251.96271818181799</v>
       </c>
       <c r="E132">
-        <v>263.21056363636302</v>
+        <v>253.754454545454</v>
       </c>
       <c r="F132">
-        <v>248.74690909090901</v>
+        <v>248.03986363636301</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -7381,19 +7538,19 @@
         <v>2</v>
       </c>
       <c r="B133">
-        <v>241.08087272727201</v>
+        <v>229.751509090909</v>
       </c>
       <c r="C133">
-        <v>253.413409090909</v>
+        <v>241.50343636363601</v>
       </c>
       <c r="D133">
-        <v>262.64159999999998</v>
+        <v>251.96271818181799</v>
       </c>
       <c r="E133">
-        <v>263.21056363636302</v>
+        <v>253.754454545454</v>
       </c>
       <c r="F133">
-        <v>248.74690909090901</v>
+        <v>248.03986363636301</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -7401,19 +7558,19 @@
         <v>2</v>
       </c>
       <c r="B134">
-        <v>241.08087272727201</v>
+        <v>229.751509090909</v>
       </c>
       <c r="C134">
-        <v>253.413409090909</v>
+        <v>241.50343636363601</v>
       </c>
       <c r="D134">
-        <v>262.64159999999998</v>
+        <v>251.96271818181799</v>
       </c>
       <c r="E134">
-        <v>263.21056363636302</v>
+        <v>253.754454545454</v>
       </c>
       <c r="F134">
-        <v>248.74690909090901</v>
+        <v>248.570563636363</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -7421,19 +7578,19 @@
         <v>2</v>
       </c>
       <c r="B135">
-        <v>241.08087272727201</v>
+        <v>230.32879090909</v>
       </c>
       <c r="C135">
-        <v>253.413409090909</v>
+        <v>241.50343636363601</v>
       </c>
       <c r="D135">
-        <v>262.64159999999998</v>
+        <v>251.96271818181799</v>
       </c>
       <c r="E135">
-        <v>263.93590909090898</v>
+        <v>254.446527272727</v>
       </c>
       <c r="F135">
-        <v>248.74690909090901</v>
+        <v>248.570563636363</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
@@ -7441,19 +7598,19 @@
         <v>2</v>
       </c>
       <c r="B136">
-        <v>241.67312727272699</v>
+        <v>230.32879090909</v>
       </c>
       <c r="C136">
-        <v>254.10049090909001</v>
+        <v>242.138945454545</v>
       </c>
       <c r="D136">
-        <v>263.38191818181798</v>
+        <v>252.65978181818099</v>
       </c>
       <c r="E136">
-        <v>263.93590909090898</v>
+        <v>254.446527272727</v>
       </c>
       <c r="F136">
-        <v>248.74690909090901</v>
+        <v>248.570563636363</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -7461,19 +7618,19 @@
         <v>2</v>
       </c>
       <c r="B137">
-        <v>241.67312727272699</v>
+        <v>231.20719090909</v>
       </c>
       <c r="C137">
-        <v>254.10049090909001</v>
+        <v>242.138945454545</v>
       </c>
       <c r="D137">
-        <v>263.38191818181798</v>
+        <v>252.65978181818099</v>
       </c>
       <c r="E137">
-        <v>268.85195454545402</v>
+        <v>259.18622727272702</v>
       </c>
       <c r="F137">
-        <v>249.30589090909001</v>
+        <v>248.570563636363</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -7481,19 +7638,19 @@
         <v>2</v>
       </c>
       <c r="B138">
-        <v>241.78126363636301</v>
+        <v>231.20719090909</v>
       </c>
       <c r="C138">
-        <v>254.719363636363</v>
+        <v>244.215163636363</v>
       </c>
       <c r="D138">
-        <v>268.97672727272698</v>
+        <v>259.58882727272697</v>
       </c>
       <c r="E138">
-        <v>270.56383636363603</v>
+        <v>259.94817272727198</v>
       </c>
       <c r="F138">
-        <v>249.30589090909001</v>
+        <v>248.570563636363</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -7501,19 +7658,19 @@
         <v>2</v>
       </c>
       <c r="B139">
-        <v>241.78126363636301</v>
+        <v>231.20719090909</v>
       </c>
       <c r="C139">
-        <v>254.719363636363</v>
+        <v>244.215163636363</v>
       </c>
       <c r="D139">
-        <v>268.97672727272698</v>
+        <v>259.58882727272697</v>
       </c>
       <c r="E139">
-        <v>270.56383636363603</v>
+        <v>259.94817272727198</v>
       </c>
       <c r="F139">
-        <v>250.022918181818</v>
+        <v>248.71529999999899</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -7521,19 +7678,19 @@
         <v>2</v>
       </c>
       <c r="B140">
-        <v>241.78126363636301</v>
+        <v>231.20719090909</v>
       </c>
       <c r="C140">
-        <v>254.719363636363</v>
+        <v>244.215163636363</v>
       </c>
       <c r="D140">
-        <v>268.97672727272698</v>
+        <v>259.58882727272697</v>
       </c>
       <c r="E140">
-        <v>270.56383636363603</v>
+        <v>259.94817272727198</v>
       </c>
       <c r="F140">
-        <v>250.022918181818</v>
+        <v>248.71529999999899</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -7541,19 +7698,19 @@
         <v>2</v>
       </c>
       <c r="B141">
-        <v>241.78126363636301</v>
+        <v>231.20719090909</v>
       </c>
       <c r="C141">
-        <v>254.719363636363</v>
+        <v>244.215163636363</v>
       </c>
       <c r="D141">
-        <v>268.97672727272698</v>
+        <v>259.58882727272697</v>
       </c>
       <c r="E141">
-        <v>270.56383636363603</v>
+        <v>259.94817272727198</v>
       </c>
       <c r="F141">
-        <v>250.022918181818</v>
+        <v>248.71529999999899</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -7561,19 +7718,19 @@
         <v>2</v>
       </c>
       <c r="B142">
-        <v>241.78126363636301</v>
+        <v>233.54293636363599</v>
       </c>
       <c r="C142">
-        <v>254.719363636363</v>
+        <v>244.215163636363</v>
       </c>
       <c r="D142">
-        <v>268.97672727272698</v>
+        <v>259.58882727272697</v>
       </c>
       <c r="E142">
-        <v>270.56383636363603</v>
+        <v>259.94817272727198</v>
       </c>
       <c r="F142">
-        <v>250.022918181818</v>
+        <v>248.71529999999899</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -7581,19 +7738,19 @@
         <v>2</v>
       </c>
       <c r="B143">
-        <v>242.78609999999901</v>
+        <v>233.54293636363599</v>
       </c>
       <c r="C143">
-        <v>257.579154545454</v>
+        <v>245.35641818181799</v>
       </c>
       <c r="D143">
-        <v>272.32063636363603</v>
+        <v>260.85319090909002</v>
       </c>
       <c r="E143">
-        <v>273.31549090908999</v>
+        <v>264.91246363636299</v>
       </c>
       <c r="F143">
-        <v>250.022918181818</v>
+        <v>248.71529999999899</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -7601,19 +7758,19 @@
         <v>2</v>
       </c>
       <c r="B144">
-        <v>242.78609999999901</v>
+        <v>234.12520909090901</v>
       </c>
       <c r="C144">
-        <v>257.579154545454</v>
+        <v>245.35641818181799</v>
       </c>
       <c r="D144">
-        <v>272.32063636363603</v>
+        <v>260.85319090909002</v>
       </c>
       <c r="E144">
-        <v>273.31549090908999</v>
+        <v>264.91246363636299</v>
       </c>
       <c r="F144">
-        <v>250.022918181818</v>
+        <v>248.71529999999899</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -7621,19 +7778,19 @@
         <v>2</v>
       </c>
       <c r="B145">
-        <v>242.78609999999901</v>
+        <v>234.12520909090901</v>
       </c>
       <c r="C145">
-        <v>258.26956363636299</v>
+        <v>245.995254545454</v>
       </c>
       <c r="D145">
-        <v>272.917881818181</v>
+        <v>260.85319090909002</v>
       </c>
       <c r="E145">
-        <v>273.31549090908999</v>
+        <v>264.91246363636299</v>
       </c>
       <c r="F145">
-        <v>250.022918181818</v>
+        <v>248.71529999999899</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
@@ -7641,19 +7798,19 @@
         <v>2</v>
       </c>
       <c r="B146">
-        <v>242.78609999999901</v>
+        <v>234.12520909090901</v>
       </c>
       <c r="C146">
-        <v>258.26956363636299</v>
+        <v>245.995254545454</v>
       </c>
       <c r="D146">
-        <v>272.917881818181</v>
+        <v>260.85319090909002</v>
       </c>
       <c r="E146">
-        <v>273.31549090908999</v>
+        <v>264.91246363636299</v>
       </c>
       <c r="F146">
-        <v>250.66508181818099</v>
+        <v>248.84839090909</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -7661,19 +7818,19 @@
         <v>2</v>
       </c>
       <c r="B147">
-        <v>242.78609999999901</v>
+        <v>234.12520909090901</v>
       </c>
       <c r="C147">
-        <v>258.26956363636299</v>
+        <v>245.995254545454</v>
       </c>
       <c r="D147">
-        <v>272.917881818181</v>
+        <v>260.85319090909002</v>
       </c>
       <c r="E147">
-        <v>273.31549090908999</v>
+        <v>264.91246363636299</v>
       </c>
       <c r="F147">
-        <v>250.66508181818099</v>
+        <v>248.84839090909</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -7681,19 +7838,19 @@
         <v>2</v>
       </c>
       <c r="B148">
-        <v>244.09870909090901</v>
+        <v>234.12520909090901</v>
       </c>
       <c r="C148">
-        <v>258.26956363636299</v>
+        <v>245.995254545454</v>
       </c>
       <c r="D148">
-        <v>272.917881818181</v>
+        <v>261.12935454545402</v>
       </c>
       <c r="E148">
-        <v>276.63777272727202</v>
+        <v>266.86723636363598</v>
       </c>
       <c r="F148">
-        <v>250.66508181818099</v>
+        <v>248.84839090909</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -7701,19 +7858,19 @@
         <v>2</v>
       </c>
       <c r="B149">
-        <v>244.09870909090901</v>
+        <v>234.12520909090901</v>
       </c>
       <c r="C149">
-        <v>258.26956363636299</v>
+        <v>245.995254545454</v>
       </c>
       <c r="D149">
-        <v>272.917881818181</v>
+        <v>261.12935454545402</v>
       </c>
       <c r="E149">
-        <v>276.63777272727202</v>
+        <v>266.86723636363598</v>
       </c>
       <c r="F149">
-        <v>250.66508181818099</v>
+        <v>248.84839090909</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -7721,19 +7878,19 @@
         <v>2</v>
       </c>
       <c r="B150">
-        <v>244.71259090909001</v>
+        <v>234.12520909090901</v>
       </c>
       <c r="C150">
-        <v>258.26956363636299</v>
+        <v>245.995254545454</v>
       </c>
       <c r="D150">
-        <v>273.06428181818097</v>
+        <v>261.82974545454499</v>
       </c>
       <c r="E150">
-        <v>277.36977272727199</v>
+        <v>267.55930909090898</v>
       </c>
       <c r="F150">
-        <v>250.96120909090899</v>
+        <v>248.84839090909</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -7741,19 +7898,19 @@
         <v>2</v>
       </c>
       <c r="B151">
-        <v>244.71259090909001</v>
+        <v>237.27280909090899</v>
       </c>
       <c r="C151">
-        <v>258.26956363636299</v>
+        <v>245.995254545454</v>
       </c>
       <c r="D151">
-        <v>273.06428181818097</v>
+        <v>261.82974545454499</v>
       </c>
       <c r="E151">
-        <v>277.36977272727199</v>
+        <v>267.55930909090898</v>
       </c>
       <c r="F151">
-        <v>250.96120909090899</v>
+        <v>249.29590909090899</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -7761,19 +7918,19 @@
         <v>2</v>
       </c>
       <c r="B152">
-        <v>244.71259090909001</v>
+        <v>237.27280909090899</v>
       </c>
       <c r="C152">
-        <v>263.67804545454499</v>
+        <v>250.34566363636301</v>
       </c>
       <c r="D152">
-        <v>273.06428181818097</v>
+        <v>261.82974545454499</v>
       </c>
       <c r="E152">
-        <v>277.36977272727199</v>
+        <v>267.55930909090898</v>
       </c>
       <c r="F152">
-        <v>250.96120909090899</v>
+        <v>249.29590909090899</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -7781,19 +7938,19 @@
         <v>2</v>
       </c>
       <c r="B153">
-        <v>244.71259090909001</v>
+        <v>237.27280909090899</v>
       </c>
       <c r="C153">
-        <v>263.67804545454499</v>
+        <v>250.34566363636301</v>
       </c>
       <c r="D153">
-        <v>273.06428181818097</v>
+        <v>261.82974545454499</v>
       </c>
       <c r="E153">
-        <v>277.36977272727199</v>
+        <v>267.55930909090898</v>
       </c>
       <c r="F153">
-        <v>250.96120909090899</v>
+        <v>249.29590909090899</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -7801,19 +7958,19 @@
         <v>2</v>
       </c>
       <c r="B154">
-        <v>244.71259090909001</v>
+        <v>238.14289090909</v>
       </c>
       <c r="C154">
-        <v>263.67804545454499</v>
+        <v>250.34566363636301</v>
       </c>
       <c r="D154">
-        <v>273.06428181818097</v>
+        <v>261.82974545454499</v>
       </c>
       <c r="E154">
-        <v>277.36977272727199</v>
+        <v>267.55930909090898</v>
       </c>
       <c r="F154">
-        <v>250.96120909090899</v>
+        <v>249.29590909090899</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -7821,19 +7978,19 @@
         <v>2</v>
       </c>
       <c r="B155">
-        <v>244.71259090909001</v>
+        <v>238.14289090909</v>
       </c>
       <c r="C155">
-        <v>263.67804545454499</v>
+        <v>250.34566363636301</v>
       </c>
       <c r="D155">
-        <v>273.06428181818097</v>
+        <v>261.82974545454499</v>
       </c>
       <c r="E155">
-        <v>277.36977272727199</v>
+        <v>267.55930909090898</v>
       </c>
       <c r="F155">
-        <v>251.380445454545</v>
+        <v>249.971345454545</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -7841,19 +7998,19 @@
         <v>2</v>
       </c>
       <c r="B156">
-        <v>244.71259090909001</v>
+        <v>238.14289090909</v>
       </c>
       <c r="C156">
-        <v>263.67804545454499</v>
+        <v>250.34566363636301</v>
       </c>
       <c r="D156">
-        <v>273.06428181818097</v>
+        <v>261.82974545454499</v>
       </c>
       <c r="E156">
-        <v>277.36977272727199</v>
+        <v>267.55930909090898</v>
       </c>
       <c r="F156">
-        <v>251.380445454545</v>
+        <v>249.971345454545</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -7861,19 +8018,19 @@
         <v>2</v>
       </c>
       <c r="B157">
-        <v>247.33448181818099</v>
+        <v>238.14289090909</v>
       </c>
       <c r="C157">
-        <v>265.80583636363599</v>
+        <v>253.91416363636301</v>
       </c>
       <c r="D157">
-        <v>281.74679999999898</v>
+        <v>271.78161818181798</v>
       </c>
       <c r="E157">
-        <v>284.490136363636</v>
+        <v>275.55474545454501</v>
       </c>
       <c r="F157">
-        <v>263.77952727272702</v>
+        <v>263.37859090909001</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -7881,19 +8038,19 @@
         <v>2</v>
       </c>
       <c r="B158">
-        <v>249.354136363636</v>
+        <v>238.14289090909</v>
       </c>
       <c r="C158">
-        <v>265.80583636363599</v>
+        <v>253.91416363636301</v>
       </c>
       <c r="D158">
-        <v>281.74679999999898</v>
+        <v>271.78161818181798</v>
       </c>
       <c r="E158">
-        <v>284.490136363636</v>
+        <v>275.55474545454501</v>
       </c>
       <c r="F158">
-        <v>263.77952727272702</v>
+        <v>263.37859090909001</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -7901,19 +8058,19 @@
         <v>2</v>
       </c>
       <c r="B159">
-        <v>249.354136363636</v>
+        <v>238.60039090909001</v>
       </c>
       <c r="C159">
-        <v>265.80583636363599</v>
+        <v>253.91416363636301</v>
       </c>
       <c r="D159">
-        <v>281.74679999999898</v>
+        <v>271.78161818181798</v>
       </c>
       <c r="E159">
-        <v>284.490136363636</v>
+        <v>275.55474545454501</v>
       </c>
       <c r="F159">
-        <v>263.77952727272702</v>
+        <v>263.37859090909001</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -7921,19 +8078,19 @@
         <v>2</v>
       </c>
       <c r="B160">
-        <v>249.354136363636</v>
+        <v>239.67010909090899</v>
       </c>
       <c r="C160">
-        <v>268.261363636363</v>
+        <v>255.63436363636299</v>
       </c>
       <c r="D160">
-        <v>286.78595454545399</v>
+        <v>275.702809090909</v>
       </c>
       <c r="E160">
-        <v>290.31951818181801</v>
+        <v>281.77674545454499</v>
       </c>
       <c r="F160">
-        <v>266.45299090908998</v>
+        <v>265.41321818181802</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -7941,19 +8098,19 @@
         <v>2</v>
       </c>
       <c r="B161">
-        <v>253.57311818181799</v>
+        <v>240.21744545454499</v>
       </c>
       <c r="C161">
-        <v>268.906854545454</v>
+        <v>256.23327272727198</v>
       </c>
       <c r="D161">
-        <v>286.94732727272702</v>
+        <v>276.38489999999899</v>
       </c>
       <c r="E161">
-        <v>293.76823636363599</v>
+        <v>283.82800909090901</v>
       </c>
       <c r="F161">
-        <v>267.15171818181801</v>
+        <v>266.07534545454502</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -7961,19 +8118,19 @@
         <v>2</v>
       </c>
       <c r="B162">
-        <v>254.142081818181</v>
+        <v>240.21744545454499</v>
       </c>
       <c r="C162">
-        <v>268.906854545454</v>
+        <v>256.23327272727198</v>
       </c>
       <c r="D162">
-        <v>287.50464545454503</v>
+        <v>276.38489999999899</v>
       </c>
       <c r="E162">
-        <v>294.48193636363601</v>
+        <v>284.50677272727199</v>
       </c>
       <c r="F162">
-        <v>267.15171818181801</v>
+        <v>266.07534545454502</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -7981,59 +8138,53 @@
         <v>2</v>
       </c>
       <c r="B163">
-        <v>254.142081818181</v>
+        <v>249.853227272727</v>
       </c>
       <c r="C163">
-        <v>268.906854545454</v>
+        <v>256.23327272727198</v>
       </c>
       <c r="D163">
-        <v>287.50464545454503</v>
+        <v>276.38489999999899</v>
       </c>
       <c r="E163">
-        <v>294.48193636363601</v>
+        <v>284.50677272727199</v>
       </c>
       <c r="F163">
-        <v>267.15171818181801</v>
+        <v>266.07534545454502</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>2</v>
       </c>
-      <c r="B164">
-        <v>262.66988181818101</v>
-      </c>
       <c r="C164">
-        <v>269.06989090909002</v>
+        <v>256.39630909090903</v>
       </c>
       <c r="D164">
-        <v>287.50464545454503</v>
+        <v>276.787499999999</v>
       </c>
       <c r="E164">
-        <v>294.48193636363601</v>
+        <v>284.50677272727199</v>
       </c>
       <c r="F164">
-        <v>273.22731818181802</v>
+        <v>272.80309090908997</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>2</v>
       </c>
-      <c r="B165">
-        <v>287.927209090909</v>
-      </c>
       <c r="C165">
-        <v>285.20383636363601</v>
+        <v>269.89838181818101</v>
       </c>
       <c r="D165">
-        <v>304.14599999999899</v>
+        <v>291.49071818181801</v>
       </c>
       <c r="E165">
-        <v>304.35229090909002</v>
+        <v>293.25084545454501</v>
       </c>
       <c r="F165">
-        <v>286.187045454545</v>
+        <v>283.31394545454498</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -8041,16 +8192,16 @@
         <v>2</v>
       </c>
       <c r="C166">
-        <v>335.04139090909001</v>
+        <v>311.978399999999</v>
       </c>
       <c r="D166">
-        <v>363.27662727272701</v>
+        <v>342.63089999999897</v>
       </c>
       <c r="E166">
-        <v>360.16396363636301</v>
+        <v>346.196072727272</v>
       </c>
       <c r="F166">
-        <v>335.22439090909</v>
+        <v>326.43872727272702</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
@@ -8058,16 +8209,16 @@
         <v>2</v>
       </c>
       <c r="C167">
-        <v>335.04139090909001</v>
+        <v>311.978399999999</v>
       </c>
       <c r="D167">
-        <v>365.600727272727</v>
+        <v>344.46589090908998</v>
       </c>
       <c r="E167">
-        <v>362.28676363636299</v>
+        <v>348.042709090909</v>
       </c>
       <c r="F167">
-        <v>337.28896363636301</v>
+        <v>328.10236363636301</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
@@ -8075,16 +8226,16 @@
         <v>2</v>
       </c>
       <c r="C168">
-        <v>473.795318181818</v>
+        <v>459.494699999999</v>
       </c>
       <c r="D168">
-        <v>365.600727272727</v>
+        <v>344.46589090908998</v>
       </c>
       <c r="E168">
-        <v>362.28676363636299</v>
+        <v>348.042709090909</v>
       </c>
       <c r="F168">
-        <v>337.28896363636301</v>
+        <v>328.10236363636301</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -8092,13 +8243,13 @@
         <v>2</v>
       </c>
       <c r="D169">
-        <v>365.600727272727</v>
+        <v>344.46589090908998</v>
       </c>
       <c r="E169">
-        <v>362.28676363636299</v>
+        <v>348.042709090909</v>
       </c>
       <c r="F169">
-        <v>337.28896363636301</v>
+        <v>328.10236363636301</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -8106,13 +8257,13 @@
         <v>2</v>
       </c>
       <c r="D170">
-        <v>365.600727272727</v>
+        <v>344.46589090908998</v>
       </c>
       <c r="E170">
-        <v>362.28676363636299</v>
+        <v>348.042709090909</v>
       </c>
       <c r="F170">
-        <v>337.28896363636301</v>
+        <v>328.10236363636301</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -8120,13 +8271,13 @@
         <v>2</v>
       </c>
       <c r="D171">
-        <v>365.600727272727</v>
+        <v>344.46589090908998</v>
       </c>
       <c r="E171">
-        <v>362.28676363636299</v>
+        <v>348.042709090909</v>
       </c>
       <c r="F171">
-        <v>337.28896363636301</v>
+        <v>328.10236363636301</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -8134,13 +8285,13 @@
         <v>2</v>
       </c>
       <c r="D172">
-        <v>510.668154545454</v>
+        <v>500.30536363636298</v>
       </c>
       <c r="E172">
-        <v>506.40092727272702</v>
+        <v>497.69678181818102</v>
       </c>
       <c r="F172">
-        <v>477.262336363636</v>
+        <v>478.36033636363601</v>
       </c>
     </row>
   </sheetData>
